--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,23 +473,23 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>83568.2</v>
+        <v>130768.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>22866.67</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>60701.53</v>
+        <v>130768.2</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>29303.2</v>
+        <v>53603.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>29303.2</v>
+        <v>53603.2</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>40296</v>
+        <v>48596</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>40296</v>
+        <v>48596</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>7086.3</v>
+        <v>14586.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4486.3</v>
+        <v>14586.3</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>38529.36</v>
+        <v>48927.36</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>38529.36</v>
+        <v>48927.36</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>10796</v>
+        <v>11194</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10796</v>
+        <v>11194</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>15029.91</v>
+        <v>26035.41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>15029.91</v>
+        <v>26035.41</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>21695.11</v>
+        <v>22476.03</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>21495.11</v>
+        <v>22276.03</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>35796</v>
+        <v>46266.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>35796</v>
+        <v>46266.7</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>7800</v>
+        <v>8600</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7800</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>33400</v>
+        <v>57307.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>33400</v>
+        <v>57307.7</v>
       </c>
     </row>
     <row r="13">
@@ -881,11 +881,11 @@
         <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>72784</v>
+        <v>85576</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>72784</v>
+        <v>85576</v>
       </c>
     </row>
     <row r="15">
@@ -915,23 +915,23 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>9996</v>
+        <v>24188</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>9598</v>
+        <v>24188</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>12996</v>
+        <v>74190</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>12996</v>
+        <v>74190</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>11194</v>
+        <v>13788</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>11194</v>
+        <v>13788</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>2530.6</v>
+        <v>2914.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2530.6</v>
+        <v>2914.6</v>
       </c>
     </row>
     <row r="19">
@@ -1051,23 +1051,23 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>47955.8</v>
+        <v>50733.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>42955.8</v>
+        <v>50733.9</v>
       </c>
     </row>
     <row r="20">
@@ -1085,23 +1085,23 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>54149.8</v>
+        <v>74747.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>50149.8</v>
+        <v>74747.8</v>
       </c>
     </row>
     <row r="21">
@@ -1187,11 +1187,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>74584</v>
+        <v>84982</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>74584</v>
+        <v>84982</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>150000</v>
       </c>
       <c r="D24" t="n">
-        <v>1200</v>
+        <v>2196</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1200</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="25">
@@ -1259,19 +1259,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>9800</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>68166</v>
+        <v>77966</v>
       </c>
     </row>
     <row r="26">
@@ -1289,11 +1289,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>20358</v>
+        <v>21154</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>20358</v>
+        <v>21154</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>20398</v>
+        <v>24058</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>20398</v>
+        <v>24058</v>
       </c>
     </row>
     <row r="28">
@@ -1357,23 +1357,23 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>12996</v>
+        <v>13394</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>19399.98</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>149.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>-6403.98</v>
+        <v>13394</v>
       </c>
     </row>
     <row r="29">
@@ -1395,19 +1395,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>73382</v>
+        <v>80382</v>
       </c>
     </row>
     <row r="30">
@@ -1527,23 +1527,23 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>70181.64</v>
+        <v>94375.64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>33800</v>
+        <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>36381.64</v>
+        <v>94375.64</v>
       </c>
     </row>
     <row r="34">
@@ -1561,23 +1561,23 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>67279.75999999999</v>
+        <v>77529.84999999999</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>61279.75999999999</v>
+        <v>77529.84999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1595,23 +1595,23 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>43549</v>
+        <v>45488.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>36949</v>
+        <v>45488.92</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>10398</v>
+        <v>10996</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10398</v>
+        <v>10996</v>
       </c>
     </row>
     <row r="37">
@@ -1697,11 +1697,11 @@
         <v>30000</v>
       </c>
       <c r="D38" t="n">
-        <v>499</v>
+        <v>897</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>499</v>
+        <v>897</v>
       </c>
     </row>
     <row r="39">
@@ -1731,11 +1731,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>28074</v>
+        <v>48472</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>28074</v>
+        <v>48472</v>
       </c>
     </row>
     <row r="40">
@@ -1765,23 +1765,23 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>174694</v>
+        <v>380238</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>162694</v>
+        <v>380238</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>28395</v>
+        <v>49191</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>28395</v>
+        <v>49191</v>
       </c>
     </row>
     <row r="42">
@@ -1833,23 +1833,23 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>16596</v>
+        <v>116372</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>7600</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>8996</v>
+        <v>116372</v>
       </c>
     </row>
     <row r="43">
@@ -1935,11 +1935,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>23481.5</v>
+        <v>42355.64000000001</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>23481.5</v>
+        <v>42355.64000000001</v>
       </c>
     </row>
     <row r="46">
@@ -2003,11 +2003,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>66477</v>
+        <v>139540</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>66477</v>
+        <v>139540</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>27983</v>
+        <v>64521</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>27983</v>
+        <v>64521</v>
       </c>
     </row>
     <row r="49">
@@ -2071,11 +2071,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>95807</v>
+        <v>134512.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>95807</v>
+        <v>134512.5</v>
       </c>
     </row>
     <row r="50">
@@ -2173,11 +2173,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>91504</v>
+        <v>196419</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>91504</v>
+        <v>196419</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>35106.1</v>
+        <v>57792.10000000001</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>35106.1</v>
+        <v>57792.10000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>130278</v>
+        <v>167022</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>130278</v>
+        <v>167022</v>
       </c>
     </row>
     <row r="55">
@@ -2275,23 +2275,23 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>26295</v>
+        <v>90393</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>16295</v>
+        <v>90393</v>
       </c>
     </row>
     <row r="56">
@@ -2343,11 +2343,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>44058</v>
+        <v>54456</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>44058</v>
+        <v>54456</v>
       </c>
     </row>
     <row r="58">
@@ -2445,11 +2445,11 @@
         <v>20000</v>
       </c>
       <c r="D60" t="n">
-        <v>20000</v>
+        <v>25398</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>127.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>20000</v>
+        <v>25398</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>24194</v>
+        <v>26970</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>24194</v>
+        <v>26970</v>
       </c>
     </row>
     <row r="62">
@@ -2513,23 +2513,23 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>44497</v>
+        <v>60675</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>15800</v>
+        <v>0</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>28697</v>
+        <v>60675</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>8278</v>
+        <v>9074</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>138.0%</t>
+          <t>151.2%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>8278</v>
+        <v>9074</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -477,19 +477,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>22866.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>130768.2</v>
+        <v>107901.53</v>
       </c>
     </row>
     <row r="3">
@@ -579,19 +579,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>14586.3</v>
+        <v>11986.3</v>
       </c>
     </row>
     <row r="6">
@@ -919,19 +919,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>24188</v>
+        <v>23790</v>
       </c>
     </row>
     <row r="16">
@@ -1055,19 +1055,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>50733.9</v>
+        <v>45733.9</v>
       </c>
     </row>
     <row r="20">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>74747.8</v>
+        <v>70747.8</v>
       </c>
     </row>
     <row r="21">
@@ -1259,19 +1259,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>77966</v>
+        <v>68166</v>
       </c>
     </row>
     <row r="26">
@@ -1361,19 +1361,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>19399.98</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>144.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>13394</v>
+        <v>-6005.98</v>
       </c>
     </row>
     <row r="29">
@@ -1395,19 +1395,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>80382</v>
+        <v>73382</v>
       </c>
     </row>
     <row r="30">
@@ -1531,19 +1531,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>33800</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>94375.64</v>
+        <v>60575.64</v>
       </c>
     </row>
     <row r="34">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>77529.84999999999</v>
+        <v>71529.84999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1599,19 +1599,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>45488.92</v>
+        <v>38888.92</v>
       </c>
     </row>
     <row r="36">
@@ -1769,19 +1769,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>380238</v>
+        <v>368238</v>
       </c>
     </row>
     <row r="41">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>103.6%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>116372</v>
+        <v>108772</v>
       </c>
     </row>
     <row r="43">
@@ -2279,19 +2279,19 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>90393</v>
+        <v>80393</v>
       </c>
     </row>
     <row r="56">
@@ -2313,19 +2313,19 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>30796</v>
+        <v>25796</v>
       </c>
     </row>
     <row r="57">
@@ -2415,19 +2415,19 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>115.3%</t>
+          <t>102.0%</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>69208</v>
+        <v>61208</v>
       </c>
     </row>
     <row r="60">
@@ -2517,19 +2517,19 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>15800</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>60675</v>
+        <v>44875</v>
       </c>
     </row>
     <row r="63">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,23 +473,23 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>130768.2</v>
+        <v>146448.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>22866.67</v>
+        <v>39866.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>107901.53</v>
+        <v>106581.53</v>
       </c>
     </row>
     <row r="3">
@@ -541,11 +541,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>48596</v>
+        <v>49902.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>48596</v>
+        <v>49902.6</v>
       </c>
     </row>
     <row r="5">
@@ -677,11 +677,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>26035.41</v>
+        <v>36035.41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>26035.41</v>
+        <v>36035.41</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>22476.03</v>
+        <v>32838.64</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>22276.03</v>
+        <v>32638.64</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>46266.7</v>
+        <v>54266.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>46266.7</v>
+        <v>54266.7</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>8600</v>
+        <v>11700</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8600</v>
+        <v>11700</v>
       </c>
     </row>
     <row r="12">
@@ -915,23 +915,23 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>24188</v>
+        <v>36188</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>398</v>
+        <v>9198</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>23790</v>
+        <v>26990</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>74190</v>
+        <v>74588</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>74190</v>
+        <v>74588</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>13788</v>
+        <v>18788</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>13788</v>
+        <v>18788</v>
       </c>
     </row>
     <row r="18">
@@ -1085,7 +1085,7 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>74747.8</v>
+        <v>74839.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1097,11 +1097,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>70747.8</v>
+        <v>70839.8</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>18318</v>
+        <v>8716</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>18318</v>
+        <v>8716</v>
       </c>
     </row>
     <row r="22">
@@ -1289,11 +1289,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>21154</v>
+        <v>31154</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>21154</v>
+        <v>31154</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>24058</v>
+        <v>24456</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>24058</v>
+        <v>24456</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>13394</v>
+        <v>14390</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>144.8%</t>
+          <t>134.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>-6005.98</v>
+        <v>-5009.98</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>80382</v>
+        <v>83580</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>73382</v>
+        <v>76580</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>60000</v>
       </c>
       <c r="D30" t="n">
-        <v>16176</v>
+        <v>26176</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>16176</v>
+        <v>26176</v>
       </c>
     </row>
     <row r="31">
@@ -1561,11 +1561,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>77529.84999999999</v>
+        <v>85529.84999999999</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1573,11 +1573,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>71529.84999999999</v>
+        <v>79529.84999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>45488.92</v>
+        <v>55488.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>38888.92</v>
+        <v>48888.92</v>
       </c>
     </row>
     <row r="36">
@@ -1629,23 +1629,23 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>10996</v>
+        <v>42192</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10996</v>
+        <v>41992</v>
       </c>
     </row>
     <row r="37">
@@ -1697,11 +1697,11 @@
         <v>30000</v>
       </c>
       <c r="D38" t="n">
-        <v>897</v>
+        <v>10897</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>897</v>
+        <v>10897</v>
       </c>
     </row>
     <row r="39">
@@ -1765,23 +1765,23 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>380238</v>
+        <v>425416</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>101.7%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>12000</v>
+        <v>18600</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>368238</v>
+        <v>406816</v>
       </c>
     </row>
     <row r="41">
@@ -1969,11 +1969,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>1980</v>
+        <v>5078</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1980</v>
+        <v>5078</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>139540</v>
+        <v>126544</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>139540</v>
+        <v>126544</v>
       </c>
     </row>
     <row r="48">
@@ -2173,11 +2173,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>196419</v>
+        <v>198311</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>196419</v>
+        <v>198311</v>
       </c>
     </row>
     <row r="53">
@@ -2241,11 +2241,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>167022</v>
+        <v>167420</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>167022</v>
+        <v>167420</v>
       </c>
     </row>
     <row r="55">
@@ -2309,11 +2309,11 @@
         <v>80000</v>
       </c>
       <c r="D56" t="n">
-        <v>30796</v>
+        <v>31194</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>25796</v>
+        <v>26194</v>
       </c>
     </row>
     <row r="57">
@@ -2377,11 +2377,11 @@
         <v>60000</v>
       </c>
       <c r="D58" t="n">
-        <v>10000</v>
+        <v>16660</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>10000</v>
+        <v>16660</v>
       </c>
     </row>
     <row r="59">
@@ -2479,11 +2479,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>26970</v>
+        <v>27368</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>26970</v>
+        <v>27368</v>
       </c>
     </row>
     <row r="62">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>146448.2</v>
+        <v>150258.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>106581.53</v>
+        <v>110392.13</v>
       </c>
     </row>
     <row r="3">
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>14586.3</v>
+        <v>14815.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>11986.3</v>
+        <v>12215.1</v>
       </c>
     </row>
     <row r="6">
@@ -677,11 +677,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>36035.41</v>
+        <v>26108.11</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>36035.41</v>
+        <v>26108.11</v>
       </c>
     </row>
     <row r="9">
@@ -881,11 +881,11 @@
         <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>85576</v>
+        <v>95974</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>85576</v>
+        <v>95974</v>
       </c>
     </row>
     <row r="15">
@@ -949,11 +949,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>74588</v>
+        <v>75982</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>74588</v>
+        <v>75982</v>
       </c>
     </row>
     <row r="17">
@@ -1017,11 +1017,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>2914.6</v>
+        <v>3710.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2914.6</v>
+        <v>3710.6</v>
       </c>
     </row>
     <row r="19">
@@ -1119,11 +1119,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>8716</v>
+        <v>9314</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>8716</v>
+        <v>9314</v>
       </c>
     </row>
     <row r="22">
@@ -1187,11 +1187,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>84982</v>
+        <v>85380</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>84982</v>
+        <v>85380</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>150000</v>
       </c>
       <c r="D24" t="n">
-        <v>2196</v>
+        <v>2794</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2196</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>77966</v>
+        <v>78564</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>68166</v>
+        <v>68764</v>
       </c>
     </row>
     <row r="26">
@@ -1289,11 +1289,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>31154</v>
+        <v>31552</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>31154</v>
+        <v>31552</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>24456</v>
+        <v>24956</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>24456</v>
+        <v>24956</v>
       </c>
     </row>
     <row r="28">
@@ -1391,11 +1391,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>83580</v>
+        <v>84178</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>76580</v>
+        <v>77178</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>60000</v>
       </c>
       <c r="D30" t="n">
-        <v>26176</v>
+        <v>38176</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>26176</v>
+        <v>38176</v>
       </c>
     </row>
     <row r="31">
@@ -1527,11 +1527,11 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>94375.64</v>
+        <v>94773.64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>60575.64</v>
+        <v>60973.64</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>85529.84999999999</v>
+        <v>86127.84999999999</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>79529.84999999999</v>
+        <v>80127.84999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>55488.92</v>
+        <v>56446.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>48888.92</v>
+        <v>49846.92</v>
       </c>
     </row>
     <row r="36">
@@ -1765,23 +1765,23 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>425416</v>
+        <v>440814</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>101.7%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>18600</v>
+        <v>59800</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>406816</v>
+        <v>381014</v>
       </c>
     </row>
     <row r="41">
@@ -1969,11 +1969,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>5078</v>
+        <v>15078</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5078</v>
+        <v>15078</v>
       </c>
     </row>
     <row r="47">
@@ -2173,11 +2173,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>198311</v>
+        <v>198850</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>198311</v>
+        <v>198850</v>
       </c>
     </row>
     <row r="53">
@@ -2207,7 +2207,7 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>57792.10000000001</v>
+        <v>57962.10000000001</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>57792.10000000001</v>
+        <v>57962.10000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2377,11 +2377,11 @@
         <v>60000</v>
       </c>
       <c r="D58" t="n">
-        <v>16660</v>
+        <v>22078</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>16660</v>
+        <v>22078</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>69208</v>
+        <v>99606</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>102.0%</t>
+          <t>152.7%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>61208</v>
+        <v>91606</v>
       </c>
     </row>
     <row r="60">
@@ -2547,11 +2547,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>9074</v>
+        <v>9472</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>151.2%</t>
+          <t>157.9%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>9074</v>
+        <v>9472</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>150258.8</v>
+        <v>209058.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>110392.13</v>
+        <v>169192.13</v>
       </c>
     </row>
     <row r="3">
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>14815.1</v>
+        <v>15015.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>12215.1</v>
+        <v>12415.1</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>48927.36</v>
+        <v>49685.36</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>48927.36</v>
+        <v>49685.36</v>
       </c>
     </row>
     <row r="7">
@@ -711,11 +711,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>32838.64</v>
+        <v>34038.64</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>32638.64</v>
+        <v>33838.64</v>
       </c>
     </row>
     <row r="10">
@@ -813,11 +813,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>57307.7</v>
+        <v>102907.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>57307.7</v>
+        <v>102907.7</v>
       </c>
     </row>
     <row r="13">
@@ -881,11 +881,11 @@
         <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>95974</v>
+        <v>96372</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>95974</v>
+        <v>96372</v>
       </c>
     </row>
     <row r="15">
@@ -953,19 +953,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>9200</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>75982</v>
+        <v>66782</v>
       </c>
     </row>
     <row r="17">
@@ -1017,11 +1017,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>3710.6</v>
+        <v>10310.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3710.6</v>
+        <v>10310.6</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>50733.9</v>
+        <v>70733.89999999999</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>45733.9</v>
+        <v>65733.89999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>74839.8</v>
+        <v>76035.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>70839.8</v>
+        <v>72035.8</v>
       </c>
     </row>
     <row r="21">
@@ -1187,11 +1187,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>85380</v>
+        <v>90778</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>85380</v>
+        <v>90778</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>150000</v>
       </c>
       <c r="D24" t="n">
-        <v>2794</v>
+        <v>3590</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2794</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>78564</v>
+        <v>81564</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>68764</v>
+        <v>71764</v>
       </c>
     </row>
     <row r="26">
@@ -1323,11 +1323,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>24956</v>
+        <v>35752</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>24956</v>
+        <v>35752</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>14390</v>
+        <v>14788</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>134.8%</t>
+          <t>131.2%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>-5009.98</v>
+        <v>-4611.98</v>
       </c>
     </row>
     <row r="29">
@@ -1561,23 +1561,23 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>86127.84999999999</v>
+        <v>91127.84999999999</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>6000</v>
+        <v>14500</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>80127.84999999999</v>
+        <v>76627.84999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1629,11 +1629,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>42192</v>
+        <v>42988</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>41992</v>
+        <v>42788</v>
       </c>
     </row>
     <row r="37">
@@ -1765,11 +1765,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>440814</v>
+        <v>461410</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>100.4%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>381014</v>
+        <v>401610</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>49191</v>
+        <v>69389</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>49191</v>
+        <v>69389</v>
       </c>
     </row>
     <row r="42">
@@ -1833,11 +1833,11 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>116372</v>
+        <v>117770</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>103.6%</t>
+          <t>104.9%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>108772</v>
+        <v>110170</v>
       </c>
     </row>
     <row r="43">
@@ -1935,11 +1935,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>42355.64000000001</v>
+        <v>43411.64000000001</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>42355.64000000001</v>
+        <v>43411.64000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>15078</v>
+        <v>25476</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>15078</v>
+        <v>25476</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>126544</v>
+        <v>130600</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>126544</v>
+        <v>130600</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>64521</v>
+        <v>66421</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>64521</v>
+        <v>66421</v>
       </c>
     </row>
     <row r="49">
@@ -2071,11 +2071,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>134512.5</v>
+        <v>142401.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>134512.5</v>
+        <v>142401.5</v>
       </c>
     </row>
     <row r="50">
@@ -2173,11 +2173,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>198850</v>
+        <v>216049</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>198850</v>
+        <v>216049</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>57962.10000000001</v>
+        <v>61756.10000000001</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>57962.10000000001</v>
+        <v>61756.10000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>167420</v>
+        <v>200551</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>83.6%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>167420</v>
+        <v>200551</v>
       </c>
     </row>
     <row r="55">
@@ -2381,19 +2381,19 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>22078</v>
+        <v>15078</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>99606</v>
+        <v>106206</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>152.7%</t>
+          <t>163.7%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>91606</v>
+        <v>98206</v>
       </c>
     </row>
     <row r="60">
@@ -2513,11 +2513,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>60675</v>
+        <v>61073</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>44875</v>
+        <v>45273</v>
       </c>
     </row>
     <row r="63">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>209058.8</v>
+        <v>214823.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>169192.13</v>
+        <v>174956.63</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>53603.2</v>
+        <v>53844.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>53603.2</v>
+        <v>53844.1</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>49902.6</v>
+        <v>60169.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>49902.6</v>
+        <v>60169.8</v>
       </c>
     </row>
     <row r="5">
@@ -609,11 +609,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>49685.36</v>
+        <v>50890.16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>49685.36</v>
+        <v>50890.16</v>
       </c>
     </row>
     <row r="7">
@@ -1561,11 +1561,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>91127.84999999999</v>
+        <v>91443.25</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>76627.84999999999</v>
+        <v>76943.25</v>
       </c>
     </row>
     <row r="35">
@@ -1935,11 +1935,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>43411.64000000001</v>
+        <v>75876.64000000001</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>43411.64000000001</v>
+        <v>75876.64000000001</v>
       </c>
     </row>
     <row r="46">
@@ -2037,11 +2037,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>66421</v>
+        <v>77268</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>66421</v>
+        <v>77268</v>
       </c>
     </row>
     <row r="49">
@@ -2071,11 +2071,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>142401.5</v>
+        <v>148555.04</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>142401.5</v>
+        <v>148555.04</v>
       </c>
     </row>
     <row r="50">
@@ -2173,11 +2173,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>216049</v>
+        <v>229564.64</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>216049</v>
+        <v>229564.64</v>
       </c>
     </row>
     <row r="53">
@@ -2241,11 +2241,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>200551</v>
+        <v>201951</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>200551</v>
+        <v>201951</v>
       </c>
     </row>
     <row r="55">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>214823.3</v>
+        <v>215574.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>174956.63</v>
+        <v>175708.03</v>
       </c>
     </row>
     <row r="3">
@@ -541,11 +541,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>60169.8</v>
+        <v>60567.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>60169.8</v>
+        <v>60567.8</v>
       </c>
     </row>
     <row r="5">
@@ -609,11 +609,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>50890.16</v>
+        <v>57490.16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>50890.16</v>
+        <v>57490.16</v>
       </c>
     </row>
     <row r="7">
@@ -677,11 +677,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>26108.11</v>
+        <v>26506.11</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>26108.11</v>
+        <v>26506.11</v>
       </c>
     </row>
     <row r="9">
@@ -745,11 +745,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>54266.7</v>
+        <v>62266.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>54266.7</v>
+        <v>62266.7</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>102907.7</v>
+        <v>110805.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>102907.7</v>
+        <v>110805.7</v>
       </c>
     </row>
     <row r="13">
@@ -915,11 +915,11 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>36188</v>
+        <v>48188</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>26990</v>
+        <v>38990</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>75982</v>
+        <v>76380</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>66782</v>
+        <v>67180</v>
       </c>
     </row>
     <row r="17">
@@ -1017,11 +1017,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>10310.6</v>
+        <v>35510.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>10310.6</v>
+        <v>35510.6</v>
       </c>
     </row>
     <row r="19">
@@ -1187,11 +1187,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>90778</v>
+        <v>114778</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>90778</v>
+        <v>114778</v>
       </c>
     </row>
     <row r="24">
@@ -1391,11 +1391,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>84178</v>
+        <v>85174</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>77178</v>
+        <v>78174</v>
       </c>
     </row>
     <row r="30">
@@ -1429,19 +1429,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>38176</v>
+        <v>28176</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>60000</v>
       </c>
       <c r="D31" t="n">
-        <v>12098</v>
+        <v>12496</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>12098</v>
+        <v>12496</v>
       </c>
     </row>
     <row r="32">
@@ -1527,11 +1527,11 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>94773.64</v>
+        <v>124069.64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>60973.64</v>
+        <v>90269.64</v>
       </c>
     </row>
     <row r="34">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>14500</v>
+        <v>39833.4</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>76943.25</v>
+        <v>51609.85</v>
       </c>
     </row>
     <row r="35">
@@ -1633,19 +1633,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>200</v>
+        <v>6200</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>42788</v>
+        <v>36788</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>40000</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>796</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>796</v>
       </c>
     </row>
     <row r="38">
@@ -1765,23 +1765,23 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>461410</v>
+        <v>483008</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>100.4%</t>
+          <t>104.2%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>59800</v>
+        <v>66300</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>401610</v>
+        <v>416708</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>69389</v>
+        <v>101189</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>69389</v>
+        <v>101189</v>
       </c>
     </row>
     <row r="42">
@@ -1833,11 +1833,11 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>117770</v>
+        <v>118566</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>104.9%</t>
+          <t>105.7%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>110170</v>
+        <v>110966</v>
       </c>
     </row>
     <row r="43">
@@ -2275,11 +2275,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>90393</v>
+        <v>96993</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2287,11 +2287,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>80393</v>
+        <v>86993</v>
       </c>
     </row>
     <row r="56">
@@ -2309,11 +2309,11 @@
         <v>80000</v>
       </c>
       <c r="D56" t="n">
-        <v>31194</v>
+        <v>41194</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>26194</v>
+        <v>36194</v>
       </c>
     </row>
     <row r="57">
@@ -2479,11 +2479,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>27368</v>
+        <v>37368</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>27368</v>
+        <v>37368</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>61073</v>
+        <v>51572</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>45273</v>
+        <v>35772</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>9472</v>
+        <v>9870</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>157.9%</t>
+          <t>164.5%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>9472</v>
+        <v>9870</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>215574.7</v>
+        <v>229174.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>175708.03</v>
+        <v>189307.93</v>
       </c>
     </row>
     <row r="3">
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>15015.1</v>
+        <v>42388.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>12415.1</v>
+        <v>39788.8</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>57490.16</v>
+        <v>69150.06</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>57490.16</v>
+        <v>69150.06</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>11194</v>
+        <v>12194</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>11194</v>
+        <v>12194</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>26506.11</v>
+        <v>27601.93</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>26506.11</v>
+        <v>27601.93</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>34038.64</v>
+        <v>35270.96</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>33838.64</v>
+        <v>35070.96</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>62266.7</v>
+        <v>83675.61</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>62266.7</v>
+        <v>83675.61</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>11700</v>
+        <v>12500</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>11700</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>110805.7</v>
+        <v>128205.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>110805.7</v>
+        <v>128205.7</v>
       </c>
     </row>
     <row r="13">
@@ -881,11 +881,11 @@
         <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>96372</v>
+        <v>96770</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>96372</v>
+        <v>96770</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>48188</v>
+        <v>51760</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>38990</v>
+        <v>42562</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>76380</v>
+        <v>96976</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>67180</v>
+        <v>87776</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>18788</v>
+        <v>19584</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>18788</v>
+        <v>19584</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>35510.6</v>
+        <v>38158</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>35510.6</v>
+        <v>38158</v>
       </c>
     </row>
     <row r="19">
@@ -1085,11 +1085,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>76035.8</v>
+        <v>77727.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>72035.8</v>
+        <v>73727.8</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>9314</v>
+        <v>10279.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9314</v>
+        <v>10279.8</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>60000</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>114778</v>
+        <v>163558</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>114778</v>
+        <v>163558</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>150000</v>
       </c>
       <c r="D24" t="n">
-        <v>3590</v>
+        <v>8590</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3590</v>
+        <v>8590</v>
       </c>
     </row>
     <row r="25">
@@ -1391,11 +1391,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>85174</v>
+        <v>97572</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>78174</v>
+        <v>90572</v>
       </c>
     </row>
     <row r="30">
@@ -1459,11 +1459,11 @@
         <v>60000</v>
       </c>
       <c r="D31" t="n">
-        <v>12496</v>
+        <v>22496</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>12496</v>
+        <v>22496</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>30000</v>
       </c>
       <c r="D32" t="n">
-        <v>10796</v>
+        <v>21792</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>10796</v>
+        <v>21792</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>124069.64</v>
+        <v>160069.64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>90269.64</v>
+        <v>126269.64</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>91443.25</v>
+        <v>142265.13</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1573,11 +1573,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>51609.85</v>
+        <v>102431.73</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>56446.92</v>
+        <v>67044.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>49846.92</v>
+        <v>60444.92</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>42988</v>
+        <v>49980</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>36788</v>
+        <v>43780</v>
       </c>
     </row>
     <row r="37">
@@ -1731,11 +1731,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>48472</v>
+        <v>68472</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>48472</v>
+        <v>68472</v>
       </c>
     </row>
     <row r="40">
@@ -1765,23 +1765,23 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>483008</v>
+        <v>496884</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>104.2%</t>
+          <t>106.4%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>66300</v>
+        <v>71300</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>416708</v>
+        <v>425584</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>101189</v>
+        <v>102869</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>101189</v>
+        <v>102869</v>
       </c>
     </row>
     <row r="42">
@@ -1867,23 +1867,23 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>35751</v>
+        <v>106151</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>35751</v>
+        <v>97151</v>
       </c>
     </row>
     <row r="44">
@@ -1935,11 +1935,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>75876.64000000001</v>
+        <v>98466.64000000001</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>75876.64000000001</v>
+        <v>98466.64000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>25476</v>
+        <v>31103</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>25476</v>
+        <v>31103</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>130600</v>
+        <v>157308</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>130600</v>
+        <v>157308</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>77268</v>
+        <v>108869</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>77268</v>
+        <v>108869</v>
       </c>
     </row>
     <row r="49">
@@ -2071,11 +2071,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>148555.04</v>
+        <v>219861.04</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>148555.04</v>
+        <v>219861.04</v>
       </c>
     </row>
     <row r="50">
@@ -2105,11 +2105,11 @@
         <v>80000</v>
       </c>
       <c r="D50" t="n">
-        <v>398</v>
+        <v>1996</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>398</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="51">
@@ -2173,11 +2173,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>229564.64</v>
+        <v>299056.64</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>229564.64</v>
+        <v>299056.64</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>61756.10000000001</v>
+        <v>141525.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>61756.10000000001</v>
+        <v>141525.1</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>201951</v>
+        <v>209949</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>201951</v>
+        <v>209949</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>96993</v>
+        <v>107789</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2287,11 +2287,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>86993</v>
+        <v>97789</v>
       </c>
     </row>
     <row r="56">
@@ -2343,11 +2343,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>54456</v>
+        <v>54854</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>54456</v>
+        <v>54854</v>
       </c>
     </row>
     <row r="58">
@@ -2411,11 +2411,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>106206</v>
+        <v>112806</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>163.7%</t>
+          <t>174.7%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>98206</v>
+        <v>104806</v>
       </c>
     </row>
     <row r="60">
@@ -2513,11 +2513,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>51572</v>
+        <v>52071</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>35772</v>
+        <v>36271</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>9870</v>
+        <v>19870</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>164.5%</t>
+          <t>331.2%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>9870</v>
+        <v>19870</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -507,11 +507,11 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>53844.1</v>
+        <v>59644.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>53844.1</v>
+        <v>59644.1</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>60567.8</v>
+        <v>53067.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>60567.8</v>
+        <v>53067.8</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>42388.8</v>
+        <v>43184.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>39788.8</v>
+        <v>40584.8</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>69150.06</v>
+        <v>74548.06</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>69150.06</v>
+        <v>74548.06</v>
       </c>
     </row>
     <row r="7">
@@ -677,11 +677,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>27601.93</v>
+        <v>28110.39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>27601.93</v>
+        <v>28110.39</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>35270.96</v>
+        <v>37343.66</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>35070.96</v>
+        <v>37143.66</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>83675.61</v>
+        <v>84275.32000000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>83675.61</v>
+        <v>84275.32000000001</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>12500</v>
+        <v>20000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>12500</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>128205.7</v>
+        <v>129805.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>128205.7</v>
+        <v>129805.7</v>
       </c>
     </row>
     <row r="13">
@@ -1017,11 +1017,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>38158</v>
+        <v>48556</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>38158</v>
+        <v>48556</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>70733.89999999999</v>
+        <v>112391.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>65733.89999999999</v>
+        <v>107391.9</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>77727.8</v>
+        <v>77568.60000000001</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>73727.8</v>
+        <v>73568.60000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>10279.8</v>
+        <v>2359.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10279.8</v>
+        <v>2359.8</v>
       </c>
     </row>
     <row r="22">
@@ -1187,11 +1187,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>163558</v>
+        <v>152164</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>163558</v>
+        <v>152164</v>
       </c>
     </row>
     <row r="24">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>81564</v>
+        <v>79584</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>71764</v>
+        <v>69784</v>
       </c>
     </row>
     <row r="26">
@@ -1323,11 +1323,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>35752</v>
+        <v>26150</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>35752</v>
+        <v>26150</v>
       </c>
     </row>
     <row r="28">
@@ -1391,11 +1391,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>97572</v>
+        <v>96170</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>90572</v>
+        <v>89170</v>
       </c>
     </row>
     <row r="30">
@@ -1459,11 +1459,11 @@
         <v>60000</v>
       </c>
       <c r="D31" t="n">
-        <v>22496</v>
+        <v>22098</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>22496</v>
+        <v>22098</v>
       </c>
     </row>
     <row r="32">
@@ -1527,11 +1527,11 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>160069.64</v>
+        <v>160269.64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>126269.64</v>
+        <v>126469.64</v>
       </c>
     </row>
     <row r="34">
@@ -1595,11 +1595,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>67044.92</v>
+        <v>79044.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>60444.92</v>
+        <v>72444.92</v>
       </c>
     </row>
     <row r="36">
@@ -1697,11 +1697,11 @@
         <v>30000</v>
       </c>
       <c r="D38" t="n">
-        <v>10897</v>
+        <v>21295</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>10897</v>
+        <v>21295</v>
       </c>
     </row>
     <row r="39">
@@ -1731,11 +1731,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>68472</v>
+        <v>75072</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>68472</v>
+        <v>75072</v>
       </c>
     </row>
     <row r="40">
@@ -1765,11 +1765,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>496884</v>
+        <v>467484</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>106.4%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>425584</v>
+        <v>396184</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>102869</v>
+        <v>100889</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>102869</v>
+        <v>100889</v>
       </c>
     </row>
     <row r="42">
@@ -1833,11 +1833,11 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>118566</v>
+        <v>128566</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>105.7%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>110966</v>
+        <v>120966</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>106151</v>
+        <v>104171</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1879,11 +1879,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>97151</v>
+        <v>95171</v>
       </c>
     </row>
     <row r="44">
@@ -1935,11 +1935,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>98466.64000000001</v>
+        <v>102303.64</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>98466.64000000001</v>
+        <v>102303.64</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>31103</v>
+        <v>31803</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>31103</v>
+        <v>31803</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>157308</v>
+        <v>174767</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>157308</v>
+        <v>174767</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>108869</v>
+        <v>114357</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>108869</v>
+        <v>114357</v>
       </c>
     </row>
     <row r="49">
@@ -2071,11 +2071,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>219861.04</v>
+        <v>231661.04</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>100.7%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>219861.04</v>
+        <v>231661.04</v>
       </c>
     </row>
     <row r="50">
@@ -2105,11 +2105,11 @@
         <v>80000</v>
       </c>
       <c r="D50" t="n">
-        <v>1996</v>
+        <v>1598</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1996</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="51">
@@ -2173,11 +2173,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>299056.64</v>
+        <v>319909.65</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>106.6%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>299056.64</v>
+        <v>319909.65</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>141525.1</v>
+        <v>144428.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>141525.1</v>
+        <v>144428.1</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>209949</v>
+        <v>232767</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>209949</v>
+        <v>232767</v>
       </c>
     </row>
     <row r="55">
@@ -2309,11 +2309,11 @@
         <v>80000</v>
       </c>
       <c r="D56" t="n">
-        <v>41194</v>
+        <v>10398</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>36194</v>
+        <v>5398</v>
       </c>
     </row>
     <row r="57">
@@ -2411,11 +2411,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>112806</v>
+        <v>122806</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>174.7%</t>
+          <t>191.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>104806</v>
+        <v>114806</v>
       </c>
     </row>
     <row r="60">
@@ -2513,11 +2513,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>52071</v>
+        <v>52570</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>36271</v>
+        <v>36770</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>19870</v>
+        <v>18590</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>331.2%</t>
+          <t>309.8%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>19870</v>
+        <v>18590</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>229174.6</v>
+        <v>229374.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>189307.93</v>
+        <v>189507.93</v>
       </c>
     </row>
     <row r="3">
@@ -541,11 +541,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>53067.8</v>
+        <v>60567.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>53067.8</v>
+        <v>60567.8</v>
       </c>
     </row>
     <row r="5">
@@ -711,11 +711,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>37343.66</v>
+        <v>45343.66</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>37143.66</v>
+        <v>45143.66</v>
       </c>
     </row>
     <row r="10">
@@ -1085,11 +1085,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>77568.60000000001</v>
+        <v>78166.60000000001</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>73568.60000000001</v>
+        <v>74166.60000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>2359.8</v>
+        <v>10279.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2359.8</v>
+        <v>10279.8</v>
       </c>
     </row>
     <row r="22">
@@ -1187,11 +1187,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>152164</v>
+        <v>173558</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>152164</v>
+        <v>173558</v>
       </c>
     </row>
     <row r="24">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>79584</v>
+        <v>81564</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>69784</v>
+        <v>71764</v>
       </c>
     </row>
     <row r="26">
@@ -1323,11 +1323,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>26150</v>
+        <v>36150</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>26150</v>
+        <v>36150</v>
       </c>
     </row>
     <row r="28">
@@ -1391,11 +1391,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>96170</v>
+        <v>97970</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>89170</v>
+        <v>90970</v>
       </c>
     </row>
     <row r="30">
@@ -1459,11 +1459,11 @@
         <v>60000</v>
       </c>
       <c r="D31" t="n">
-        <v>22098</v>
+        <v>22496</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>22098</v>
+        <v>22496</v>
       </c>
     </row>
     <row r="32">
@@ -1527,11 +1527,11 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>160269.64</v>
+        <v>160667.64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>126469.64</v>
+        <v>126867.64</v>
       </c>
     </row>
     <row r="34">
@@ -1765,11 +1765,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>467484</v>
+        <v>513482</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>110.5%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>396184</v>
+        <v>442182</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>100889</v>
+        <v>102869</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>100889</v>
+        <v>102869</v>
       </c>
     </row>
     <row r="42">
@@ -1867,11 +1867,11 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>104171</v>
+        <v>106151</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1879,11 +1879,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>95171</v>
+        <v>97151</v>
       </c>
     </row>
     <row r="44">
@@ -1969,11 +1969,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>31803</v>
+        <v>33783</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>31803</v>
+        <v>33783</v>
       </c>
     </row>
     <row r="47">
@@ -2105,11 +2105,11 @@
         <v>80000</v>
       </c>
       <c r="D50" t="n">
-        <v>1598</v>
+        <v>1996</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1598</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="51">
@@ -2241,11 +2241,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>232767</v>
+        <v>234747</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>232767</v>
+        <v>234747</v>
       </c>
     </row>
     <row r="55">
@@ -2309,11 +2309,11 @@
         <v>80000</v>
       </c>
       <c r="D56" t="n">
-        <v>10398</v>
+        <v>41194</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>5398</v>
+        <v>36194</v>
       </c>
     </row>
     <row r="57">
@@ -2547,11 +2547,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>18590</v>
+        <v>19870</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>309.8%</t>
+          <t>331.2%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>18590</v>
+        <v>19870</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>81564</v>
+        <v>74964</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>71764</v>
+        <v>65164</v>
       </c>
     </row>
     <row r="26">
@@ -2513,11 +2513,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>52570</v>
+        <v>62570</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>36770</v>
+        <v>46770</v>
       </c>
     </row>
     <row r="63">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>74964</v>
+        <v>81564</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>65164</v>
+        <v>71764</v>
       </c>
     </row>
     <row r="26">
@@ -2513,11 +2513,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>62570</v>
+        <v>52570</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>46770</v>
+        <v>36770</v>
       </c>
     </row>
     <row r="63">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>229374.6</v>
+        <v>230370.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>189507.93</v>
+        <v>190503.93</v>
       </c>
     </row>
     <row r="3">
@@ -643,11 +643,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>12194</v>
+        <v>18794</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>12194</v>
+        <v>18794</v>
       </c>
     </row>
     <row r="8">
@@ -745,11 +745,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>84275.32000000001</v>
+        <v>87740.48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>84275.32000000001</v>
+        <v>87740.48</v>
       </c>
     </row>
     <row r="11">
@@ -915,11 +915,11 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>51760</v>
+        <v>60158</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>42562</v>
+        <v>50960</v>
       </c>
     </row>
     <row r="16">
@@ -1051,11 +1051,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>112391.9</v>
+        <v>122391.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>107391.9</v>
+        <v>117391.9</v>
       </c>
     </row>
     <row r="20">
@@ -1119,11 +1119,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>10279.8</v>
+        <v>10677.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10279.8</v>
+        <v>10677.8</v>
       </c>
     </row>
     <row r="22">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>81564</v>
+        <v>75562</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>71764</v>
+        <v>65762</v>
       </c>
     </row>
     <row r="26">
@@ -1323,11 +1323,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>36150</v>
+        <v>36548</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>36150</v>
+        <v>36548</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>14788</v>
+        <v>15186</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>131.2%</t>
+          <t>127.7%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>-4611.98</v>
+        <v>-4213.98</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>97970</v>
+        <v>110368</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>90970</v>
+        <v>103368</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>60000</v>
       </c>
       <c r="D30" t="n">
-        <v>38176</v>
+        <v>48176</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>28176</v>
+        <v>38176</v>
       </c>
     </row>
     <row r="31">
@@ -1561,11 +1561,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>142265.13</v>
+        <v>164265.13</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1573,11 +1573,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>102431.73</v>
+        <v>124431.73</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>79044.92</v>
+        <v>91044.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>72444.92</v>
+        <v>84444.92</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>49980</v>
+        <v>62778</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>43780</v>
+        <v>56578</v>
       </c>
     </row>
     <row r="37">
@@ -1765,11 +1765,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>513482</v>
+        <v>503080</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>110.5%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>442182</v>
+        <v>431780</v>
       </c>
     </row>
     <row r="41">
@@ -1833,11 +1833,11 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>128566</v>
+        <v>135166</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>121.5%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>120966</v>
+        <v>127566</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>106151</v>
+        <v>106549</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1879,11 +1879,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>97151</v>
+        <v>97549</v>
       </c>
     </row>
     <row r="44">
@@ -1905,19 +1905,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>102303.64</v>
+        <v>144607.64</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>102303.64</v>
+        <v>144607.64</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>33783</v>
+        <v>43783</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>33783</v>
+        <v>43783</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>174767</v>
+        <v>187909</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>174767</v>
+        <v>187909</v>
       </c>
     </row>
     <row r="48">
@@ -2071,11 +2071,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>231661.04</v>
+        <v>241661.04</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>100.7%</t>
+          <t>105.1%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>231661.04</v>
+        <v>241661.04</v>
       </c>
     </row>
     <row r="50">
@@ -2105,11 +2105,11 @@
         <v>80000</v>
       </c>
       <c r="D50" t="n">
-        <v>1996</v>
+        <v>4469</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1996</v>
+        <v>4469</v>
       </c>
     </row>
     <row r="51">
@@ -2173,11 +2173,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>319909.65</v>
+        <v>320773.65</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>106.6%</t>
+          <t>106.9%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>319909.65</v>
+        <v>320773.65</v>
       </c>
     </row>
     <row r="53">
@@ -2241,11 +2241,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>234747</v>
+        <v>235826</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>234747</v>
+        <v>235826</v>
       </c>
     </row>
     <row r="55">
@@ -2479,11 +2479,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>37368</v>
+        <v>37766</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>37368</v>
+        <v>37766</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>52570</v>
+        <v>62570</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>36770</v>
+        <v>46770</v>
       </c>
     </row>
     <row r="63">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>230370.6</v>
+        <v>258166.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>190503.93</v>
+        <v>218299.93</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>59644.1</v>
+        <v>67944.10000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>59644.1</v>
+        <v>67944.10000000001</v>
       </c>
     </row>
     <row r="4">
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>43184.8</v>
+        <v>43782.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>40584.8</v>
+        <v>41182.8</v>
       </c>
     </row>
     <row r="6">
@@ -643,11 +643,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>18794</v>
+        <v>19192</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>18794</v>
+        <v>19192</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>28110.39</v>
+        <v>29790.39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>28110.39</v>
+        <v>29790.39</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>45343.66</v>
+        <v>65864.13</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>45143.66</v>
+        <v>65664.13</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>87740.48</v>
+        <v>120740.48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>120.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>87740.48</v>
+        <v>120740.48</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>129805.7</v>
+        <v>137305.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>129805.7</v>
+        <v>137305.7</v>
       </c>
     </row>
     <row r="13">
@@ -881,11 +881,11 @@
         <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>96770</v>
+        <v>106770</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>96770</v>
+        <v>106770</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>60158</v>
+        <v>65954</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>50960</v>
+        <v>56756</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>96976</v>
+        <v>98956</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>87776</v>
+        <v>89756</v>
       </c>
     </row>
     <row r="17">
@@ -1051,11 +1051,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>122391.9</v>
+        <v>125115.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>117391.9</v>
+        <v>120115.5</v>
       </c>
     </row>
     <row r="20">
@@ -1289,11 +1289,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>31552</v>
+        <v>51552</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>31552</v>
+        <v>51552</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>36548</v>
+        <v>39428</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>36548</v>
+        <v>39428</v>
       </c>
     </row>
     <row r="28">
@@ -1391,11 +1391,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>110368</v>
+        <v>112168</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>103368</v>
+        <v>105168</v>
       </c>
     </row>
     <row r="30">
@@ -1459,11 +1459,11 @@
         <v>60000</v>
       </c>
       <c r="D31" t="n">
-        <v>22496</v>
+        <v>22894</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>22496</v>
+        <v>22894</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>30000</v>
       </c>
       <c r="D32" t="n">
-        <v>21792</v>
+        <v>28392</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>21792</v>
+        <v>28392</v>
       </c>
     </row>
     <row r="33">
@@ -1629,11 +1629,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>62778</v>
+        <v>82778</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>76.6%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>56578</v>
+        <v>76578</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>40000</v>
       </c>
       <c r="D37" t="n">
-        <v>796</v>
+        <v>11592</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>796</v>
+        <v>11592</v>
       </c>
     </row>
     <row r="38">
@@ -1731,11 +1731,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>75072</v>
+        <v>85470</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>75072</v>
+        <v>85470</v>
       </c>
     </row>
     <row r="40">
@@ -1765,11 +1765,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>503080</v>
+        <v>548680</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>119.3%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>431780</v>
+        <v>477380</v>
       </c>
     </row>
     <row r="41">
@@ -1969,11 +1969,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>43783</v>
+        <v>44181</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>43783</v>
+        <v>44181</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>187909</v>
+        <v>187307</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>187909</v>
+        <v>187307</v>
       </c>
     </row>
     <row r="48">
@@ -2343,11 +2343,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>54854</v>
+        <v>55252</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>54854</v>
+        <v>55252</v>
       </c>
     </row>
     <row r="58">
@@ -2547,11 +2547,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>19870</v>
+        <v>20268</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>331.2%</t>
+          <t>337.8%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>19870</v>
+        <v>20268</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>258166.6</v>
+        <v>270650</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>100.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>218299.93</v>
+        <v>230783.33</v>
       </c>
     </row>
     <row r="3">
@@ -541,11 +541,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>60567.8</v>
+        <v>75267.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>60567.8</v>
+        <v>75267.8</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>43782.8</v>
+        <v>47480.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>41182.8</v>
+        <v>44880.8</v>
       </c>
     </row>
     <row r="6">
@@ -643,11 +643,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>19192</v>
+        <v>19590</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19192</v>
+        <v>19590</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>29790.39</v>
+        <v>30586.39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>29790.39</v>
+        <v>30586.39</v>
       </c>
     </row>
     <row r="9">
@@ -745,11 +745,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>120740.48</v>
+        <v>144740.48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>120.7%</t>
+          <t>144.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>120740.48</v>
+        <v>144740.48</v>
       </c>
     </row>
     <row r="11">
@@ -885,19 +885,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>106770</v>
+        <v>96770</v>
       </c>
     </row>
     <row r="15">
@@ -915,7 +915,7 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>65954</v>
+        <v>85954</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -923,11 +923,11 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>9198</v>
+        <v>29198</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1017,11 +1017,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>48556</v>
+        <v>48954</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>48556</v>
+        <v>48954</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>125115.5</v>
+        <v>125713.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>120115.5</v>
+        <v>120713.5</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>78166.60000000001</v>
+        <v>78896.89999999999</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>74166.60000000001</v>
+        <v>74896.89999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>10677.8</v>
+        <v>11276.55</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10677.8</v>
+        <v>11276.55</v>
       </c>
     </row>
     <row r="22">
@@ -1187,11 +1187,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>173558</v>
+        <v>173956</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>173558</v>
+        <v>173956</v>
       </c>
     </row>
     <row r="24">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>75562</v>
+        <v>77242</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>65762</v>
+        <v>67442</v>
       </c>
     </row>
     <row r="26">
@@ -1323,11 +1323,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>39428</v>
+        <v>44428</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>39428</v>
+        <v>44428</v>
       </c>
     </row>
     <row r="28">
@@ -1561,11 +1561,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>164265.13</v>
+        <v>164863.13</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>124431.73</v>
+        <v>125029.73</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>91044.92</v>
+        <v>91642.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>84444.92</v>
+        <v>85042.92</v>
       </c>
     </row>
     <row r="36">
@@ -1633,19 +1633,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>6200</v>
+        <v>6598</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>76578</v>
+        <v>76180</v>
       </c>
     </row>
     <row r="37">
@@ -1765,23 +1765,23 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>548680</v>
+        <v>565476</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>119.3%</t>
+          <t>121.7%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>71300</v>
+        <v>78650</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>477380</v>
+        <v>486826</v>
       </c>
     </row>
     <row r="41">
@@ -1935,11 +1935,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>144607.64</v>
+        <v>149519.64</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>144607.64</v>
+        <v>149519.64</v>
       </c>
     </row>
     <row r="46">
@@ -2003,11 +2003,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>187307</v>
+        <v>188544</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>187307</v>
+        <v>188544</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>114357</v>
+        <v>118397</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>114357</v>
+        <v>118397</v>
       </c>
     </row>
     <row r="49">
@@ -2173,11 +2173,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>320773.65</v>
+        <v>337792.15</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>112.6%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>320773.65</v>
+        <v>337792.15</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>144428.1</v>
+        <v>149610.3</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>144428.1</v>
+        <v>149610.3</v>
       </c>
     </row>
     <row r="54">
@@ -2275,11 +2275,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>107789</v>
+        <v>117789</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2287,11 +2287,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>97789</v>
+        <v>107789</v>
       </c>
     </row>
     <row r="56">
@@ -2445,11 +2445,11 @@
         <v>20000</v>
       </c>
       <c r="D60" t="n">
-        <v>25398</v>
+        <v>25796</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>127.0%</t>
+          <t>129.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>25398</v>
+        <v>25796</v>
       </c>
     </row>
     <row r="61">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -507,23 +507,23 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>67944.10000000001</v>
+        <v>71044.10000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>67944.10000000001</v>
+        <v>65544.10000000001</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>75267.8</v>
+        <v>78800.67999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>75267.8</v>
+        <v>78800.67999999999</v>
       </c>
     </row>
     <row r="5">
@@ -643,11 +643,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>19590</v>
+        <v>19988</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19590</v>
+        <v>19988</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>30586.39</v>
+        <v>45937.21</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>30586.39</v>
+        <v>45937.21</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>65864.13</v>
+        <v>66076.69</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>65664.13</v>
+        <v>65876.69</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>144740.48</v>
+        <v>161172.17</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>144.7%</t>
+          <t>161.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>144740.48</v>
+        <v>161172.17</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>137305.7</v>
+        <v>171205.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>137305.7</v>
+        <v>171205.7</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>100000</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>15599.23</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>15599.23</v>
       </c>
     </row>
     <row r="14">
@@ -885,19 +885,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>10000</v>
+        <v>21500</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>96770</v>
+        <v>85270</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>85954</v>
+        <v>93954</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>56756</v>
+        <v>64756</v>
       </c>
     </row>
     <row r="16">
@@ -953,19 +953,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9200</v>
+        <v>18200</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>89756</v>
+        <v>80756</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>19584</v>
+        <v>20780</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>19584</v>
+        <v>20780</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>48954</v>
+        <v>78954</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>48954</v>
+        <v>78954</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>125713.5</v>
+        <v>126350.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>120713.5</v>
+        <v>121350.1</v>
       </c>
     </row>
     <row r="20">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>77242</v>
+        <v>77640</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>67442</v>
+        <v>67840</v>
       </c>
     </row>
     <row r="26">
@@ -1323,11 +1323,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>44428</v>
+        <v>55204</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>110.4%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>44428</v>
+        <v>55204</v>
       </c>
     </row>
     <row r="28">
@@ -1391,11 +1391,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>112168</v>
+        <v>128968</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>105168</v>
+        <v>121968</v>
       </c>
     </row>
     <row r="30">
@@ -1561,11 +1561,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>164863.13</v>
+        <v>165461.13</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1573,11 +1573,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>125029.73</v>
+        <v>125627.73</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>91642.92</v>
+        <v>104240.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>85042.92</v>
+        <v>97640.92</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>82778</v>
+        <v>105378</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>76180</v>
+        <v>98780</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>40000</v>
       </c>
       <c r="D37" t="n">
-        <v>11592</v>
+        <v>12190</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>11592</v>
+        <v>12190</v>
       </c>
     </row>
     <row r="38">
@@ -1697,11 +1697,11 @@
         <v>30000</v>
       </c>
       <c r="D38" t="n">
-        <v>21295</v>
+        <v>31295</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>104.3%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>21295</v>
+        <v>31295</v>
       </c>
     </row>
     <row r="39">
@@ -1731,11 +1731,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>85470</v>
+        <v>85770</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>85470</v>
+        <v>85770</v>
       </c>
     </row>
     <row r="40">
@@ -1765,11 +1765,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>565476</v>
+        <v>590852</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>121.7%</t>
+          <t>128.1%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>486826</v>
+        <v>512202</v>
       </c>
     </row>
     <row r="41">
@@ -1867,23 +1867,23 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>106549</v>
+        <v>126947</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>103.8%</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>9000</v>
+        <v>18000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>97549</v>
+        <v>108947</v>
       </c>
     </row>
     <row r="44">
@@ -1935,11 +1935,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>149519.64</v>
+        <v>199049.64</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>149519.64</v>
+        <v>199049.64</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>44181</v>
+        <v>44977</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>44181</v>
+        <v>44977</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>188544</v>
+        <v>222393</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>188544</v>
+        <v>222393</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>118397</v>
+        <v>145798.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>118397</v>
+        <v>145798.4</v>
       </c>
     </row>
     <row r="49">
@@ -2071,11 +2071,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>241661.04</v>
+        <v>274837.04</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>105.1%</t>
+          <t>119.5%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>241661.04</v>
+        <v>274837.04</v>
       </c>
     </row>
     <row r="50">
@@ -2105,11 +2105,11 @@
         <v>80000</v>
       </c>
       <c r="D50" t="n">
-        <v>4469</v>
+        <v>8399</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>4469</v>
+        <v>8399</v>
       </c>
     </row>
     <row r="51">
@@ -2173,11 +2173,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>337792.15</v>
+        <v>363630.97</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>112.6%</t>
+          <t>121.2%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>337792.15</v>
+        <v>363630.97</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>149610.3</v>
+        <v>208911.3</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>149610.3</v>
+        <v>208911.3</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>235826</v>
+        <v>266418</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>235826</v>
+        <v>266418</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>117789</v>
+        <v>139381</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>129.4%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2287,11 +2287,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>107789</v>
+        <v>129381</v>
       </c>
     </row>
     <row r="56">
@@ -2309,11 +2309,11 @@
         <v>80000</v>
       </c>
       <c r="D56" t="n">
-        <v>41194</v>
+        <v>41990</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>36194</v>
+        <v>36990</v>
       </c>
     </row>
     <row r="57">
@@ -2377,11 +2377,11 @@
         <v>60000</v>
       </c>
       <c r="D58" t="n">
-        <v>22078</v>
+        <v>22476</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>15078</v>
+        <v>15476</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>122806</v>
+        <v>124000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>191.3%</t>
+          <t>193.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>114806</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="60">
@@ -2479,11 +2479,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>37766</v>
+        <v>57566</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>37766</v>
+        <v>57566</v>
       </c>
     </row>
     <row r="62">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>270650</v>
+        <v>288048</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>100.3%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>230783.33</v>
+        <v>248181.33</v>
       </c>
     </row>
     <row r="3">
@@ -541,11 +541,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>78800.67999999999</v>
+        <v>79998.67999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>78800.67999999999</v>
+        <v>79998.67999999999</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>47480.8</v>
+        <v>59480.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>44880.8</v>
+        <v>56880.8</v>
       </c>
     </row>
     <row r="6">
@@ -677,11 +677,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>45937.21</v>
+        <v>46137.21</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>45937.21</v>
+        <v>46137.21</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>66076.69</v>
+        <v>66601.50999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>65876.69</v>
+        <v>66401.50999999999</v>
       </c>
     </row>
     <row r="10">
@@ -847,11 +847,11 @@
         <v>100000</v>
       </c>
       <c r="D13" t="n">
-        <v>15599.23</v>
+        <v>31399.23</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>15599.23</v>
+        <v>31399.23</v>
       </c>
     </row>
     <row r="14">
@@ -915,11 +915,11 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>93954</v>
+        <v>96232</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>64756</v>
+        <v>67034</v>
       </c>
     </row>
     <row r="16">
@@ -983,11 +983,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>20780</v>
+        <v>21178</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>20780</v>
+        <v>21178</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>78954</v>
+        <v>79397</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>78954</v>
+        <v>79397</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>126350.1</v>
+        <v>129937.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>121350.1</v>
+        <v>124937.4</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>78896.89999999999</v>
+        <v>81188.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>74896.89999999999</v>
+        <v>77188.7</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>11276.55</v>
+        <v>21276.55</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>11276.55</v>
+        <v>21276.55</v>
       </c>
     </row>
     <row r="22">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>77640</v>
+        <v>107640</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>67840</v>
+        <v>97840</v>
       </c>
     </row>
     <row r="26">
@@ -1323,11 +1323,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>55204</v>
+        <v>62202</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>110.4%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>55204</v>
+        <v>62202</v>
       </c>
     </row>
     <row r="28">
@@ -1425,11 +1425,11 @@
         <v>60000</v>
       </c>
       <c r="D30" t="n">
-        <v>48176</v>
+        <v>48376</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>38176</v>
+        <v>38376</v>
       </c>
     </row>
     <row r="31">
@@ -1731,11 +1731,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>85770</v>
+        <v>87750</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>85770</v>
+        <v>87750</v>
       </c>
     </row>
     <row r="40">
@@ -1765,11 +1765,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>590852</v>
+        <v>608834</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>128.1%</t>
+          <t>132.5%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>512202</v>
+        <v>530184</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>102869</v>
+        <v>103869</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>102869</v>
+        <v>103869</v>
       </c>
     </row>
     <row r="42">
@@ -1935,11 +1935,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>199049.64</v>
+        <v>223590.46</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>199049.64</v>
+        <v>223590.46</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>44977</v>
+        <v>56723</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>44977</v>
+        <v>56723</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>222393</v>
+        <v>226954</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>222393</v>
+        <v>226954</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>145798.4</v>
+        <v>152490.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>145798.4</v>
+        <v>152490.4</v>
       </c>
     </row>
     <row r="49">
@@ -2071,11 +2071,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>274837.04</v>
+        <v>286122.04</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>119.5%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>274837.04</v>
+        <v>286122.04</v>
       </c>
     </row>
     <row r="50">
@@ -2139,11 +2139,11 @@
         <v>80000</v>
       </c>
       <c r="D51" t="n">
-        <v>15940</v>
+        <v>16338</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>15940</v>
+        <v>16338</v>
       </c>
     </row>
     <row r="52">
@@ -2173,11 +2173,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>363630.97</v>
+        <v>384244.97</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>121.2%</t>
+          <t>128.1%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>363630.97</v>
+        <v>384244.97</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>208911.3</v>
+        <v>227243.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>103.3%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>208911.3</v>
+        <v>227243.8</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>266418</v>
+        <v>287418</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>119.8%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>266418</v>
+        <v>287418</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>139381</v>
+        <v>139779</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>129.4%</t>
+          <t>129.8%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>129381</v>
+        <v>129779</v>
       </c>
     </row>
     <row r="56">
@@ -2377,11 +2377,11 @@
         <v>60000</v>
       </c>
       <c r="D58" t="n">
-        <v>22476</v>
+        <v>33272</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>15476</v>
+        <v>26272</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>124000</v>
+        <v>134000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>193.3%</t>
+          <t>210.0%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>116000</v>
+        <v>126000</v>
       </c>
     </row>
     <row r="60">
@@ -2479,11 +2479,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>57566</v>
+        <v>57964</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>57566</v>
+        <v>57964</v>
       </c>
     </row>
     <row r="62">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,23 +473,23 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>288048</v>
+        <v>298048</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>104.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>39866.67</v>
+        <v>57366.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>248181.33</v>
+        <v>240681.33</v>
       </c>
     </row>
     <row r="3">
@@ -541,11 +541,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>79998.67999999999</v>
+        <v>90598.67999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>79998.67999999999</v>
+        <v>90598.67999999999</v>
       </c>
     </row>
     <row r="5">
@@ -677,11 +677,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>46137.21</v>
+        <v>62137.21</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>46137.21</v>
+        <v>62137.21</v>
       </c>
     </row>
     <row r="9">
@@ -745,7 +745,7 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>161172.17</v>
+        <v>161239.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>161172.17</v>
+        <v>161239.7</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>20000</v>
+        <v>27500</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>20000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="12">
@@ -813,23 +813,23 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>171205.7</v>
+        <v>171278.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>56600</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>171205.7</v>
+        <v>114678.4</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>100000</v>
       </c>
       <c r="D13" t="n">
-        <v>31399.23</v>
+        <v>38899.23</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>31399.23</v>
+        <v>38899.23</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>106770</v>
+        <v>118770</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -893,11 +893,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>85270</v>
+        <v>97270</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>96232</v>
+        <v>106630</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>67034</v>
+        <v>77432</v>
       </c>
     </row>
     <row r="16">
@@ -983,11 +983,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>21178</v>
+        <v>29576</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>21178</v>
+        <v>29576</v>
       </c>
     </row>
     <row r="18">
@@ -1119,11 +1119,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>21276.55</v>
+        <v>31674.55</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>21276.55</v>
+        <v>31674.55</v>
       </c>
     </row>
     <row r="22">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>107640</v>
+        <v>124440</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>97840</v>
+        <v>114640</v>
       </c>
     </row>
     <row r="26">
@@ -1323,11 +1323,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>62202</v>
+        <v>63822</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>127.6%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>62202</v>
+        <v>63822</v>
       </c>
     </row>
     <row r="28">
@@ -1561,7 +1561,7 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>165461.13</v>
+        <v>165530.37</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>125627.73</v>
+        <v>125696.97</v>
       </c>
     </row>
     <row r="35">
@@ -1629,11 +1629,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>105378</v>
+        <v>142174</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>135.6%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>98780</v>
+        <v>135576</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>40000</v>
       </c>
       <c r="D37" t="n">
-        <v>12190</v>
+        <v>14288</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>12190</v>
+        <v>14288</v>
       </c>
     </row>
     <row r="38">
@@ -1735,19 +1735,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>87750</v>
+        <v>81150</v>
       </c>
     </row>
     <row r="40">
@@ -1765,23 +1765,23 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>608834</v>
+        <v>622406</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>132.5%</t>
+          <t>134.9%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>78650</v>
+        <v>82650</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>530184</v>
+        <v>539756</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>103869</v>
+        <v>104869</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>103869</v>
+        <v>104869</v>
       </c>
     </row>
     <row r="42">
@@ -1871,19 +1871,19 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>103.8%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>18000</v>
+        <v>32222.24</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>108947</v>
+        <v>94724.76000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1935,11 +1935,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>223590.46</v>
+        <v>233590.46</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>223590.46</v>
+        <v>233590.46</v>
       </c>
     </row>
     <row r="46">
@@ -2003,11 +2003,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>226954</v>
+        <v>228917</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>226954</v>
+        <v>228917</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>152490.4</v>
+        <v>162490.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>152490.4</v>
+        <v>162490.4</v>
       </c>
     </row>
     <row r="49">
@@ -2173,11 +2173,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>384244.97</v>
+        <v>386638.97</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>128.1%</t>
+          <t>128.9%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>384244.97</v>
+        <v>386638.97</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>227243.8</v>
+        <v>237335.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>103.3%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>227243.8</v>
+        <v>237335.8</v>
       </c>
     </row>
     <row r="54">
@@ -2275,11 +2275,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>139779</v>
+        <v>140177</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>129.8%</t>
+          <t>130.2%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2287,11 +2287,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>129779</v>
+        <v>130177</v>
       </c>
     </row>
     <row r="56">
@@ -2309,11 +2309,11 @@
         <v>80000</v>
       </c>
       <c r="D56" t="n">
-        <v>41990</v>
+        <v>42388</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>36990</v>
+        <v>37388</v>
       </c>
     </row>
     <row r="57">
@@ -2411,11 +2411,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>134000</v>
+        <v>134398</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>210.0%</t>
+          <t>210.7%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>126000</v>
+        <v>126398</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>20000</v>
       </c>
       <c r="D60" t="n">
-        <v>25796</v>
+        <v>46592</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>129.0%</t>
+          <t>233.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>25796</v>
+        <v>46592</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>57964</v>
+        <v>62944</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>57964</v>
+        <v>62944</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>62570</v>
+        <v>63570</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>46770</v>
+        <v>47770</v>
       </c>
     </row>
     <row r="63">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>298048</v>
+        <v>314242</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>104.6%</t>
+          <t>111.7%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>240681.33</v>
+        <v>256875.33</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>71044.10000000001</v>
+        <v>88544.10000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65544.10000000001</v>
+        <v>83044.10000000001</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>90598.67999999999</v>
+        <v>98098.67999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>90598.67999999999</v>
+        <v>98098.67999999999</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>59480.8</v>
+        <v>59878.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>56880.8</v>
+        <v>57278.8</v>
       </c>
     </row>
     <row r="6">
@@ -643,11 +643,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>19988</v>
+        <v>29988</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19988</v>
+        <v>29988</v>
       </c>
     </row>
     <row r="8">
@@ -711,7 +711,7 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>66601.50999999999</v>
+        <v>66636.22</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>66401.50999999999</v>
+        <v>66436.22</v>
       </c>
     </row>
     <row r="10">
@@ -813,11 +813,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>171278.4</v>
+        <v>178778.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>114678.4</v>
+        <v>122178.4</v>
       </c>
     </row>
     <row r="13">
@@ -949,11 +949,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>98956</v>
+        <v>93976</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>80756</v>
+        <v>75776</v>
       </c>
     </row>
     <row r="17">
@@ -1017,11 +1017,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>79397</v>
+        <v>80750.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>79397</v>
+        <v>80750.8</v>
       </c>
     </row>
     <row r="19">
@@ -1119,11 +1119,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>31674.55</v>
+        <v>32072.55</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>31674.55</v>
+        <v>32072.55</v>
       </c>
     </row>
     <row r="22">
@@ -1187,11 +1187,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>173956</v>
+        <v>186554</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>173956</v>
+        <v>186554</v>
       </c>
     </row>
     <row r="24">
@@ -1323,11 +1323,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>63822</v>
+        <v>80622</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>127.6%</t>
+          <t>161.2%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>63822</v>
+        <v>80622</v>
       </c>
     </row>
     <row r="28">
@@ -1391,7 +1391,7 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>128968</v>
+        <v>145856</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1399,15 +1399,15 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>7000</v>
+        <v>24000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>121968</v>
+        <v>121856</v>
       </c>
     </row>
     <row r="30">
@@ -1629,11 +1629,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>142174</v>
+        <v>144374</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>135.6%</t>
+          <t>137.8%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>135576</v>
+        <v>137776</v>
       </c>
     </row>
     <row r="37">
@@ -1731,11 +1731,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>87750</v>
+        <v>99750</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1743,11 +1743,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>81150</v>
+        <v>93150</v>
       </c>
     </row>
     <row r="40">
@@ -1765,11 +1765,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>622406</v>
+        <v>650706</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>134.9%</t>
+          <t>142.0%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>539756</v>
+        <v>568056</v>
       </c>
     </row>
     <row r="41">
@@ -1833,11 +1833,11 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>135166</v>
+        <v>135564</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>121.5%</t>
+          <t>121.9%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>127566</v>
+        <v>127964</v>
       </c>
     </row>
     <row r="43">
@@ -1935,11 +1935,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>233590.46</v>
+        <v>237393.46</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>233590.46</v>
+        <v>237393.46</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>56723</v>
+        <v>77723</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>56723</v>
+        <v>77723</v>
       </c>
     </row>
     <row r="47">
@@ -2207,11 +2207,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>237335.8</v>
+        <v>236335.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>237335.8</v>
+        <v>236335.8</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>287418</v>
+        <v>288214</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>119.8%</t>
+          <t>120.1%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>287418</v>
+        <v>288214</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>140177</v>
+        <v>157175</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>130.2%</t>
+          <t>147.2%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2287,11 +2287,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>130177</v>
+        <v>147175</v>
       </c>
     </row>
     <row r="56">
@@ -2309,11 +2309,11 @@
         <v>80000</v>
       </c>
       <c r="D56" t="n">
-        <v>42388</v>
+        <v>52786</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>37388</v>
+        <v>47786</v>
       </c>
     </row>
     <row r="57">
@@ -2411,11 +2411,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>134398</v>
+        <v>144398</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>210.7%</t>
+          <t>227.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>126398</v>
+        <v>136398</v>
       </c>
     </row>
     <row r="60">
@@ -2479,11 +2479,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>62944</v>
+        <v>57964</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>62944</v>
+        <v>57964</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>63570</v>
+        <v>73570</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>47770</v>
+        <v>57770</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>20268</v>
+        <v>10268</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>337.8%</t>
+          <t>171.1%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>20268</v>
+        <v>10268</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,23 +473,23 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>314242</v>
+        <v>349259</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>111.7%</t>
+          <t>122.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>57366.67</v>
+        <v>68366.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>256875.33</v>
+        <v>280892.33</v>
       </c>
     </row>
     <row r="3">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>27500</v>
+        <v>28300</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>27500</v>
+        <v>28300</v>
       </c>
     </row>
     <row r="12">
@@ -949,11 +949,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>93976</v>
+        <v>94374</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -961,11 +961,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>75776</v>
+        <v>76174</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>29576</v>
+        <v>29974</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>29576</v>
+        <v>29974</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>80750.8</v>
+        <v>81348.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>80750.8</v>
+        <v>81348.8</v>
       </c>
     </row>
     <row r="19">
@@ -1051,23 +1051,23 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>129937.4</v>
+        <v>130387.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5000</v>
+        <v>13000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>124937.4</v>
+        <v>117387.7</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>81188.7</v>
+        <v>91188.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>77188.7</v>
+        <v>87188.7</v>
       </c>
     </row>
     <row r="21">
@@ -1187,11 +1187,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>186554</v>
+        <v>204150</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>186554</v>
+        <v>204150</v>
       </c>
     </row>
     <row r="24">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>124440</v>
+        <v>134440</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>83.1%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>114640</v>
+        <v>124640</v>
       </c>
     </row>
     <row r="26">
@@ -1293,19 +1293,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>51552</v>
+        <v>41552</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>80622</v>
+        <v>81020</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>161.2%</t>
+          <t>162.0%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>80622</v>
+        <v>81020</v>
       </c>
     </row>
     <row r="28">
@@ -1527,11 +1527,11 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>160667.64</v>
+        <v>162765.64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>126867.64</v>
+        <v>128965.64</v>
       </c>
     </row>
     <row r="34">
@@ -1595,11 +1595,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>104240.92</v>
+        <v>104838.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>97640.92</v>
+        <v>98238.92</v>
       </c>
     </row>
     <row r="36">
@@ -1663,11 +1663,11 @@
         <v>40000</v>
       </c>
       <c r="D37" t="n">
-        <v>14288</v>
+        <v>15788</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>14288</v>
+        <v>15788</v>
       </c>
     </row>
     <row r="38">
@@ -1735,19 +1735,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>6600</v>
+        <v>26400</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>93150</v>
+        <v>73350</v>
       </c>
     </row>
     <row r="40">
@@ -1765,11 +1765,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>650706</v>
+        <v>660706.01</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>142.0%</t>
+          <t>144.5%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>568056</v>
+        <v>578056.01</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>104869</v>
+        <v>111469</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>104869</v>
+        <v>111469</v>
       </c>
     </row>
     <row r="42">
@@ -1833,11 +1833,11 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>135564</v>
+        <v>142164</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>121.9%</t>
+          <t>128.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>127964</v>
+        <v>134564</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>126947</v>
+        <v>127345</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1879,11 +1879,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>94724.76000000001</v>
+        <v>95122.76000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1935,11 +1935,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>237393.46</v>
+        <v>241686.46</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>237393.46</v>
+        <v>241686.46</v>
       </c>
     </row>
     <row r="46">
@@ -2003,11 +2003,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>228917</v>
+        <v>233563</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>228917</v>
+        <v>233563</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>162490.4</v>
+        <v>155121.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>162490.4</v>
+        <v>155121.4</v>
       </c>
     </row>
     <row r="49">
@@ -2071,11 +2071,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>286122.04</v>
+        <v>297151.04</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>129.2%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>286122.04</v>
+        <v>297151.04</v>
       </c>
     </row>
     <row r="50">
@@ -2173,11 +2173,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>386638.97</v>
+        <v>426689.97</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>128.9%</t>
+          <t>142.2%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>386638.97</v>
+        <v>426689.97</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>236335.8</v>
+        <v>238293.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>108.3%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>236335.8</v>
+        <v>238293.8</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>288214</v>
+        <v>288490</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>120.1%</t>
+          <t>120.2%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>288214</v>
+        <v>288490</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>157175</v>
+        <v>177573</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>147.2%</t>
+          <t>167.6%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2287,11 +2287,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>147175</v>
+        <v>167573</v>
       </c>
     </row>
     <row r="56">
@@ -2513,11 +2513,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>73570</v>
+        <v>73968</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>57770</v>
+        <v>58168</v>
       </c>
     </row>
     <row r="63">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,91 +461,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>赵越</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>230000</v>
+        <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>349259</v>
+        <v>2678</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>122.1%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>68366.67</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>280892.33</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>田奇</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>150000</v>
+        <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>88544.10000000001</v>
+        <v>77176</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>83044.10000000001</v>
+        <v>77176</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>李明</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>120000</v>
+        <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>98098.67999999999</v>
+        <v>1996</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,63 +557,63 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>98098.67999999999</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>苏怡意</t>
+          <t>陈翔宇</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>150000</v>
+        <v>140000</v>
       </c>
       <c r="D5" t="n">
-        <v>59878.8</v>
+        <v>698</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>57278.8</v>
+        <v>698</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>姜玮</t>
+          <t>王秋</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>100000</v>
+        <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>74548.06</v>
+        <v>17198</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,29 +625,29 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>74548.06</v>
+        <v>17198</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>李家慧</t>
+          <t>余婉丽</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50000</v>
+        <v>140000</v>
       </c>
       <c r="D7" t="n">
-        <v>29988</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,29 +659,29 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>29988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>孙君兰</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>200000</v>
+        <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>62137.21</v>
+        <v>31500</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,63 +693,63 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>62137.21</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>陈紫灵</t>
+          <t>白蕾</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>200000</v>
+        <v>140000</v>
       </c>
       <c r="D9" t="n">
-        <v>66636.22</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>66436.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>林非凡</t>
+          <t>刘沁</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>100000</v>
+        <v>140000</v>
       </c>
       <c r="D10" t="n">
-        <v>161239.7</v>
+        <v>398</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>161.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,29 +761,29 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>161239.7</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>米兰兰</t>
+          <t>芊雅</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>100000</v>
+        <v>140000</v>
       </c>
       <c r="D11" t="n">
-        <v>28300</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,63 +795,63 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>28300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>刘馨</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>178778.4</v>
+        <v>6194</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>56600</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>122178.4</v>
+        <v>6194</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>朱锋剑</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>100000</v>
+        <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>38899.23</v>
+        <v>13274</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,131 +863,131 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>38899.23</v>
+        <v>13274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>韩雪</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>120000</v>
+        <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>118770</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>97270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>120000</v>
+        <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>106630</v>
+        <v>47668</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>29198</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>77432</v>
+        <v>47668</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>朱碧丹</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>120000</v>
+        <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>94374</v>
+        <v>28196</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>18200</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>76174</v>
+        <v>28196</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>王钰尧</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>50000</v>
+        <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>29974</v>
+        <v>26469</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,29 +999,29 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>29974</v>
+        <v>26469</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>邓璐</t>
+          <t>唐晟</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>280000</v>
+        <v>90000</v>
       </c>
       <c r="D18" t="n">
-        <v>81348.8</v>
+        <v>2090</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,97 +1033,97 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>81348.8</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>马雅丽</t>
+          <t>王凯</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>180000</v>
+        <v>90000</v>
       </c>
       <c r="D19" t="n">
-        <v>130387.7</v>
+        <v>0</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>117387.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周思若</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>220000</v>
+        <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>91188.7</v>
+        <v>30887</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>87188.7</v>
+        <v>30887</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>袁登玉</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>60000</v>
+        <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>32072.55</v>
+        <v>36695</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,29 +1135,29 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>32072.55</v>
+        <v>36695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>邝玉萍</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>60000</v>
+        <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>398</v>
+        <v>10398</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,29 +1169,29 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>398</v>
+        <v>10398</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>200000</v>
+        <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>204150</v>
+        <v>11894</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,29 +1203,29 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>204150</v>
+        <v>11894</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>白蕾</t>
+          <t>郑巨光</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>150000</v>
+        <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>8590</v>
+        <v>2225.88</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1237,97 +1237,97 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>8590</v>
+        <v>2225.88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>刘沁</t>
+          <t>陈舒羽</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>134440</v>
+        <v>1798</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>9800</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>124640</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>王芊雅</t>
+          <t>沈悦</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>51552</v>
+        <v>0</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>41552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>刘馨</t>
+          <t>张回</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>50000</v>
+        <v>70000</v>
       </c>
       <c r="D27" t="n">
-        <v>81020</v>
+        <v>3398</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>162.0%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,131 +1339,131 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>81020</v>
+        <v>3398</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>陈月娇</t>
+          <t>冯兰兰</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>15186</v>
+        <v>0</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>19399.98</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>127.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>-4213.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>160000</v>
+        <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>145856</v>
+        <v>26777.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>121856</v>
+        <v>26777.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>杨红瑞</t>
+          <t>田奇</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>60000</v>
+        <v>130000</v>
       </c>
       <c r="D30" t="n">
-        <v>48376</v>
+        <v>7500</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>38376</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>普元媛</t>
+          <t>李明</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>60000</v>
+        <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>22894</v>
+        <v>8098</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1475,29 +1475,29 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>22894</v>
+        <v>8098</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>马奇君</t>
+          <t>苏怡意</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>30000</v>
+        <v>115000</v>
       </c>
       <c r="D32" t="n">
-        <v>28392</v>
+        <v>398</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1509,165 +1509,165 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>28392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>姜玮</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>180000</v>
+        <v>125000</v>
       </c>
       <c r="D33" t="n">
-        <v>162765.64</v>
+        <v>16998</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>33800</v>
+        <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>128965.64</v>
+        <v>16998</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>郑巨光</t>
+          <t>李家慧</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>180000</v>
+        <v>65000</v>
       </c>
       <c r="D34" t="n">
-        <v>165530.37</v>
+        <v>10000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>39833.4</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>125696.97</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>陈舒羽</t>
+          <t>邓璐</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>130000</v>
+        <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>104838.92</v>
+        <v>13596.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>98238.92</v>
+        <v>13596.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>沈悦</t>
+          <t>马雅丽</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="D36" t="n">
-        <v>144374</v>
+        <v>495.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>137.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>6598</v>
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>137776</v>
+        <v>495.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>张回</t>
+          <t>袁登玉</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>40000</v>
+        <v>100000</v>
       </c>
       <c r="D37" t="n">
-        <v>15788</v>
+        <v>20000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1679,29 +1679,29 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>15788</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>冯兰兰</t>
+          <t>黄惠作</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>30000</v>
+        <v>200000</v>
       </c>
       <c r="D38" t="n">
-        <v>31295</v>
+        <v>0</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>104.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,97 +1713,97 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>31295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>陶雯</t>
+          <t>韦新妮</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="D39" t="n">
-        <v>99750</v>
+        <v>0</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>26400</v>
+        <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>73350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>郭海明</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>400000</v>
+        <v>200000</v>
       </c>
       <c r="D40" t="n">
-        <v>660706.01</v>
+        <v>0</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>144.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>82650</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>578056.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>赵越</t>
+          <t>杨琴</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="D41" t="n">
-        <v>111469</v>
+        <v>0</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,131 +1815,131 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>111469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>王秋</t>
+          <t>陈新星</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>105000</v>
+        <v>70000</v>
       </c>
       <c r="D42" t="n">
-        <v>142164</v>
+        <v>0</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>128.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>7600</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>134564</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>陈翔宇</t>
+          <t>田婉丽</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>105000</v>
+        <v>110000</v>
       </c>
       <c r="D43" t="n">
-        <v>127345</v>
+        <v>5000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>32222.24</v>
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>95122.76000000001</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>余婉丽</t>
+          <t>罗晗</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>50000</v>
       </c>
       <c r="D44" t="n">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>996</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>陈思羽</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>270000</v>
+        <v>30000</v>
       </c>
       <c r="D45" t="n">
-        <v>241686.46</v>
+        <v>0</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,29 +1951,29 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>241686.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>韩雪</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>120000</v>
+        <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>77723</v>
+        <v>32796</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,29 +1985,29 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>77723</v>
+        <v>32796</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>250000</v>
+        <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>233563</v>
+        <v>5996</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,29 +2019,29 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>233563</v>
+        <v>5996</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>朱碧丹</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>210000</v>
+        <v>110000</v>
       </c>
       <c r="D48" t="n">
-        <v>155121.4</v>
+        <v>8000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,29 +2053,29 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>155121.4</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>王钰尧</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>230000</v>
+        <v>70000</v>
       </c>
       <c r="D49" t="n">
-        <v>297151.04</v>
+        <v>0</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>129.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2087,29 +2087,29 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>297151.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>唐晟</t>
+          <t>孙君兰</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>80000</v>
+        <v>160000</v>
       </c>
       <c r="D50" t="n">
-        <v>8399</v>
+        <v>5668.15</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,29 +2121,29 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>8399</v>
+        <v>5668.15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>王凯</t>
+          <t>陈紫灵</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>80000</v>
+        <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>16338</v>
+        <v>11368.38</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2155,29 +2155,29 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>16338</v>
+        <v>11368.38</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>林非凡</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>300000</v>
+        <v>160000</v>
       </c>
       <c r="D52" t="n">
-        <v>426689.97</v>
+        <v>67.16</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>142.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,29 +2189,29 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>426689.97</v>
+        <v>67.16</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>米兰兰</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>220000</v>
+        <v>110000</v>
       </c>
       <c r="D53" t="n">
-        <v>238293.8</v>
+        <v>28800</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>108.3%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,29 +2223,29 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>238293.8</v>
+        <v>28800</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>240000</v>
+        <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>288490</v>
+        <v>7500</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>120.2%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,41 +2257,41 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>288490</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>朱锋剑</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="D55" t="n">
-        <v>177573</v>
+        <v>10700</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>167.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>167573</v>
+        <v>10700</v>
       </c>
     </row>
     <row r="56">
@@ -2302,30 +2302,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>谌黎平</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>80000</v>
+        <v>90000</v>
       </c>
       <c r="D56" t="n">
-        <v>52786</v>
+        <v>50398</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>47786</v>
+        <v>50398</v>
       </c>
     </row>
     <row r="57">
@@ -2336,18 +2336,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>马春兰</t>
+          <t>谌黎平</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>55252</v>
+        <v>796</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>55252</v>
+        <v>796</v>
       </c>
     </row>
     <row r="58">
@@ -2370,30 +2370,30 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>李颜君</t>
+          <t>马春兰</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="D58" t="n">
-        <v>33272</v>
+        <v>10000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>26272</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="59">
@@ -2404,30 +2404,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>蔡清霞</t>
+          <t>李颜君</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>144398</v>
+        <v>20000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>227.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>136398</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="60">
@@ -2438,18 +2438,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>吴静文</t>
+          <t>蔡清霞</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>46592</v>
+        <v>0</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>233.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,29 +2461,29 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>46592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>陈新星</t>
+          <t>吴静文</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="D61" t="n">
-        <v>57964</v>
+        <v>20000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,63 +2495,63 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>57964</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>田婉丽</t>
+          <t>陈月娇</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>120000</v>
+        <v>70000</v>
       </c>
       <c r="D62" t="n">
-        <v>73968</v>
+        <v>0</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>15800</v>
+        <v>0</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>58168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>罗晗</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6000</v>
+        <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>10268</v>
+        <v>12996</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>171.1%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,109 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>10268</v>
+        <v>12996</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>杨红瑞</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>普元媛</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D65" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>马奇君</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1594</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1594</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>2678</v>
+        <v>3376</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2678</v>
+        <v>3376</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>77176</v>
+        <v>87176</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>58800</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>77176</v>
+        <v>28376</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>1996</v>
+        <v>2694</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1996</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="5">
@@ -609,11 +609,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>17198</v>
+        <v>17596</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>17198</v>
+        <v>17596</v>
       </c>
     </row>
     <row r="7">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>31500</v>
+        <v>32296</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>31500</v>
+        <v>32296</v>
       </c>
     </row>
     <row r="9">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>47668</v>
+        <v>48066</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>47668</v>
+        <v>48066</v>
       </c>
     </row>
     <row r="16">
@@ -983,11 +983,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>26469</v>
+        <v>31469</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>26469</v>
+        <v>31469</v>
       </c>
     </row>
     <row r="18">
@@ -1119,11 +1119,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>36695</v>
+        <v>50606</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>36695</v>
+        <v>50606</v>
       </c>
     </row>
     <row r="22">
@@ -1187,11 +1187,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>11894</v>
+        <v>12782.32</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>11894</v>
+        <v>12782.32</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>2225.88</v>
+        <v>14623.88</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2225.88</v>
+        <v>14623.88</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>1798</v>
+        <v>2794</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1798</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="26">
@@ -1391,11 +1391,11 @@
         <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>26777.6</v>
+        <v>26977.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>26777.6</v>
+        <v>26977.6</v>
       </c>
     </row>
     <row r="30">
@@ -1459,11 +1459,11 @@
         <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>8098</v>
+        <v>15598</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>8098</v>
+        <v>15598</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>115000</v>
       </c>
       <c r="D32" t="n">
-        <v>398</v>
+        <v>20498</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>398</v>
+        <v>20498</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>125000</v>
       </c>
       <c r="D33" t="n">
-        <v>16998</v>
+        <v>17796</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>16998</v>
+        <v>17796</v>
       </c>
     </row>
     <row r="34">
@@ -1599,19 +1599,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>33600</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>247.1%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>13596.8</v>
+        <v>-20003.2</v>
       </c>
     </row>
     <row r="36">
@@ -1667,19 +1667,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>20000</v>
+        <v>18020</v>
       </c>
     </row>
     <row r="38">
@@ -1901,11 +1901,11 @@
         <v>50000</v>
       </c>
       <c r="D44" t="n">
-        <v>996</v>
+        <v>8996</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>996</v>
+        <v>8996</v>
       </c>
     </row>
     <row r="45">
@@ -1969,11 +1969,11 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>32796</v>
+        <v>33394</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>32796</v>
+        <v>33394</v>
       </c>
     </row>
     <row r="47">
@@ -2003,23 +2003,23 @@
         <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>5996</v>
+        <v>12596</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>9200</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>5996</v>
+        <v>3396</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>110000</v>
       </c>
       <c r="D48" t="n">
-        <v>8000</v>
+        <v>8398</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>8000</v>
+        <v>8398</v>
       </c>
     </row>
     <row r="49">
@@ -2105,11 +2105,11 @@
         <v>160000</v>
       </c>
       <c r="D50" t="n">
-        <v>5668.15</v>
+        <v>15668.15</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>5668.15</v>
+        <v>15668.15</v>
       </c>
     </row>
     <row r="51">
@@ -2139,23 +2139,23 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>11368.38</v>
+        <v>21368.38</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>11368.38</v>
+        <v>13368.38</v>
       </c>
     </row>
     <row r="52">
@@ -2309,11 +2309,11 @@
         <v>90000</v>
       </c>
       <c r="D56" t="n">
-        <v>50398</v>
+        <v>70796</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>50398</v>
+        <v>70796</v>
       </c>
     </row>
     <row r="57">
@@ -2343,11 +2343,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>796</v>
+        <v>1194</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>796</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="58">
@@ -2411,11 +2411,11 @@
         <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>20000</v>
+        <v>65600</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>20000</v>
+        <v>65600</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="61">
@@ -2547,11 +2547,11 @@
         <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>12996</v>
+        <v>13394</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>12996</v>
+        <v>13394</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>3376</v>
+        <v>3774</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3376</v>
+        <v>3774</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>87176</v>
+        <v>93776</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>28376</v>
+        <v>34976</v>
       </c>
     </row>
     <row r="4">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>32296</v>
+        <v>32694</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>32296</v>
+        <v>32694</v>
       </c>
     </row>
     <row r="9">
@@ -847,11 +847,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>13274</v>
+        <v>-48594.33000000002</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>13274</v>
+        <v>-48594.33000000002</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>20398</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>20398</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>48066</v>
+        <v>49866</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>48066</v>
+        <v>49866</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>28196</v>
+        <v>29394</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>28196</v>
+        <v>29394</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>31469</v>
+        <v>64963.61</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>31469</v>
+        <v>64963.61</v>
       </c>
     </row>
     <row r="18">
@@ -1085,11 +1085,11 @@
         <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>30887</v>
+        <v>85298.64</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>30887</v>
+        <v>85298.64</v>
       </c>
     </row>
     <row r="21">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>10398</v>
+        <v>36056</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>10398</v>
+        <v>36056</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>12782.32</v>
+        <v>32782.32</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>12782.32</v>
+        <v>32782.32</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>14623.88</v>
+        <v>25021.88</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>14623.88</v>
+        <v>25021.88</v>
       </c>
     </row>
     <row r="25">
@@ -1323,11 +1323,11 @@
         <v>70000</v>
       </c>
       <c r="D27" t="n">
-        <v>3398</v>
+        <v>3796</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3398</v>
+        <v>3796</v>
       </c>
     </row>
     <row r="28">
@@ -1391,11 +1391,11 @@
         <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>26977.6</v>
+        <v>53977.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>26977.6</v>
+        <v>53977.6</v>
       </c>
     </row>
     <row r="30">
@@ -1425,23 +1425,23 @@
         <v>130000</v>
       </c>
       <c r="D30" t="n">
-        <v>7500</v>
+        <v>7700</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>7500</v>
+        <v>700</v>
       </c>
     </row>
     <row r="31">
@@ -1459,23 +1459,23 @@
         <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>15598</v>
+        <v>18698</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>15598</v>
+        <v>9198</v>
       </c>
     </row>
     <row r="32">
@@ -1531,19 +1531,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>17796</v>
+        <v>9296</v>
       </c>
     </row>
     <row r="34">
@@ -1595,11 +1595,11 @@
         <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>13596.8</v>
+        <v>24592.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>247.1%</t>
+          <t>136.6%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>-20003.2</v>
+        <v>-9007.200000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1867,11 +1867,11 @@
         <v>110000</v>
       </c>
       <c r="D43" t="n">
-        <v>5000</v>
+        <v>6680</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>5000</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="44">
@@ -2139,11 +2139,11 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>21368.38</v>
+        <v>32211.24</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2151,11 +2151,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>13368.38</v>
+        <v>24211.24</v>
       </c>
     </row>
     <row r="52">
@@ -2173,11 +2173,11 @@
         <v>160000</v>
       </c>
       <c r="D52" t="n">
-        <v>67.16</v>
+        <v>533.8199999999999</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>67.16</v>
+        <v>533.8199999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2241,11 +2241,11 @@
         <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>7500</v>
+        <v>8572.700000000001</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>7500</v>
+        <v>8572.700000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>150000</v>
       </c>
       <c r="D55" t="n">
-        <v>10700</v>
+        <v>20700</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>10700</v>
+        <v>20700</v>
       </c>
     </row>
     <row r="56">
@@ -2377,11 +2377,11 @@
         <v>80000</v>
       </c>
       <c r="D58" t="n">
-        <v>10000</v>
+        <v>20398</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>10000</v>
+        <v>20398</v>
       </c>
     </row>
     <row r="59">
@@ -2445,11 +2445,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>398</v>
+        <v>796</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>398</v>
+        <v>796</v>
       </c>
     </row>
     <row r="61">
@@ -2547,11 +2547,11 @@
         <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>13394</v>
+        <v>42792</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>13394</v>
+        <v>42792</v>
       </c>
     </row>
     <row r="64">
@@ -2581,11 +2581,11 @@
         <v>50000</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>796</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>796</v>
       </c>
     </row>
     <row r="65">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>3774</v>
+        <v>41370</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3774</v>
+        <v>41370</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>93776</v>
+        <v>271308</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>34976</v>
+        <v>212508</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>2694</v>
+        <v>73668</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2694</v>
+        <v>73668</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>140000</v>
       </c>
       <c r="D5" t="n">
-        <v>698</v>
+        <v>60698</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>698</v>
+        <v>60698</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>17596</v>
+        <v>28392</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>17596</v>
+        <v>26792</v>
       </c>
     </row>
     <row r="7">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>32694</v>
+        <v>33490</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>32694</v>
+        <v>33490</v>
       </c>
     </row>
     <row r="9">
@@ -745,11 +745,11 @@
         <v>140000</v>
       </c>
       <c r="D10" t="n">
-        <v>398</v>
+        <v>1194</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>398</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>6194</v>
+        <v>6592</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6194</v>
+        <v>6592</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>-48594.33000000002</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -859,11 +859,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-48594.33000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>49866</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>49866</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>29394</v>
+        <v>0</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>29394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>64963.61</v>
+        <v>0</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>64963.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>90000</v>
       </c>
       <c r="D18" t="n">
-        <v>2090</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2090</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1085,11 +1085,11 @@
         <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>85298.64</v>
+        <v>0</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>85298.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>50606</v>
+        <v>0</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>50606</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>36056</v>
+        <v>20398</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>36056</v>
+        <v>20398</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>32782.32</v>
+        <v>33180.32</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>32782.32</v>
+        <v>33180.32</v>
       </c>
     </row>
     <row r="24">
@@ -1221,23 +1221,23 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>25021.88</v>
+        <v>45419.88</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>796</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>25021.88</v>
+        <v>44623.88</v>
       </c>
     </row>
     <row r="25">
@@ -1255,23 +1255,23 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>2794</v>
+        <v>3790</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>263.9%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2794</v>
+        <v>-6210</v>
       </c>
     </row>
     <row r="26">
@@ -1289,11 +1289,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="27">
@@ -1357,11 +1357,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>598</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>53977.6</v>
+        <v>64756.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>53977.6</v>
+        <v>64756.2</v>
       </c>
     </row>
     <row r="30">
@@ -1429,19 +1429,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>7000</v>
+        <v>14500</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>188.3%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>700</v>
+        <v>-6800</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>18698</v>
+        <v>49696</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>9198</v>
+        <v>40196</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>115000</v>
       </c>
       <c r="D32" t="n">
-        <v>20498</v>
+        <v>30498</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>20498</v>
+        <v>30498</v>
       </c>
     </row>
     <row r="33">
@@ -1561,11 +1561,11 @@
         <v>65000</v>
       </c>
       <c r="D34" t="n">
-        <v>10000</v>
+        <v>20398</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>10000</v>
+        <v>20398</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>24592.8</v>
+        <v>28864</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>116.4%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>-9007.200000000001</v>
+        <v>-4736</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>150000</v>
       </c>
       <c r="D36" t="n">
-        <v>495.3</v>
+        <v>2278.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>495.3</v>
+        <v>2278.9</v>
       </c>
     </row>
     <row r="37">
@@ -1833,23 +1833,23 @@
         <v>70000</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>7083.33</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>590.3%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>-5883.33</v>
       </c>
     </row>
     <row r="43">
@@ -1969,11 +1969,11 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>33394</v>
+        <v>43792</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>33394</v>
+        <v>43792</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>12596</v>
+        <v>53790</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>3396</v>
+        <v>44590</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>110000</v>
       </c>
       <c r="D48" t="n">
-        <v>8398</v>
+        <v>52398</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>8398</v>
+        <v>52398</v>
       </c>
     </row>
     <row r="49">
@@ -2071,11 +2071,11 @@
         <v>70000</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="50">
@@ -2105,11 +2105,11 @@
         <v>160000</v>
       </c>
       <c r="D50" t="n">
-        <v>15668.15</v>
+        <v>23668.15</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>15668.15</v>
+        <v>23668.15</v>
       </c>
     </row>
     <row r="51">
@@ -2139,23 +2139,23 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>32211.24</v>
+        <v>33364.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>8000</v>
+        <v>11600</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>24211.24</v>
+        <v>21764.8</v>
       </c>
     </row>
     <row r="52">
@@ -2173,11 +2173,11 @@
         <v>160000</v>
       </c>
       <c r="D52" t="n">
-        <v>533.8199999999999</v>
+        <v>46836.3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>533.8199999999999</v>
+        <v>46836.3</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>110000</v>
       </c>
       <c r="D53" t="n">
-        <v>28800</v>
+        <v>29198</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>28800</v>
+        <v>29198</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>8572.700000000001</v>
+        <v>10972.7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>8572.700000000001</v>
+        <v>10972.7</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>150000</v>
       </c>
       <c r="D55" t="n">
-        <v>20700</v>
+        <v>21500</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>20700</v>
+        <v>21500</v>
       </c>
     </row>
     <row r="56">
@@ -2343,11 +2343,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>1194</v>
+        <v>11194</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1194</v>
+        <v>11194</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>80000</v>
       </c>
       <c r="D58" t="n">
-        <v>20398</v>
+        <v>30398</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>20398</v>
+        <v>30398</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>65600</v>
+        <v>65998</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>65600</v>
+        <v>65998</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>796</v>
+        <v>38396</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>796</v>
+        <v>38396</v>
       </c>
     </row>
     <row r="61">
@@ -2547,23 +2547,23 @@
         <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>42792</v>
+        <v>43190</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>42792</v>
+        <v>39790</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F63" t="n">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>41370</v>
+        <v>61370</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>41370</v>
+        <v>61370</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>271308</v>
+        <v>281908</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>212508</v>
+        <v>223108</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>73668</v>
+        <v>93468</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>73668</v>
+        <v>93468</v>
       </c>
     </row>
     <row r="5">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>33490</v>
+        <v>40090</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>33490</v>
+        <v>40090</v>
       </c>
     </row>
     <row r="9">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-598</v>
       </c>
     </row>
     <row r="10">
@@ -847,11 +847,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>22279.66999999998</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>22279.66999999998</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>20398</v>
+        <v>42671.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>20398</v>
+        <v>42671.55</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>75946</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>75946</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>63906.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>63906.2</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>112331.61</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>112331.61</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>90000</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2090</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>90000</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>128100.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>128100.6</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>64606</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>64606</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>20398</v>
+        <v>74349</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>20398</v>
+        <v>74349</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>33180.32</v>
+        <v>40980.32</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>33180.32</v>
+        <v>40980.32</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>45419.88</v>
+        <v>55419.88</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>44623.88</v>
+        <v>54623.88</v>
       </c>
     </row>
     <row r="25">
@@ -1391,11 +1391,11 @@
         <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>64756.2</v>
+        <v>75154.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>64756.2</v>
+        <v>75154.2</v>
       </c>
     </row>
     <row r="30">
@@ -1493,11 +1493,11 @@
         <v>115000</v>
       </c>
       <c r="D32" t="n">
-        <v>30498</v>
+        <v>30896</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>30498</v>
+        <v>30896</v>
       </c>
     </row>
     <row r="33">
@@ -1595,11 +1595,11 @@
         <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>28864</v>
+        <v>39660</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>116.4%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>-4736</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="36">
@@ -1671,15 +1671,15 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1980</v>
+        <v>3960</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>18020</v>
+        <v>16040</v>
       </c>
     </row>
     <row r="38">
@@ -1935,11 +1935,11 @@
         <v>30000</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="46">
@@ -2003,11 +2003,11 @@
         <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>53790</v>
+        <v>118590</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>44590</v>
+        <v>109390</v>
       </c>
     </row>
     <row r="48">
@@ -2071,11 +2071,11 @@
         <v>70000</v>
       </c>
       <c r="D49" t="n">
-        <v>398</v>
+        <v>5398</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>398</v>
+        <v>5398</v>
       </c>
     </row>
     <row r="50">
@@ -2139,11 +2139,11 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>33364.8</v>
+        <v>33564.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2151,11 +2151,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>21764.8</v>
+        <v>21964.8</v>
       </c>
     </row>
     <row r="52">
@@ -2207,11 +2207,11 @@
         <v>110000</v>
       </c>
       <c r="D53" t="n">
-        <v>29198</v>
+        <v>36698</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>29198</v>
+        <v>36698</v>
       </c>
     </row>
     <row r="54">
@@ -2309,11 +2309,11 @@
         <v>90000</v>
       </c>
       <c r="D56" t="n">
-        <v>70796</v>
+        <v>70996</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>70796</v>
+        <v>70996</v>
       </c>
     </row>
     <row r="57">
@@ -2343,11 +2343,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>11194</v>
+        <v>30994</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>11194</v>
+        <v>30994</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>80000</v>
       </c>
       <c r="D58" t="n">
-        <v>30398</v>
+        <v>30796</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>30398</v>
+        <v>30796</v>
       </c>
     </row>
     <row r="59">
@@ -2419,15 +2419,15 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>65998</v>
+        <v>64998</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>38396</v>
+        <v>38794</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>38396</v>
+        <v>38794</v>
       </c>
     </row>
     <row r="61">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -507,11 +507,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>281908</v>
+        <v>223108</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -609,11 +609,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>28392</v>
+        <v>26792</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -711,11 +711,11 @@
         <v>140000</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-598</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>55419.88</v>
+        <v>54623.88</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>3790</v>
+        <v>-6210</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1425,11 +1425,11 @@
         <v>130000</v>
       </c>
       <c r="D30" t="n">
-        <v>7700</v>
+        <v>-6800</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1459,11 +1459,11 @@
         <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>49696</v>
+        <v>40196</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1527,11 +1527,11 @@
         <v>125000</v>
       </c>
       <c r="D33" t="n">
-        <v>17796</v>
+        <v>9296</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1595,11 +1595,11 @@
         <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>39660</v>
+        <v>6060</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1663,11 +1663,11 @@
         <v>100000</v>
       </c>
       <c r="D37" t="n">
-        <v>20000</v>
+        <v>16040</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1833,11 +1833,11 @@
         <v>70000</v>
       </c>
       <c r="D42" t="n">
-        <v>1200</v>
+        <v>-5883.33</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2003,11 +2003,11 @@
         <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>118590</v>
+        <v>109390</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2139,11 +2139,11 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>33564.8</v>
+        <v>21964.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2411,11 +2411,11 @@
         <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>65998</v>
+        <v>64998</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2547,11 +2547,11 @@
         <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>43190</v>
+        <v>39790</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F63" t="n">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -507,11 +507,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>223108</v>
+        <v>281908</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -609,11 +609,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>26792</v>
+        <v>28392</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -711,11 +711,11 @@
         <v>140000</v>
       </c>
       <c r="D9" t="n">
-        <v>-598</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>54623.88</v>
+        <v>55419.88</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>-6210</v>
+        <v>3790</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1425,11 +1425,11 @@
         <v>130000</v>
       </c>
       <c r="D30" t="n">
-        <v>-6800</v>
+        <v>7700</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1459,11 +1459,11 @@
         <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>40196</v>
+        <v>49696</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1527,11 +1527,11 @@
         <v>125000</v>
       </c>
       <c r="D33" t="n">
-        <v>9296</v>
+        <v>17796</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1595,11 +1595,11 @@
         <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>6060</v>
+        <v>39660</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1663,11 +1663,11 @@
         <v>100000</v>
       </c>
       <c r="D37" t="n">
-        <v>16040</v>
+        <v>20000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1833,11 +1833,11 @@
         <v>70000</v>
       </c>
       <c r="D42" t="n">
-        <v>-5883.33</v>
+        <v>1200</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2003,11 +2003,11 @@
         <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>109390</v>
+        <v>118590</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2139,11 +2139,11 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>21964.8</v>
+        <v>33564.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2411,11 +2411,11 @@
         <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>64998</v>
+        <v>65998</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2547,11 +2547,11 @@
         <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>39790</v>
+        <v>43190</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F63" t="n">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>61370</v>
+        <v>71370</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>61370</v>
+        <v>71370</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>281908</v>
+        <v>320804</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>58800</v>
+        <v>66300</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>223108</v>
+        <v>254504</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>93468</v>
+        <v>113268</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>93468</v>
+        <v>113268</v>
       </c>
     </row>
     <row r="5">
@@ -609,11 +609,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>28392</v>
+        <v>38392</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -621,11 +621,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>26792</v>
+        <v>36792</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>140000</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>16600</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>16600</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>40090</v>
+        <v>61288</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>40090</v>
+        <v>59608</v>
       </c>
     </row>
     <row r="9">
@@ -813,23 +813,23 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>6592</v>
+        <v>7192</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6592</v>
+        <v>6794</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>22279.66999999998</v>
+        <v>26022.66999999998</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>22279.66999999998</v>
+        <v>26022.66999999998</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>42671.55</v>
+        <v>55467.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>42671.55</v>
+        <v>55467.55</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>75946</v>
+        <v>77660.29000000001</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>75946</v>
+        <v>77660.29000000001</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>63906.2</v>
+        <v>84906.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>63906.2</v>
+        <v>84906.2</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>112331.61</v>
+        <v>115986.61</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>112331.61</v>
+        <v>115986.61</v>
       </c>
     </row>
     <row r="18">
@@ -1119,11 +1119,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>64606</v>
+        <v>42606</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>64606</v>
+        <v>42606</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>74349</v>
+        <v>80949</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>74349</v>
+        <v>80949</v>
       </c>
     </row>
     <row r="23">
@@ -1195,15 +1195,15 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>40980.32</v>
+        <v>40582.32</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>55419.88</v>
+        <v>55885.04</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>54623.88</v>
+        <v>55089.04</v>
       </c>
     </row>
     <row r="25">
@@ -1391,11 +1391,11 @@
         <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>75154.2</v>
+        <v>86352.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>75154.2</v>
+        <v>86352.2</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>130000</v>
       </c>
       <c r="D30" t="n">
-        <v>7700</v>
+        <v>9300</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>188.3%</t>
+          <t>155.9%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>-6800</v>
+        <v>-5200</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>49696</v>
+        <v>51296</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>40196</v>
+        <v>41796</v>
       </c>
     </row>
     <row r="32">
@@ -1833,11 +1833,11 @@
         <v>70000</v>
       </c>
       <c r="D42" t="n">
-        <v>1200</v>
+        <v>1598</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>590.3%</t>
+          <t>443.3%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>-5883.33</v>
+        <v>-5485.33</v>
       </c>
     </row>
     <row r="43">
@@ -1969,11 +1969,11 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>43792</v>
+        <v>54190</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>43792</v>
+        <v>54190</v>
       </c>
     </row>
     <row r="47">
@@ -2071,23 +2071,23 @@
         <v>70000</v>
       </c>
       <c r="D49" t="n">
-        <v>5398</v>
+        <v>5796</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>5398</v>
+        <v>4596</v>
       </c>
     </row>
     <row r="50">
@@ -2105,11 +2105,11 @@
         <v>160000</v>
       </c>
       <c r="D50" t="n">
-        <v>23668.15</v>
+        <v>24411.55</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>23668.15</v>
+        <v>24411.55</v>
       </c>
     </row>
     <row r="51">
@@ -2173,11 +2173,11 @@
         <v>160000</v>
       </c>
       <c r="D52" t="n">
-        <v>46836.3</v>
+        <v>47234.3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>46836.3</v>
+        <v>47234.3</v>
       </c>
     </row>
     <row r="53">
@@ -2275,11 +2275,11 @@
         <v>150000</v>
       </c>
       <c r="D55" t="n">
-        <v>21500</v>
+        <v>22300</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>21500</v>
+        <v>22300</v>
       </c>
     </row>
     <row r="56">
@@ -2343,11 +2343,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>30994</v>
+        <v>40994</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>30994</v>
+        <v>40994</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>80000</v>
       </c>
       <c r="D58" t="n">
-        <v>30796</v>
+        <v>31194</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>30796</v>
+        <v>31194</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>65998</v>
+        <v>66396</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>64998</v>
+        <v>65396</v>
       </c>
     </row>
     <row r="60">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -507,11 +507,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>320804</v>
+        <v>400500</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>114.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>254504</v>
+        <v>334200</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>113268</v>
+        <v>123268</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>113268</v>
+        <v>120268</v>
       </c>
     </row>
     <row r="5">
@@ -617,15 +617,15 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1600</v>
+        <v>22400</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>36792</v>
+        <v>15992</v>
       </c>
     </row>
     <row r="7">
@@ -753,15 +753,15 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>251.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1194</v>
+        <v>-1806</v>
       </c>
     </row>
     <row r="11">
@@ -813,23 +813,23 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>7192</v>
+        <v>9172</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>398</v>
+        <v>998</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6794</v>
+        <v>8174</v>
       </c>
     </row>
     <row r="13">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>77660.29000000001</v>
+        <v>98086.29000000001</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>77660.29000000001</v>
+        <v>98086.29000000001</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>84906.2</v>
+        <v>93996.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>84906.2</v>
+        <v>93996.2</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>115986.61</v>
+        <v>167786.61</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>115986.61</v>
+        <v>167786.61</v>
       </c>
     </row>
     <row r="18">
@@ -1085,11 +1085,11 @@
         <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>128100.6</v>
+        <v>153676.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>128100.6</v>
+        <v>153676.6</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>42606</v>
+        <v>47550</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>42606</v>
+        <v>47550</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>80949</v>
+        <v>87761</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>80949</v>
+        <v>87761</v>
       </c>
     </row>
     <row r="23">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>55885.04</v>
+        <v>65885.03999999999</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>55089.04</v>
+        <v>65089.03999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1289,11 +1289,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>398</v>
+        <v>996</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>398</v>
+        <v>996</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>70000</v>
       </c>
       <c r="D27" t="n">
-        <v>3796</v>
+        <v>11796</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3796</v>
+        <v>11796</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>598</v>
+        <v>5548</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>598</v>
+        <v>5548</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>86352.2</v>
+        <v>88163.62</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>86352.2</v>
+        <v>88163.62</v>
       </c>
     </row>
     <row r="30">
@@ -1493,11 +1493,11 @@
         <v>115000</v>
       </c>
       <c r="D32" t="n">
-        <v>30896</v>
+        <v>31920.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>30896</v>
+        <v>31920.8</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>125000</v>
       </c>
       <c r="D33" t="n">
-        <v>17796</v>
+        <v>18938.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>9296</v>
+        <v>10438.6</v>
       </c>
     </row>
     <row r="34">
@@ -1637,15 +1637,15 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>438.8%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2278.9</v>
+        <v>-7721.1</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>100000</v>
       </c>
       <c r="D37" t="n">
-        <v>20000</v>
+        <v>20398</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1675,11 +1675,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>16040</v>
+        <v>16438</v>
       </c>
     </row>
     <row r="38">
@@ -1867,11 +1867,11 @@
         <v>110000</v>
       </c>
       <c r="D43" t="n">
-        <v>6680</v>
+        <v>21680</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6680</v>
+        <v>21680</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>50000</v>
       </c>
       <c r="D44" t="n">
-        <v>8996</v>
+        <v>9394</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>8996</v>
+        <v>9394</v>
       </c>
     </row>
     <row r="45">
@@ -2105,11 +2105,11 @@
         <v>160000</v>
       </c>
       <c r="D50" t="n">
-        <v>24411.55</v>
+        <v>24809.55</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>24411.55</v>
+        <v>24809.55</v>
       </c>
     </row>
     <row r="51">
@@ -2139,11 +2139,11 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>33564.8</v>
+        <v>43962.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2151,11 +2151,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>21964.8</v>
+        <v>32362.8</v>
       </c>
     </row>
     <row r="52">
@@ -2241,11 +2241,11 @@
         <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>10972.7</v>
+        <v>18472.7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>10972.7</v>
+        <v>18472.7</v>
       </c>
     </row>
     <row r="55">
@@ -2351,15 +2351,15 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>40994</v>
+        <v>39314</v>
       </c>
     </row>
     <row r="58">
@@ -2411,11 +2411,11 @@
         <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>66396</v>
+        <v>76396</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>65396</v>
+        <v>75396</v>
       </c>
     </row>
     <row r="60">
@@ -2547,23 +2547,23 @@
         <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>43190</v>
+        <v>53190</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>3400</v>
+        <v>5400</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>39790</v>
+        <v>47790</v>
       </c>
     </row>
     <row r="64">
@@ -2649,11 +2649,11 @@
         <v>40000</v>
       </c>
       <c r="D66" t="n">
-        <v>1594</v>
+        <v>11992</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1594</v>
+        <v>11992</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>71370</v>
+        <v>91568</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>71370</v>
+        <v>91568</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>400500</v>
+        <v>407498</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>114.4%</t>
+          <t>116.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>334200</v>
+        <v>341198</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>123268</v>
+        <v>123666</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>88.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3000</v>
+        <v>7800</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>120268</v>
+        <v>115866</v>
       </c>
     </row>
     <row r="5">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>61288</v>
+        <v>62284</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>59608</v>
+        <v>60604</v>
       </c>
     </row>
     <row r="9">
@@ -881,11 +881,11 @@
         <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>55467.55</v>
+        <v>58025.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>55467.55</v>
+        <v>58025.55</v>
       </c>
     </row>
     <row r="15">
@@ -949,11 +949,11 @@
         <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>93996.2</v>
+        <v>125491.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>93996.2</v>
+        <v>125491.3</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>167786.61</v>
+        <v>168184.61</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>167786.61</v>
+        <v>168184.61</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>90000</v>
       </c>
       <c r="D18" t="n">
-        <v>2090</v>
+        <v>3590</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2090</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="19">
@@ -1119,11 +1119,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>47550</v>
+        <v>58748</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>47550</v>
+        <v>58748</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>87761</v>
+        <v>88159</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>87761</v>
+        <v>88159</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>40980.32</v>
+        <v>41313.76</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>40582.32</v>
+        <v>40915.76</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>65885.03999999999</v>
+        <v>67683.03999999999</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>65089.03999999999</v>
+        <v>66887.03999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1459,11 +1459,11 @@
         <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>51296</v>
+        <v>58796</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>41796</v>
+        <v>49296</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>115000</v>
       </c>
       <c r="D32" t="n">
-        <v>31920.8</v>
+        <v>32454.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>31920.8</v>
+        <v>32454.4</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>125000</v>
       </c>
       <c r="D33" t="n">
-        <v>18938.6</v>
+        <v>29336.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>10438.6</v>
+        <v>20836.6</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>65000</v>
       </c>
       <c r="D34" t="n">
-        <v>20398</v>
+        <v>20798</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>20398</v>
+        <v>20798</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>39660</v>
+        <v>40258</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6060</v>
+        <v>6658</v>
       </c>
     </row>
     <row r="36">
@@ -1663,7 +1663,7 @@
         <v>100000</v>
       </c>
       <c r="D37" t="n">
-        <v>20398</v>
+        <v>20398.01</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>16438</v>
+        <v>16438.01</v>
       </c>
     </row>
     <row r="38">
@@ -1833,11 +1833,11 @@
         <v>70000</v>
       </c>
       <c r="D42" t="n">
-        <v>1598</v>
+        <v>11996</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>443.3%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>-5485.33</v>
+        <v>4912.67</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>110000</v>
       </c>
       <c r="D43" t="n">
-        <v>21680</v>
+        <v>22078</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>21680</v>
+        <v>22078</v>
       </c>
     </row>
     <row r="44">
@@ -2003,11 +2003,11 @@
         <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>118590</v>
+        <v>128590</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>116.9%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>109390</v>
+        <v>119390</v>
       </c>
     </row>
     <row r="48">
@@ -2105,11 +2105,11 @@
         <v>160000</v>
       </c>
       <c r="D50" t="n">
-        <v>24809.55</v>
+        <v>45207.55</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>24809.55</v>
+        <v>45207.55</v>
       </c>
     </row>
     <row r="51">
@@ -2207,11 +2207,11 @@
         <v>110000</v>
       </c>
       <c r="D53" t="n">
-        <v>36698</v>
+        <v>37198</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>36698</v>
+        <v>37198</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>18472.7</v>
+        <v>48472.7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>18472.7</v>
+        <v>48472.7</v>
       </c>
     </row>
     <row r="55">
@@ -2309,11 +2309,11 @@
         <v>90000</v>
       </c>
       <c r="D56" t="n">
-        <v>70996</v>
+        <v>90996</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>101.1%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>70996</v>
+        <v>90996</v>
       </c>
     </row>
     <row r="57">
@@ -2377,11 +2377,11 @@
         <v>80000</v>
       </c>
       <c r="D58" t="n">
-        <v>31194</v>
+        <v>31592</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>31194</v>
+        <v>31592</v>
       </c>
     </row>
     <row r="59">
@@ -2445,11 +2445,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>38794</v>
+        <v>48794</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>38794</v>
+        <v>48794</v>
       </c>
     </row>
     <row r="61">
@@ -2547,11 +2547,11 @@
         <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>53190</v>
+        <v>53588</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>47790</v>
+        <v>48188</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>91568</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>91568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>407498</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>116.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>66300</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>341198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -541,23 +541,23 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>123666</v>
+        <v>21200</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>88.3%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7800</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>115866</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>140000</v>
       </c>
       <c r="D5" t="n">
-        <v>60698</v>
+        <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>60698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>38392</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>22400</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>15992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>140000</v>
       </c>
       <c r="D7" t="n">
-        <v>16600</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>16600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>62284</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>60604</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>598</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -745,23 +745,23 @@
         <v>140000</v>
       </c>
       <c r="D10" t="n">
-        <v>1194</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>251.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-1806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -813,23 +813,23 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>9172</v>
+        <v>600</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>998</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8174</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>26022.66999999998</v>
+        <v>38401.66999999993</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>26022.66999999998</v>
+        <v>38401.66999999993</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>58025.55</v>
+        <v>37627.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>58025.55</v>
+        <v>37627.55</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>98086.29000000001</v>
+        <v>99886.29000000001</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>98086.29000000001</v>
+        <v>99886.29000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1085,11 +1085,11 @@
         <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>153676.6</v>
+        <v>146477.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>153676.6</v>
+        <v>146477.6</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>58748</v>
+        <v>61648</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>58748</v>
+        <v>61648</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>88159</v>
+        <v>61161</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>88159</v>
+        <v>61161</v>
       </c>
     </row>
     <row r="23">
@@ -1187,23 +1187,23 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>41313.76</v>
+        <v>425.76</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>40915.76</v>
+        <v>425.76</v>
       </c>
     </row>
     <row r="24">
@@ -1221,23 +1221,23 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>67683.03999999999</v>
+        <v>22493.04</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>796</v>
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>66887.03999999999</v>
+        <v>22493.04</v>
       </c>
     </row>
     <row r="25">
@@ -1255,23 +1255,23 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>3790</v>
+        <v>0</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>263.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>-6210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1289,11 +1289,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>996</v>
+        <v>0</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>70000</v>
       </c>
       <c r="D27" t="n">
-        <v>11796</v>
+        <v>0</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>11796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>5548</v>
+        <v>0</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>88163.62</v>
+        <v>6992.72</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>88163.62</v>
+        <v>6992.72</v>
       </c>
     </row>
     <row r="30">
@@ -1425,23 +1425,23 @@
         <v>130000</v>
       </c>
       <c r="D30" t="n">
-        <v>9300</v>
+        <v>0</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>14500</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>155.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>-5200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1459,23 +1459,23 @@
         <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>58796</v>
+        <v>200</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>49296</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>115000</v>
       </c>
       <c r="D32" t="n">
-        <v>32454.4</v>
+        <v>1558.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>32454.4</v>
+        <v>1558.4</v>
       </c>
     </row>
     <row r="33">
@@ -1527,23 +1527,23 @@
         <v>125000</v>
       </c>
       <c r="D33" t="n">
-        <v>29336.6</v>
+        <v>3142.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>8500</v>
+        <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>20836.6</v>
+        <v>3142.6</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>65000</v>
       </c>
       <c r="D34" t="n">
-        <v>20798</v>
+        <v>400</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>20798</v>
+        <v>400</v>
       </c>
     </row>
     <row r="35">
@@ -1595,23 +1595,23 @@
         <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>40258</v>
+        <v>4872</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>33600</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6658</v>
+        <v>4872</v>
       </c>
     </row>
     <row r="36">
@@ -1629,23 +1629,23 @@
         <v>150000</v>
       </c>
       <c r="D36" t="n">
-        <v>2278.9</v>
+        <v>1482.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>438.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>-7721.1</v>
+        <v>1482.9</v>
       </c>
     </row>
     <row r="37">
@@ -1663,23 +1663,23 @@
         <v>100000</v>
       </c>
       <c r="D37" t="n">
-        <v>20398.01</v>
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3960</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>16438.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1833,23 +1833,23 @@
         <v>70000</v>
       </c>
       <c r="D42" t="n">
-        <v>11996</v>
+        <v>0</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>7083.33</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>4912.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>110000</v>
       </c>
       <c r="D43" t="n">
-        <v>22078</v>
+        <v>0</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>22078</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>50000</v>
       </c>
       <c r="D44" t="n">
-        <v>9394</v>
+        <v>0</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>9394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>30000</v>
       </c>
       <c r="D45" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>54190</v>
+        <v>0</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>54190</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2003,23 +2003,23 @@
         <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>128590</v>
+        <v>0</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>116.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>9200</v>
+        <v>0</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>119390</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>110000</v>
       </c>
       <c r="D48" t="n">
-        <v>52398</v>
+        <v>0</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>52398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2071,23 +2071,23 @@
         <v>70000</v>
       </c>
       <c r="D49" t="n">
-        <v>5796</v>
+        <v>0</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>4596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2105,11 +2105,11 @@
         <v>160000</v>
       </c>
       <c r="D50" t="n">
-        <v>45207.55</v>
+        <v>3819.55</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>45207.55</v>
+        <v>3819.55</v>
       </c>
     </row>
     <row r="51">
@@ -2139,23 +2139,23 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>43962.8</v>
+        <v>12494.32</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>11600</v>
+        <v>0</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>32362.8</v>
+        <v>12494.32</v>
       </c>
     </row>
     <row r="52">
@@ -2173,11 +2173,11 @@
         <v>160000</v>
       </c>
       <c r="D52" t="n">
-        <v>47234.3</v>
+        <v>21040.3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>47234.3</v>
+        <v>21040.3</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>110000</v>
       </c>
       <c r="D53" t="n">
-        <v>37198</v>
+        <v>0</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>37198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>48472.7</v>
+        <v>272.7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>48472.7</v>
+        <v>272.7</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>150000</v>
       </c>
       <c r="D55" t="n">
-        <v>22300</v>
+        <v>0</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>22300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2309,11 +2309,11 @@
         <v>90000</v>
       </c>
       <c r="D56" t="n">
-        <v>90996</v>
+        <v>0</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>101.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>90996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2343,23 +2343,23 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>40994</v>
+        <v>0</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>39314</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>80000</v>
       </c>
       <c r="D58" t="n">
-        <v>31592</v>
+        <v>0</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>31592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2411,23 +2411,23 @@
         <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>76396</v>
+        <v>0</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>75396</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>48794</v>
+        <v>0</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>48794</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>30000</v>
       </c>
       <c r="D61" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2547,23 +2547,23 @@
         <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>53588</v>
+        <v>0</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>48188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2581,11 +2581,11 @@
         <v>50000</v>
       </c>
       <c r="D64" t="n">
-        <v>796</v>
+        <v>0</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2615,11 +2615,11 @@
         <v>50000</v>
       </c>
       <c r="D65" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2649,11 +2649,11 @@
         <v>40000</v>
       </c>
       <c r="D66" t="n">
-        <v>11992</v>
+        <v>0</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>11992</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>66300</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-66300</v>
       </c>
     </row>
     <row r="4">
@@ -549,15 +549,15 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>21200</v>
+        <v>13400</v>
       </c>
     </row>
     <row r="5">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>22400</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-22400</v>
       </c>
     </row>
     <row r="7">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-1680</v>
       </c>
     </row>
     <row r="9">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-598</v>
       </c>
     </row>
     <row r="10">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
     </row>
     <row r="11">
@@ -821,15 +821,15 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>998</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>166.3%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>600</v>
+        <v>-398</v>
       </c>
     </row>
     <row r="13">
@@ -1195,15 +1195,15 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>425.76</v>
+        <v>27.75999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1229,15 +1229,15 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>796</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>22493.04</v>
+        <v>21697.04</v>
       </c>
     </row>
     <row r="25">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="26">
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>14500</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>-14500</v>
       </c>
     </row>
     <row r="31">
@@ -1467,15 +1467,15 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4750.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>200</v>
+        <v>-9300</v>
       </c>
     </row>
     <row r="32">
@@ -1535,15 +1535,15 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>270.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3142.6</v>
+        <v>-5357.4</v>
       </c>
     </row>
     <row r="34">
@@ -1603,15 +1603,15 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>33600</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>689.7%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4872</v>
+        <v>-28728</v>
       </c>
     </row>
     <row r="36">
@@ -1637,15 +1637,15 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>674.4%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1482.9</v>
+        <v>-8517.1</v>
       </c>
     </row>
     <row r="37">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>3960</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>-3960</v>
       </c>
     </row>
     <row r="38">
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>7083.33</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>-7083.33</v>
       </c>
     </row>
     <row r="43">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>9200</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>-9200</v>
       </c>
     </row>
     <row r="48">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>-1200</v>
       </c>
     </row>
     <row r="50">
@@ -2147,15 +2147,15 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>11600</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>12494.32</v>
+        <v>894.3199999999997</v>
       </c>
     </row>
     <row r="52">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>-1680</v>
       </c>
     </row>
     <row r="58">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="60">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>-5400</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>91568</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>91568</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>407498</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>116.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-66300</v>
+        <v>341198</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>21200</v>
+        <v>123666</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>88.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -553,11 +553,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>13400</v>
+        <v>115866</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>140000</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>60698</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>60698</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>38392</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -621,11 +621,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-22400</v>
+        <v>15992</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>140000</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>16600</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>16600</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>62284</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-1680</v>
+        <v>60604</v>
       </c>
     </row>
     <row r="9">
@@ -745,11 +745,11 @@
         <v>140000</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1194</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>251.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-3000</v>
+        <v>-1806</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>600</v>
+        <v>9172</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>166.3%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-398</v>
+        <v>8174</v>
       </c>
     </row>
     <row r="13">
@@ -881,11 +881,11 @@
         <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>37627.55</v>
+        <v>58025.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>37627.55</v>
+        <v>58025.55</v>
       </c>
     </row>
     <row r="15">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>61161</v>
+        <v>88159</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>61161</v>
+        <v>88159</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>425.76</v>
+        <v>41313.76</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>27.75999999999999</v>
+        <v>40915.76</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>22493.04</v>
+        <v>67683.03999999999</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>21697.04</v>
+        <v>66887.03999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>3790</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>263.9%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>-10000</v>
+        <v>-6210</v>
       </c>
     </row>
     <row r="26">
@@ -1289,11 +1289,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>996</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>996</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>70000</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>11796</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>11796</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>5548</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>5548</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>6992.72</v>
+        <v>88386.72</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6992.72</v>
+        <v>88386.72</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>130000</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>9300</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>155.9%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>-14500</v>
+        <v>-5200</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>200</v>
+        <v>58796</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4750.0%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>-9300</v>
+        <v>49296</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>115000</v>
       </c>
       <c r="D32" t="n">
-        <v>1558.4</v>
+        <v>32454.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1558.4</v>
+        <v>32454.4</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>125000</v>
       </c>
       <c r="D33" t="n">
-        <v>3142.6</v>
+        <v>31334.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>270.5%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>-5357.4</v>
+        <v>22834.6</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>65000</v>
       </c>
       <c r="D34" t="n">
-        <v>400</v>
+        <v>20798</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>400</v>
+        <v>20798</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>4872</v>
+        <v>40258</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>689.7%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>-28728</v>
+        <v>6658</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>150000</v>
       </c>
       <c r="D36" t="n">
-        <v>1482.9</v>
+        <v>2278.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>674.4%</t>
+          <t>438.8%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>-8517.1</v>
+        <v>-7721.1</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>100000</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>20398.01</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1675,11 +1675,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>-3960</v>
+        <v>16438.01</v>
       </c>
     </row>
     <row r="38">
@@ -1833,11 +1833,11 @@
         <v>70000</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>11996</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>-7083.33</v>
+        <v>4912.67</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>110000</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>22078</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>22078</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>50000</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>9394</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>9394</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>30000</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>54190</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>54190</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>128590</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>116.9%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>-9200</v>
+        <v>119390</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>110000</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>52398</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>52398</v>
       </c>
     </row>
     <row r="49">
@@ -2071,11 +2071,11 @@
         <v>70000</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>5796</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2083,11 +2083,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>-1200</v>
+        <v>4596</v>
       </c>
     </row>
     <row r="50">
@@ -2105,11 +2105,11 @@
         <v>160000</v>
       </c>
       <c r="D50" t="n">
-        <v>3819.55</v>
+        <v>45207.55</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3819.55</v>
+        <v>45207.55</v>
       </c>
     </row>
     <row r="51">
@@ -2139,11 +2139,11 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>12494.32</v>
+        <v>44086.32</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2151,11 +2151,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>894.3199999999997</v>
+        <v>32486.32</v>
       </c>
     </row>
     <row r="52">
@@ -2173,11 +2173,11 @@
         <v>160000</v>
       </c>
       <c r="D52" t="n">
-        <v>21040.3</v>
+        <v>47234.3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>21040.3</v>
+        <v>47234.3</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>110000</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>37198</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>37198</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>272.7</v>
+        <v>48472.7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>272.7</v>
+        <v>48472.7</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>150000</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>22300</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>22300</v>
       </c>
     </row>
     <row r="56">
@@ -2309,11 +2309,11 @@
         <v>90000</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>90996</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>101.1%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>90996</v>
       </c>
     </row>
     <row r="57">
@@ -2343,11 +2343,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>40994</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2355,11 +2355,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>-1680</v>
+        <v>39314</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>80000</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>31592</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>31592</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>76396</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>-1000</v>
+        <v>75396</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>48794</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>48794</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>30000</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="62">
@@ -2547,11 +2547,11 @@
         <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>53588</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>-5400</v>
+        <v>48188</v>
       </c>
     </row>
     <row r="64">
@@ -2581,11 +2581,11 @@
         <v>50000</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>796</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>796</v>
       </c>
     </row>
     <row r="65">
@@ -2615,11 +2615,11 @@
         <v>50000</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="66">
@@ -2649,11 +2649,11 @@
         <v>40000</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>11992</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>11992</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>91568</v>
+        <v>119164</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>85.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>91568</v>
+        <v>119164</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>407498</v>
+        <v>462294</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>116.4%</t>
+          <t>132.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>66300</v>
+        <v>68280</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>341198</v>
+        <v>394014</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>123666</v>
+        <v>124064</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>88.3%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>115866</v>
+        <v>116264</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>140000</v>
       </c>
       <c r="D5" t="n">
-        <v>60698</v>
+        <v>90998</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>60698</v>
+        <v>89318</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>38392</v>
+        <v>38790</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -621,11 +621,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>15992</v>
+        <v>16390</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>140000</v>
       </c>
       <c r="D7" t="n">
-        <v>16600</v>
+        <v>26998</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>16600</v>
+        <v>26998</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>62284</v>
+        <v>89482</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>60604</v>
+        <v>87802</v>
       </c>
     </row>
     <row r="9">
@@ -745,11 +745,11 @@
         <v>140000</v>
       </c>
       <c r="D10" t="n">
-        <v>1194</v>
+        <v>21592</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>251.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-1806</v>
+        <v>18592</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>9172</v>
+        <v>9968</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8174</v>
+        <v>8970</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>38401.66999999993</v>
+        <v>63993.66999999993</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>38401.66999999993</v>
+        <v>63993.66999999993</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>58025.55</v>
+        <v>58423.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>58025.55</v>
+        <v>58423.55</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>99886.29000000001</v>
+        <v>124532.29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>99886.29000000001</v>
+        <v>124532.29</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>125491.3</v>
+        <v>140448.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>125491.3</v>
+        <v>140448.3</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>168184.61</v>
+        <v>196025.61</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>168184.61</v>
+        <v>196025.61</v>
       </c>
     </row>
     <row r="18">
@@ -1085,11 +1085,11 @@
         <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>146477.6</v>
+        <v>184289.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>146477.6</v>
+        <v>184289.6</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>61648</v>
+        <v>95440</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>61648</v>
+        <v>95440</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>88159</v>
+        <v>98159</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>88159</v>
+        <v>98159</v>
       </c>
     </row>
     <row r="23">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>67683.03999999999</v>
+        <v>76081.03999999999</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>66887.03999999999</v>
+        <v>75285.03999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>3790</v>
+        <v>4388</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>263.9%</t>
+          <t>227.9%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>-6210</v>
+        <v>-5612</v>
       </c>
     </row>
     <row r="26">
@@ -1289,11 +1289,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>996</v>
+        <v>1992</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>996</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>70000</v>
       </c>
       <c r="D27" t="n">
-        <v>11796</v>
+        <v>22194</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>11796</v>
+        <v>22194</v>
       </c>
     </row>
     <row r="28">
@@ -1391,11 +1391,11 @@
         <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>88386.72</v>
+        <v>144165.82</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>88386.72</v>
+        <v>144165.82</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>130000</v>
       </c>
       <c r="D30" t="n">
-        <v>9300</v>
+        <v>28800</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>155.9%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>-5200</v>
+        <v>14300</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>58796</v>
+        <v>71036.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>49296</v>
+        <v>61536.5</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>115000</v>
       </c>
       <c r="D32" t="n">
-        <v>32454.4</v>
+        <v>36603.68</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>32454.4</v>
+        <v>36603.68</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>125000</v>
       </c>
       <c r="D33" t="n">
-        <v>31334.6</v>
+        <v>31732.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>22834.6</v>
+        <v>23232.6</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>65000</v>
       </c>
       <c r="D34" t="n">
-        <v>20798</v>
+        <v>21196</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>20798</v>
+        <v>21196</v>
       </c>
     </row>
     <row r="35">
@@ -1595,23 +1595,23 @@
         <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>40258</v>
+        <v>57827.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>33600</v>
+        <v>34355</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6658</v>
+        <v>23472.3</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>150000</v>
       </c>
       <c r="D36" t="n">
-        <v>2278.9</v>
+        <v>2935.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>438.8%</t>
+          <t>340.6%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>-7721.1</v>
+        <v>-7064.200000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>100000</v>
       </c>
       <c r="D37" t="n">
-        <v>20398.01</v>
+        <v>32375.01</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1675,11 +1675,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>16438.01</v>
+        <v>28415.01</v>
       </c>
     </row>
     <row r="38">
@@ -1833,11 +1833,11 @@
         <v>70000</v>
       </c>
       <c r="D42" t="n">
-        <v>11996</v>
+        <v>20394</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>4912.67</v>
+        <v>13310.67</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>110000</v>
       </c>
       <c r="D43" t="n">
-        <v>22078</v>
+        <v>29598.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>22078</v>
+        <v>29598.8</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>50000</v>
       </c>
       <c r="D44" t="n">
-        <v>9394</v>
+        <v>9792</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>9394</v>
+        <v>9792</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>30000</v>
       </c>
       <c r="D45" t="n">
-        <v>1680</v>
+        <v>2078</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1680</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>54190</v>
+        <v>72588</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>54190</v>
+        <v>72588</v>
       </c>
     </row>
     <row r="47">
@@ -2003,23 +2003,23 @@
         <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>128590</v>
+        <v>128988</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>116.9%</t>
+          <t>117.3%</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>9200</v>
+        <v>14600</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>119390</v>
+        <v>114388</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>110000</v>
       </c>
       <c r="D48" t="n">
-        <v>52398</v>
+        <v>53194</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>52398</v>
+        <v>53194</v>
       </c>
     </row>
     <row r="49">
@@ -2105,11 +2105,11 @@
         <v>160000</v>
       </c>
       <c r="D50" t="n">
-        <v>45207.55</v>
+        <v>74258.25</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>45207.55</v>
+        <v>74258.25</v>
       </c>
     </row>
     <row r="51">
@@ -2139,11 +2139,11 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>44086.32</v>
+        <v>45048.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2151,11 +2151,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>32486.32</v>
+        <v>33448.5</v>
       </c>
     </row>
     <row r="52">
@@ -2173,11 +2173,11 @@
         <v>160000</v>
       </c>
       <c r="D52" t="n">
-        <v>47234.3</v>
+        <v>47773.05</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>47234.3</v>
+        <v>47773.05</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>110000</v>
       </c>
       <c r="D53" t="n">
-        <v>37198</v>
+        <v>44298</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>37198</v>
+        <v>44298</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>48472.7</v>
+        <v>58372.7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>48472.7</v>
+        <v>58372.7</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>150000</v>
       </c>
       <c r="D55" t="n">
-        <v>22300</v>
+        <v>34098</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>22300</v>
+        <v>34098</v>
       </c>
     </row>
     <row r="56">
@@ -2309,11 +2309,11 @@
         <v>90000</v>
       </c>
       <c r="D56" t="n">
-        <v>90996</v>
+        <v>91394</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>101.1%</t>
+          <t>101.5%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>90996</v>
+        <v>91394</v>
       </c>
     </row>
     <row r="57">
@@ -2343,11 +2343,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>40994</v>
+        <v>66192</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2355,11 +2355,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>39314</v>
+        <v>64512</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>80000</v>
       </c>
       <c r="D58" t="n">
-        <v>31592</v>
+        <v>41592</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>31592</v>
+        <v>41592</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>76396</v>
+        <v>86794</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>75396</v>
+        <v>85794</v>
       </c>
     </row>
     <row r="60">
@@ -2445,23 +2445,23 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>48794</v>
+        <v>62590</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>125.2%</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>48794</v>
+        <v>55990</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>30000</v>
       </c>
       <c r="D61" t="n">
-        <v>20000</v>
+        <v>20398</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>20000</v>
+        <v>20398</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>70000</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="63">
@@ -2581,11 +2581,11 @@
         <v>50000</v>
       </c>
       <c r="D64" t="n">
-        <v>796</v>
+        <v>1194</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>796</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="65">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>119164</v>
+        <v>58192</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>119164</v>
+        <v>58192</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>462294</v>
+        <v>63386</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>132.1%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>394014</v>
+        <v>-4894</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>124064</v>
+        <v>41796</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -553,11 +553,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>116264</v>
+        <v>33996</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>140000</v>
       </c>
       <c r="D5" t="n">
-        <v>90998</v>
+        <v>30300</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>89318</v>
+        <v>28620</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>38790</v>
+        <v>17794</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -621,11 +621,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>125.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>16390</v>
+        <v>-4606</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>140000</v>
       </c>
       <c r="D7" t="n">
-        <v>26998</v>
+        <v>10398</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>26998</v>
+        <v>10398</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>89482</v>
+        <v>28592</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>87802</v>
+        <v>26912</v>
       </c>
     </row>
     <row r="9">
@@ -745,11 +745,11 @@
         <v>140000</v>
       </c>
       <c r="D10" t="n">
-        <v>21592</v>
+        <v>20398</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>18592</v>
+        <v>17398</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>9968</v>
+        <v>796</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>125.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8970</v>
+        <v>-202</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>63993.66999999993</v>
+        <v>35745.67000000016</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>63993.66999999993</v>
+        <v>35745.67000000016</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>58423.55</v>
+        <v>38204.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>58423.55</v>
+        <v>38204.55</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>124532.29</v>
+        <v>159280.29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>124532.29</v>
+        <v>159280.29</v>
       </c>
     </row>
     <row r="16">
@@ -1119,11 +1119,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>95440</v>
+        <v>95706</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>95440</v>
+        <v>95706</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>98159</v>
+        <v>101161</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>98159</v>
+        <v>101161</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>41313.76</v>
+        <v>1625.76</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>40915.76</v>
+        <v>1227.76</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>76081.03999999999</v>
+        <v>32489.04</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>75285.03999999999</v>
+        <v>31693.04</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>4388</v>
+        <v>598</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>227.9%</t>
+          <t>1672.2%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>-5612</v>
+        <v>-9402</v>
       </c>
     </row>
     <row r="26">
@@ -1289,11 +1289,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>1992</v>
+        <v>1394</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1992</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>70000</v>
       </c>
       <c r="D27" t="n">
-        <v>22194</v>
+        <v>10796</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>22194</v>
+        <v>10796</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>5548</v>
+        <v>0</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>144165.82</v>
+        <v>85567.82000000001</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>144165.82</v>
+        <v>85567.82000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>130000</v>
       </c>
       <c r="D30" t="n">
-        <v>28800</v>
+        <v>19500</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>14300</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>71036.5</v>
+        <v>19940.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>61536.5</v>
+        <v>10440.5</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>115000</v>
       </c>
       <c r="D32" t="n">
-        <v>36603.68</v>
+        <v>5707.68</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>36603.68</v>
+        <v>5707.68</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>125000</v>
       </c>
       <c r="D33" t="n">
-        <v>31732.6</v>
+        <v>14336.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>23232.6</v>
+        <v>5836.6</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>65000</v>
       </c>
       <c r="D34" t="n">
-        <v>21196</v>
+        <v>798</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21196</v>
+        <v>798</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>57827.3</v>
+        <v>36035.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>23472.3</v>
+        <v>1680.300000000003</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>150000</v>
       </c>
       <c r="D36" t="n">
-        <v>2935.8</v>
+        <v>2477.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>340.6%</t>
+          <t>403.6%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>-7064.200000000001</v>
+        <v>-7522.2</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>100000</v>
       </c>
       <c r="D37" t="n">
-        <v>32375.01</v>
+        <v>13177.01</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1675,11 +1675,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>28415.01</v>
+        <v>9217.01</v>
       </c>
     </row>
     <row r="38">
@@ -1731,23 +1731,23 @@
         <v>200000</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>13176</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>151.8%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>-6824</v>
       </c>
     </row>
     <row r="40">
@@ -1765,23 +1765,23 @@
         <v>200000</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>50318</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>48338</v>
       </c>
     </row>
     <row r="41">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>-1980</v>
       </c>
     </row>
     <row r="42">
@@ -1833,11 +1833,11 @@
         <v>70000</v>
       </c>
       <c r="D42" t="n">
-        <v>20394</v>
+        <v>20476</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>13310.67</v>
+        <v>13392.67</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>110000</v>
       </c>
       <c r="D43" t="n">
-        <v>29598.8</v>
+        <v>7918.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>29598.8</v>
+        <v>7918.8</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>50000</v>
       </c>
       <c r="D44" t="n">
-        <v>9792</v>
+        <v>398</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>9792</v>
+        <v>398</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>30000</v>
       </c>
       <c r="D45" t="n">
-        <v>2078</v>
+        <v>398</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2078</v>
+        <v>398</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>72588</v>
+        <v>18796</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>72588</v>
+        <v>18796</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>128988</v>
+        <v>10398</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>117.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>140.4%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>114388</v>
+        <v>-4202</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>110000</v>
       </c>
       <c r="D48" t="n">
-        <v>53194</v>
+        <v>796</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>53194</v>
+        <v>796</v>
       </c>
     </row>
     <row r="49">
@@ -2071,11 +2071,11 @@
         <v>70000</v>
       </c>
       <c r="D49" t="n">
-        <v>5796</v>
+        <v>398</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2083,11 +2083,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>301.5%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>4596</v>
+        <v>-802</v>
       </c>
     </row>
     <row r="50">
@@ -2105,11 +2105,11 @@
         <v>160000</v>
       </c>
       <c r="D50" t="n">
-        <v>74258.25</v>
+        <v>53666.25</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>74258.25</v>
+        <v>53666.25</v>
       </c>
     </row>
     <row r="51">
@@ -2139,11 +2139,11 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>45048.5</v>
+        <v>23523.89</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2151,11 +2151,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>33448.5</v>
+        <v>11923.89</v>
       </c>
     </row>
     <row r="52">
@@ -2173,11 +2173,11 @@
         <v>160000</v>
       </c>
       <c r="D52" t="n">
-        <v>47773.05</v>
+        <v>48399.05</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>47773.05</v>
+        <v>48399.05</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>110000</v>
       </c>
       <c r="D53" t="n">
-        <v>44298</v>
+        <v>7998</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>44298</v>
+        <v>7998</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>58372.7</v>
+        <v>48472.7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>58372.7</v>
+        <v>48472.7</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>150000</v>
       </c>
       <c r="D55" t="n">
-        <v>34098</v>
+        <v>12598</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>34098</v>
+        <v>12598</v>
       </c>
     </row>
     <row r="56">
@@ -2309,11 +2309,11 @@
         <v>90000</v>
       </c>
       <c r="D56" t="n">
-        <v>91394</v>
+        <v>33598</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>101.5%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>91394</v>
+        <v>33598</v>
       </c>
     </row>
     <row r="57">
@@ -2343,11 +2343,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>66192</v>
+        <v>25198</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2355,11 +2355,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>64512</v>
+        <v>23518</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>80000</v>
       </c>
       <c r="D58" t="n">
-        <v>41592</v>
+        <v>10398</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>41592</v>
+        <v>10398</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>86794</v>
+        <v>10398</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>124.0%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>85794</v>
+        <v>9398</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>62590</v>
+        <v>24194</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>125.2%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2457,11 +2457,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>55990</v>
+        <v>17594</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>30000</v>
       </c>
       <c r="D61" t="n">
-        <v>20398</v>
+        <v>398</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>20398</v>
+        <v>398</v>
       </c>
     </row>
     <row r="62">
@@ -2547,11 +2547,11 @@
         <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>53588</v>
+        <v>10398</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>48188</v>
+        <v>4998</v>
       </c>
     </row>
     <row r="64">
@@ -2581,11 +2581,11 @@
         <v>50000</v>
       </c>
       <c r="D64" t="n">
-        <v>1194</v>
+        <v>398</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1194</v>
+        <v>398</v>
       </c>
     </row>
     <row r="65">
@@ -2615,11 +2615,11 @@
         <v>50000</v>
       </c>
       <c r="D65" t="n">
-        <v>10000</v>
+        <v>996</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>10000</v>
+        <v>996</v>
       </c>
     </row>
     <row r="66">
@@ -2649,11 +2649,11 @@
         <v>40000</v>
       </c>
       <c r="D66" t="n">
-        <v>11992</v>
+        <v>0</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>11992</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>58192</v>
+        <v>129562</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>58192</v>
+        <v>129562</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>63386</v>
+        <v>463886</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>132.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-4894</v>
+        <v>395606</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>41796</v>
+        <v>143864</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>102.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -553,11 +553,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>33996</v>
+        <v>136064</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>140000</v>
       </c>
       <c r="D5" t="n">
-        <v>30300</v>
+        <v>90998</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28620</v>
+        <v>89318</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>17794</v>
+        <v>56186</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -621,11 +621,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>125.9%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-4606</v>
+        <v>33786</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>140000</v>
       </c>
       <c r="D7" t="n">
-        <v>10398</v>
+        <v>26998</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10398</v>
+        <v>26998</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>28592</v>
+        <v>89880</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>26912</v>
+        <v>88200</v>
       </c>
     </row>
     <row r="9">
@@ -745,11 +745,11 @@
         <v>140000</v>
       </c>
       <c r="D10" t="n">
-        <v>20398</v>
+        <v>21592</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>17398</v>
+        <v>18592</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>796</v>
+        <v>9968</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>125.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-202</v>
+        <v>8970</v>
       </c>
     </row>
     <row r="13">
@@ -881,11 +881,11 @@
         <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>38204.55</v>
+        <v>58602.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>38204.55</v>
+        <v>58602.55</v>
       </c>
     </row>
     <row r="15">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>101161</v>
+        <v>128159</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>101161</v>
+        <v>128159</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>1625.76</v>
+        <v>42513.76</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1227.76</v>
+        <v>42115.76</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>32489.04</v>
+        <v>76081.04000000001</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>31693.04</v>
+        <v>75285.04000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>598</v>
+        <v>4388</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1672.2%</t>
+          <t>227.9%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>-9402</v>
+        <v>-5612</v>
       </c>
     </row>
     <row r="26">
@@ -1289,11 +1289,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>1394</v>
+        <v>2390</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1394</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>70000</v>
       </c>
       <c r="D27" t="n">
-        <v>10796</v>
+        <v>22592</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>10796</v>
+        <v>22592</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>5548</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>5548</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>85567.82000000001</v>
+        <v>166961.82</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>85567.82000000001</v>
+        <v>166961.82</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>130000</v>
       </c>
       <c r="D30" t="n">
-        <v>19500</v>
+        <v>28800</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5000</v>
+        <v>14300</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>19940.5</v>
+        <v>71036.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>10440.5</v>
+        <v>61536.5</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>115000</v>
       </c>
       <c r="D32" t="n">
-        <v>5707.68</v>
+        <v>36603.68</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5707.68</v>
+        <v>36603.68</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>125000</v>
       </c>
       <c r="D33" t="n">
-        <v>14336.6</v>
+        <v>32130.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5836.6</v>
+        <v>23630.6</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>65000</v>
       </c>
       <c r="D34" t="n">
-        <v>798</v>
+        <v>21196</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>798</v>
+        <v>21196</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>36035.3</v>
+        <v>70823.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1680.300000000003</v>
+        <v>36468.3</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>150000</v>
       </c>
       <c r="D36" t="n">
-        <v>2477.8</v>
+        <v>3273.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>403.6%</t>
+          <t>305.5%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>-7522.2</v>
+        <v>-6726.2</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>100000</v>
       </c>
       <c r="D37" t="n">
-        <v>13177.01</v>
+        <v>33575.00999999999</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1675,11 +1675,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>9217.01</v>
+        <v>29615.00999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1833,11 +1833,11 @@
         <v>70000</v>
       </c>
       <c r="D42" t="n">
-        <v>20476</v>
+        <v>22074</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>13392.67</v>
+        <v>14990.67</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>110000</v>
       </c>
       <c r="D43" t="n">
-        <v>7918.8</v>
+        <v>29598.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>7918.8</v>
+        <v>29598.8</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>50000</v>
       </c>
       <c r="D44" t="n">
-        <v>398</v>
+        <v>9792</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>398</v>
+        <v>9792</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>30000</v>
       </c>
       <c r="D45" t="n">
-        <v>398</v>
+        <v>2078</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>398</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>18796</v>
+        <v>72986</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>18796</v>
+        <v>72986</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>10398</v>
+        <v>128988</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>117.3%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>140.4%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>-4202</v>
+        <v>114388</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>110000</v>
       </c>
       <c r="D48" t="n">
-        <v>796</v>
+        <v>53194</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>796</v>
+        <v>53194</v>
       </c>
     </row>
     <row r="49">
@@ -2071,11 +2071,11 @@
         <v>70000</v>
       </c>
       <c r="D49" t="n">
-        <v>398</v>
+        <v>6194</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2083,11 +2083,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>301.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>-802</v>
+        <v>4994</v>
       </c>
     </row>
     <row r="50">
@@ -2105,11 +2105,11 @@
         <v>160000</v>
       </c>
       <c r="D50" t="n">
-        <v>53666.25</v>
+        <v>74656.25</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>53666.25</v>
+        <v>74656.25</v>
       </c>
     </row>
     <row r="51">
@@ -2139,11 +2139,11 @@
         <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>23523.89</v>
+        <v>55115.89</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2151,11 +2151,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>11923.89</v>
+        <v>43515.89</v>
       </c>
     </row>
     <row r="52">
@@ -2173,11 +2173,11 @@
         <v>160000</v>
       </c>
       <c r="D52" t="n">
-        <v>48399.05</v>
+        <v>74593.05</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>48399.05</v>
+        <v>74593.05</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>110000</v>
       </c>
       <c r="D53" t="n">
-        <v>7998</v>
+        <v>44696</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>7998</v>
+        <v>44696</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>48472.7</v>
+        <v>66672.7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>48472.7</v>
+        <v>66672.7</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>150000</v>
       </c>
       <c r="D55" t="n">
-        <v>12598</v>
+        <v>34898</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>12598</v>
+        <v>34898</v>
       </c>
     </row>
     <row r="56">
@@ -2309,11 +2309,11 @@
         <v>90000</v>
       </c>
       <c r="D56" t="n">
-        <v>33598</v>
+        <v>104594</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>33598</v>
+        <v>104594</v>
       </c>
     </row>
     <row r="57">
@@ -2343,11 +2343,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>25198</v>
+        <v>66192</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2355,11 +2355,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>23518</v>
+        <v>64512</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>80000</v>
       </c>
       <c r="D58" t="n">
-        <v>10398</v>
+        <v>41592</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>10398</v>
+        <v>41592</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>10398</v>
+        <v>86794</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>9398</v>
+        <v>85794</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>24194</v>
+        <v>62988</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>126.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2457,11 +2457,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>17594</v>
+        <v>56388</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>30000</v>
       </c>
       <c r="D61" t="n">
-        <v>398</v>
+        <v>20398</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>398</v>
+        <v>20398</v>
       </c>
     </row>
     <row r="62">
@@ -2547,11 +2547,11 @@
         <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>10398</v>
+        <v>63588</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4998</v>
+        <v>58188</v>
       </c>
     </row>
     <row r="64">
@@ -2581,11 +2581,11 @@
         <v>50000</v>
       </c>
       <c r="D64" t="n">
-        <v>398</v>
+        <v>1194</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>398</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="65">
@@ -2615,11 +2615,11 @@
         <v>50000</v>
       </c>
       <c r="D65" t="n">
-        <v>996</v>
+        <v>10996</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>996</v>
+        <v>10996</v>
       </c>
     </row>
     <row r="66">
@@ -2649,11 +2649,11 @@
         <v>40000</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>11992</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>11992</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -549,15 +549,15 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7800</v>
+        <v>14400</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>136064</v>
+        <v>129464</v>
       </c>
     </row>
     <row r="5">
@@ -821,15 +821,15 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>998</v>
+        <v>5998</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8970</v>
+        <v>3970</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>35745.67000000016</v>
+        <v>50477.67000000016</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>35745.67000000016</v>
+        <v>50477.67000000016</v>
       </c>
     </row>
     <row r="14">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>159280.29</v>
+        <v>169523.29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>159280.29</v>
+        <v>169523.29</v>
       </c>
     </row>
     <row r="16">
@@ -1017,11 +1017,11 @@
         <v>90000</v>
       </c>
       <c r="D18" t="n">
-        <v>3590</v>
+        <v>5090</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3590</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="19">
@@ -1085,11 +1085,11 @@
         <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>184289.6</v>
+        <v>185725.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>184289.6</v>
+        <v>185725.6</v>
       </c>
     </row>
     <row r="21">
@@ -1187,11 +1187,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>42513.76</v>
+        <v>42764.36</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>42115.76</v>
+        <v>42366.36</v>
       </c>
     </row>
     <row r="24">
@@ -1663,7 +1663,7 @@
         <v>100000</v>
       </c>
       <c r="D37" t="n">
-        <v>33575.00999999999</v>
+        <v>33593.77</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>29615.00999999999</v>
+        <v>29633.77</v>
       </c>
     </row>
     <row r="38">
@@ -1731,11 +1731,11 @@
         <v>200000</v>
       </c>
       <c r="D39" t="n">
-        <v>13176</v>
+        <v>2578</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1743,11 +1743,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>151.8%</t>
+          <t>775.8%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>-6824</v>
+        <v>-17422</v>
       </c>
     </row>
     <row r="40">
@@ -1867,23 +1867,23 @@
         <v>110000</v>
       </c>
       <c r="D43" t="n">
-        <v>29598.8</v>
+        <v>29474</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>22800</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>29598.8</v>
+        <v>6674</v>
       </c>
     </row>
     <row r="44">
@@ -2105,11 +2105,11 @@
         <v>160000</v>
       </c>
       <c r="D50" t="n">
-        <v>74656.25</v>
+        <v>75069.04000000001</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>74656.25</v>
+        <v>75069.04000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2513,11 +2513,11 @@
         <v>70000</v>
       </c>
       <c r="D62" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>129562</v>
+        <v>130562</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>129562</v>
+        <v>130562</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>463886</v>
+        <v>490524</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>132.5%</t>
+          <t>140.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>395606</v>
+        <v>422244</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>143864</v>
+        <v>124064</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>102.8%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -553,11 +553,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>129464</v>
+        <v>109664</v>
       </c>
     </row>
     <row r="5">
@@ -609,11 +609,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>56186</v>
+        <v>66584</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -621,11 +621,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>33786</v>
+        <v>44184</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>140000</v>
       </c>
       <c r="D7" t="n">
-        <v>26998</v>
+        <v>27396</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>26998</v>
+        <v>27396</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>89880</v>
+        <v>101880</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>88200</v>
+        <v>100200</v>
       </c>
     </row>
     <row r="9">
@@ -745,11 +745,11 @@
         <v>140000</v>
       </c>
       <c r="D10" t="n">
-        <v>21592</v>
+        <v>21990</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>18592</v>
+        <v>18990</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>9968</v>
+        <v>20366</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3970</v>
+        <v>14368</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>50477.67000000016</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>50477.67000000016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>58602.55</v>
+        <v>20398</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>58602.55</v>
+        <v>20398</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>169523.29</v>
+        <v>796</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>169523.29</v>
+        <v>796</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>140448.3</v>
+        <v>2132</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>140448.3</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>196025.61</v>
+        <v>0</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>196025.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>90000</v>
       </c>
       <c r="D18" t="n">
-        <v>5090</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5090</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>90000</v>
       </c>
       <c r="D19" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>185725.6</v>
+        <v>0</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>185725.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>95706</v>
+        <v>10000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>95706</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>128159</v>
+        <v>36998</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>128159</v>
+        <v>36998</v>
       </c>
     </row>
     <row r="23">
@@ -1195,15 +1195,15 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>398</v>
+        <v>9398</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>42366.36</v>
+        <v>33366.36</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>76081.04000000001</v>
+        <v>88179.03999999999</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>75285.04000000001</v>
+        <v>87383.03999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1263,15 +1263,15 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10000</v>
+        <v>16400</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>227.9%</t>
+          <t>373.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>-5612</v>
+        <v>-12012</v>
       </c>
     </row>
     <row r="26">
@@ -1289,11 +1289,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>2390</v>
+        <v>22190</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2390</v>
+        <v>22190</v>
       </c>
     </row>
     <row r="27">
@@ -1379,567 +1379,567 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>陈磊</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="D29" t="n">
-        <v>166961.82</v>
+        <v>171510</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>3960</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>166961.82</v>
+        <v>167550</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>田奇</t>
+          <t>胡炫明</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>130000</v>
+        <v>200000</v>
       </c>
       <c r="D30" t="n">
-        <v>28800</v>
+        <v>398820</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>199.4%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>14500</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>14300</v>
+        <v>398820</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>李明</t>
+          <t>何晨</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>115000</v>
+        <v>200000</v>
       </c>
       <c r="D31" t="n">
-        <v>71036.5</v>
+        <v>5390</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>9500</v>
+        <v>6960</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>129.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>61536.5</v>
+        <v>-1570</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>苏怡意</t>
+          <t>徐艳霞</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>115000</v>
+        <v>200000</v>
       </c>
       <c r="D32" t="n">
-        <v>36603.68</v>
+        <v>277500</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>138.8%</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>112250</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>36603.68</v>
+        <v>165250</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>姜玮</t>
+          <t>高丹</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>125000</v>
+        <v>250000</v>
       </c>
       <c r="D33" t="n">
-        <v>32130.6</v>
+        <v>66320</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>8500</v>
+        <v>1980</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>23630.6</v>
+        <v>64340</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>李家慧</t>
+          <t>胡威特</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>65000</v>
+        <v>250000</v>
       </c>
       <c r="D34" t="n">
-        <v>21196</v>
+        <v>105540</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21196</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>邓璐</t>
+          <t>张佳慧</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="D35" t="n">
-        <v>70823.3</v>
+        <v>99600</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>34355</v>
+        <v>180</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>36468.3</v>
+        <v>99420</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>马雅丽</t>
+          <t>章浩进</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="D36" t="n">
-        <v>3273.8</v>
+        <v>57900</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>305.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>-6726.2</v>
+        <v>57900</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>袁登玉</t>
+          <t>马小辉</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="D37" t="n">
-        <v>33593.77</v>
+        <v>12160</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3960</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>29633.77</v>
+        <v>12160</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>黄惠作</t>
+          <t>陈智超</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>53760</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>27920</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>25840</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>韦新妮</t>
+          <t>唐苏媛</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="D39" t="n">
-        <v>2578</v>
+        <v>19980</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>20000</v>
+        <v>3510</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>775.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>-17422</v>
+        <v>16470</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>郭海明</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="D40" t="n">
-        <v>50318</v>
+        <v>177459.02</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>48338</v>
+        <v>177459.02</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>杨琴</t>
+          <t>田奇</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>150000</v>
+        <v>130000</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>60300</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1980</v>
+        <v>14500</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>-1980</v>
+        <v>45800</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>陈新星</t>
+          <t>李明</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>70000</v>
+        <v>115000</v>
       </c>
       <c r="D42" t="n">
-        <v>22074</v>
+        <v>71596.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>7083.33</v>
+        <v>9500</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>14990.67</v>
+        <v>62096.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>田婉丽</t>
+          <t>苏怡意</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>110000</v>
+        <v>115000</v>
       </c>
       <c r="D43" t="n">
-        <v>29474</v>
+        <v>41295.68</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>22800</v>
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6674</v>
+        <v>41295.68</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>罗晗</t>
+          <t>姜玮</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>50000</v>
+        <v>125000</v>
       </c>
       <c r="D44" t="n">
-        <v>9792</v>
+        <v>42808.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>9792</v>
+        <v>34308.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>陈思羽</t>
+          <t>李家慧</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>30000</v>
+        <v>65000</v>
       </c>
       <c r="D45" t="n">
-        <v>2078</v>
+        <v>33794</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,335 +1951,335 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2078</v>
+        <v>33794</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>邓璐</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>110000</v>
+        <v>150000</v>
       </c>
       <c r="D46" t="n">
-        <v>72986</v>
+        <v>70823.3</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>34355</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>72986</v>
+        <v>36468.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>马雅丽</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>110000</v>
+        <v>150000</v>
       </c>
       <c r="D47" t="n">
-        <v>128988</v>
+        <v>3273.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>117.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>14600</v>
+        <v>10000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>305.5%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>114388</v>
+        <v>-6726.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>朱碧丹</t>
+          <t>袁登玉</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>110000</v>
+        <v>100000</v>
       </c>
       <c r="D48" t="n">
-        <v>53194</v>
+        <v>35987.77</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>3960</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>53194</v>
+        <v>32027.77</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>王钰尧</t>
+          <t>黄惠作</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>70000</v>
+        <v>200000</v>
       </c>
       <c r="D49" t="n">
-        <v>6194</v>
+        <v>0</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>4994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>孙君兰</t>
+          <t>韦新妮</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="D50" t="n">
-        <v>75069.04000000001</v>
+        <v>89114</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>75069.04000000001</v>
+        <v>69114</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>陈紫灵</t>
+          <t>郭海明</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="D51" t="n">
-        <v>55115.89</v>
+        <v>60352</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>11600</v>
+        <v>3960</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>43515.89</v>
+        <v>56392</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>林非凡</t>
+          <t>杨琴</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>160000</v>
+        <v>150000</v>
       </c>
       <c r="D52" t="n">
-        <v>74593.05</v>
+        <v>2378</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>74593.05</v>
+        <v>398</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>米兰兰</t>
+          <t>陈新星</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>110000</v>
+        <v>70000</v>
       </c>
       <c r="D53" t="n">
-        <v>44696</v>
+        <v>22074</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>19083.33</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>44696</v>
+        <v>2990.669999999998</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>田婉丽</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>66672.7</v>
+        <v>37598.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>34.2%</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>22800</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>60.6%</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="H54" t="n">
-        <v>66672.7</v>
+        <v>14798.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>朱锋剑</t>
+          <t>罗晗</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>150000</v>
+        <v>50000</v>
       </c>
       <c r="D55" t="n">
-        <v>34898</v>
+        <v>9792</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,29 +2291,29 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>34898</v>
+        <v>9792</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>陈思羽</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>90000</v>
+        <v>30000</v>
       </c>
       <c r="D56" t="n">
-        <v>104594</v>
+        <v>2078</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,165 +2325,165 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>104594</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>谌黎平</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>80000</v>
+        <v>110000</v>
       </c>
       <c r="D57" t="n">
-        <v>66192</v>
+        <v>72986</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>64512</v>
+        <v>72986</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>马春兰</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>80000</v>
+        <v>110000</v>
       </c>
       <c r="D58" t="n">
-        <v>41592</v>
+        <v>128988</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>117.3%</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>14600</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>41592</v>
+        <v>114388</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>李颜君</t>
+          <t>朱碧丹</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>70000</v>
+        <v>110000</v>
       </c>
       <c r="D59" t="n">
-        <v>86794</v>
+        <v>53194</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>124.0%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>85794</v>
+        <v>53194</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>蔡清霞</t>
+          <t>王钰尧</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>50000</v>
+        <v>70000</v>
       </c>
       <c r="D60" t="n">
-        <v>62988</v>
+        <v>7694</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>126.0%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>6600</v>
+        <v>1200</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>56388</v>
+        <v>6494</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>吴静文</t>
+          <t>孙君兰</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>30000</v>
+        <v>160000</v>
       </c>
       <c r="D61" t="n">
-        <v>20398</v>
+        <v>75069.04000000001</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,97 +2495,97 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>20398</v>
+        <v>75069.04000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>陈月娇</t>
+          <t>陈紫灵</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>70000</v>
+        <v>160000</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>55115.89</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>11600</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>43515.89</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>林非凡</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>170000</v>
+        <v>160000</v>
       </c>
       <c r="D63" t="n">
-        <v>63588</v>
+        <v>74593.05</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>58188</v>
+        <v>74593.05</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>杨红瑞</t>
+          <t>米兰兰</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>50000</v>
+        <v>110000</v>
       </c>
       <c r="D64" t="n">
-        <v>1194</v>
+        <v>47796</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2597,29 +2597,29 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1194</v>
+        <v>47796</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>普元媛</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>50000</v>
+        <v>110000</v>
       </c>
       <c r="D65" t="n">
-        <v>10996</v>
+        <v>69772.7</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2631,40 +2631,414 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>10996</v>
+        <v>69772.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>朱锋剑</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D66" t="n">
+        <v>42398</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>28.3%</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>42398</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>陈静</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>90000</v>
+      </c>
+      <c r="D67" t="n">
+        <v>104594</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>116.2%</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>102594</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>谌黎平</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D68" t="n">
+        <v>66192</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>82.7%</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1680</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>64512</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>马春兰</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D69" t="n">
+        <v>43588</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>43588</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>李颜君</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>70000</v>
+      </c>
+      <c r="D70" t="n">
+        <v>87192</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>124.6%</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1.1%</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>86192</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>蔡清霞</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D71" t="n">
+        <v>82988</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>166.0%</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>6600</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>8.0%</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>76388</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>吴静文</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D72" t="n">
+        <v>20796</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>69.3%</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>20796</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>昆明</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>陈月娇</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>70000</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>刘玉静</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>170000</v>
+      </c>
+      <c r="D74" t="n">
+        <v>98384</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>57.9%</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>5400</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>5.5%</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>92984</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>杨红瑞</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1194</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>普元媛</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D76" t="n">
+        <v>23792</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>23792</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
         <is>
           <t>马奇君</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="C77" t="n">
         <v>40000</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D77" t="n">
         <v>11992</v>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>30.0%</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
         <v>11992</v>
       </c>
     </row>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>130562</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>130562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>490524</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>140.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>68280</v>
+        <v>72280</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>422244</v>
+        <v>-72280</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>124064</v>
+        <v>21200</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -553,11 +553,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>109664</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>140000</v>
       </c>
       <c r="D5" t="n">
-        <v>90998</v>
+        <v>300</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>560.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>89318</v>
+        <v>-1380</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>66584</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -621,11 +621,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>44184</v>
+        <v>-22400</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>140000</v>
       </c>
       <c r="D7" t="n">
-        <v>27396</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>27396</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>101880</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>100200</v>
+        <v>-1680</v>
       </c>
     </row>
     <row r="9">
@@ -745,11 +745,11 @@
         <v>140000</v>
       </c>
       <c r="D10" t="n">
-        <v>21990</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>18990</v>
+        <v>-3000</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>20366</v>
+        <v>600</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>999.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>14368</v>
+        <v>-5398</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>74998.47000000009</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>74998.47000000009</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>20398</v>
+        <v>38204.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>20398</v>
+        <v>38204.55</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>796</v>
+        <v>190639.29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>796</v>
+        <v>190639.29</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>2132</v>
+        <v>158036.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2132</v>
+        <v>158036.3</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>196025.61</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>196025.61</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>90000</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>5090</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>90000</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>245315.8800000001</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>245315.8800000001</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>10000</v>
+        <v>105286</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10000</v>
+        <v>105286</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>36998</v>
+        <v>87308</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>36998</v>
+        <v>87308</v>
       </c>
     </row>
     <row r="23">
@@ -1187,23 +1187,23 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>42764.36</v>
+        <v>11074.36</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>9398</v>
+        <v>19796</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>178.8%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>33366.36</v>
+        <v>-8721.639999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>88179.03999999999</v>
+        <v>30493.04</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>87383.03999999999</v>
+        <v>29697.04</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>4388</v>
+        <v>0</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>373.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>-12012</v>
+        <v>-16400</v>
       </c>
     </row>
     <row r="26">
@@ -1289,15 +1289,15 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>22190</v>
+        <v>0</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>22190</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>70000</v>
       </c>
       <c r="D27" t="n">
-        <v>22592</v>
+        <v>0</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>22592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>5548</v>
+        <v>0</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>200000</v>
       </c>
       <c r="D29" t="n">
-        <v>171510</v>
+        <v>0</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>167550</v>
+        <v>-3960</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>200000</v>
       </c>
       <c r="D30" t="n">
-        <v>398820</v>
+        <v>0</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>199.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>398820</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>200000</v>
       </c>
       <c r="D31" t="n">
-        <v>5390</v>
+        <v>0</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>129.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>-1570</v>
+        <v>-6960</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>200000</v>
       </c>
       <c r="D32" t="n">
-        <v>277500</v>
+        <v>0</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>138.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>165250</v>
+        <v>-112250</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>250000</v>
       </c>
       <c r="D33" t="n">
-        <v>66320</v>
+        <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>64340</v>
+        <v>-1980</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>250000</v>
       </c>
       <c r="D34" t="n">
-        <v>105540</v>
+        <v>49800</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1573,11 +1573,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>200.8%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>5540</v>
+        <v>-50200</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>250000</v>
       </c>
       <c r="D35" t="n">
-        <v>99600</v>
+        <v>0</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>99420</v>
+        <v>-180</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>250000</v>
       </c>
       <c r="D36" t="n">
-        <v>57900</v>
+        <v>0</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>57900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>250000</v>
       </c>
       <c r="D37" t="n">
-        <v>12160</v>
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>12160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1697,11 +1697,11 @@
         <v>250000</v>
       </c>
       <c r="D38" t="n">
-        <v>53760</v>
+        <v>0</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1709,11 +1709,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>25840</v>
+        <v>-27920</v>
       </c>
     </row>
     <row r="39">
@@ -1731,11 +1731,11 @@
         <v>250000</v>
       </c>
       <c r="D39" t="n">
-        <v>19980</v>
+        <v>0</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1743,11 +1743,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>16470</v>
+        <v>-3510</v>
       </c>
     </row>
     <row r="40">
@@ -1765,11 +1765,11 @@
         <v>250000</v>
       </c>
       <c r="D40" t="n">
-        <v>177459.02</v>
+        <v>7673.02</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>177459.02</v>
+        <v>7673.02</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>130000</v>
       </c>
       <c r="D41" t="n">
-        <v>60300</v>
+        <v>0</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1811,11 +1811,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>45800</v>
+        <v>-14500</v>
       </c>
     </row>
     <row r="42">
@@ -1833,11 +1833,11 @@
         <v>115000</v>
       </c>
       <c r="D42" t="n">
-        <v>71596.3</v>
+        <v>1000.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>949.7%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>62096.3</v>
+        <v>-8499.700000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>115000</v>
       </c>
       <c r="D43" t="n">
-        <v>41295.68</v>
+        <v>2209.68</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>41295.68</v>
+        <v>2209.68</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>125000</v>
       </c>
       <c r="D44" t="n">
-        <v>42808.2</v>
+        <v>3422.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1913,11 +1913,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>248.4%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>34308.2</v>
+        <v>-5077.799999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>65000</v>
       </c>
       <c r="D45" t="n">
-        <v>33794</v>
+        <v>400</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>33794</v>
+        <v>400</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>150000</v>
       </c>
       <c r="D46" t="n">
-        <v>70823.3</v>
+        <v>9843.300000000001</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1981,11 +1981,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>349.0%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>36468.3</v>
+        <v>-24511.7</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>150000</v>
       </c>
       <c r="D47" t="n">
-        <v>3273.8</v>
+        <v>2477.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>305.5%</t>
+          <t>403.6%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>-6726.2</v>
+        <v>-7522.2</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>100000</v>
       </c>
       <c r="D48" t="n">
-        <v>35987.77</v>
+        <v>2199.76</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2049,11 +2049,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>180.0%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>32027.77</v>
+        <v>-1760.24</v>
       </c>
     </row>
     <row r="49">
@@ -2105,11 +2105,11 @@
         <v>200000</v>
       </c>
       <c r="D50" t="n">
-        <v>89114</v>
+        <v>0</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2117,11 +2117,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>69114</v>
+        <v>-20000</v>
       </c>
     </row>
     <row r="51">
@@ -2139,23 +2139,23 @@
         <v>200000</v>
       </c>
       <c r="D51" t="n">
-        <v>60352</v>
+        <v>1980</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3960</v>
+        <v>5940</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>56392</v>
+        <v>-3960</v>
       </c>
     </row>
     <row r="52">
@@ -2173,11 +2173,11 @@
         <v>150000</v>
       </c>
       <c r="D52" t="n">
-        <v>2378</v>
+        <v>0</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2185,11 +2185,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>398</v>
+        <v>-1980</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>70000</v>
       </c>
       <c r="D53" t="n">
-        <v>22074</v>
+        <v>0</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2219,11 +2219,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2990.669999999998</v>
+        <v>-19083.33</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>37598.8</v>
+        <v>0</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2253,11 +2253,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>14798.8</v>
+        <v>-22800</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>50000</v>
       </c>
       <c r="D55" t="n">
-        <v>9792</v>
+        <v>0</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>9792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2309,11 +2309,11 @@
         <v>30000</v>
       </c>
       <c r="D56" t="n">
-        <v>2078</v>
+        <v>0</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2078</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2343,11 +2343,11 @@
         <v>110000</v>
       </c>
       <c r="D57" t="n">
-        <v>72986</v>
+        <v>0</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>72986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>110000</v>
       </c>
       <c r="D58" t="n">
-        <v>128988</v>
+        <v>0</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>117.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>114388</v>
+        <v>-14600</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>110000</v>
       </c>
       <c r="D59" t="n">
-        <v>53194</v>
+        <v>0</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>53194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>70000</v>
       </c>
       <c r="D60" t="n">
-        <v>7694</v>
+        <v>0</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2457,11 +2457,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>6494</v>
+        <v>-1200</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>160000</v>
       </c>
       <c r="D61" t="n">
-        <v>75069.04000000001</v>
+        <v>13885.04</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>75069.04000000001</v>
+        <v>13885.04</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>160000</v>
       </c>
       <c r="D62" t="n">
-        <v>55115.89</v>
+        <v>13125.89</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>43515.89</v>
+        <v>1525.889999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>160000</v>
       </c>
       <c r="D63" t="n">
-        <v>74593.05</v>
+        <v>21181.05</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>74593.05</v>
+        <v>21181.05</v>
       </c>
     </row>
     <row r="64">
@@ -2581,11 +2581,11 @@
         <v>110000</v>
       </c>
       <c r="D64" t="n">
-        <v>47796</v>
+        <v>500</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>47796</v>
+        <v>500</v>
       </c>
     </row>
     <row r="65">
@@ -2615,23 +2615,23 @@
         <v>110000</v>
       </c>
       <c r="D65" t="n">
-        <v>69772.7</v>
+        <v>272.7</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9094.2%</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>69772.7</v>
+        <v>-24527.3</v>
       </c>
     </row>
     <row r="66">
@@ -2649,11 +2649,11 @@
         <v>150000</v>
       </c>
       <c r="D66" t="n">
-        <v>42398</v>
+        <v>0</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>42398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2683,11 +2683,11 @@
         <v>90000</v>
       </c>
       <c r="D67" t="n">
-        <v>104594</v>
+        <v>0</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2695,11 +2695,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>102594</v>
+        <v>-2000</v>
       </c>
     </row>
     <row r="68">
@@ -2717,11 +2717,11 @@
         <v>80000</v>
       </c>
       <c r="D68" t="n">
-        <v>66192</v>
+        <v>0</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2729,11 +2729,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>64512</v>
+        <v>-1680</v>
       </c>
     </row>
     <row r="69">
@@ -2751,11 +2751,11 @@
         <v>80000</v>
       </c>
       <c r="D69" t="n">
-        <v>43588</v>
+        <v>0</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>43588</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2785,11 +2785,11 @@
         <v>70000</v>
       </c>
       <c r="D70" t="n">
-        <v>87192</v>
+        <v>0</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>124.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2797,11 +2797,11 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>86192</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="71">
@@ -2819,11 +2819,11 @@
         <v>50000</v>
       </c>
       <c r="D71" t="n">
-        <v>82988</v>
+        <v>0</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>166.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2831,11 +2831,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>76388</v>
+        <v>-6600</v>
       </c>
     </row>
     <row r="72">
@@ -2853,11 +2853,11 @@
         <v>30000</v>
       </c>
       <c r="D72" t="n">
-        <v>20796</v>
+        <v>0</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>20796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2921,11 +2921,11 @@
         <v>170000</v>
       </c>
       <c r="D74" t="n">
-        <v>98384</v>
+        <v>0</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2933,11 +2933,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>92984</v>
+        <v>-5400</v>
       </c>
     </row>
     <row r="75">
@@ -2955,11 +2955,11 @@
         <v>50000</v>
       </c>
       <c r="D75" t="n">
-        <v>1194</v>
+        <v>0</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2989,11 +2989,11 @@
         <v>50000</v>
       </c>
       <c r="D76" t="n">
-        <v>23792</v>
+        <v>0</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>23792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -3023,11 +3023,11 @@
         <v>40000</v>
       </c>
       <c r="D77" t="n">
-        <v>11992</v>
+        <v>0</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>11992</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>140562</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>140562</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>508504</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>145.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-72280</v>
+        <v>436224</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>21200</v>
+        <v>124064</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -553,11 +553,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6800</v>
+        <v>109664</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>140000</v>
       </c>
       <c r="D5" t="n">
-        <v>300</v>
+        <v>90998</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>560.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-1380</v>
+        <v>89318</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>66584</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -621,11 +621,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-22400</v>
+        <v>44184</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>140000</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>27396</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>27396</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>102278</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-1680</v>
+        <v>100598</v>
       </c>
     </row>
     <row r="9">
@@ -745,11 +745,11 @@
         <v>140000</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>24068</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-3000</v>
+        <v>21068</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>600</v>
+        <v>30366</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>999.7%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-5398</v>
+        <v>24368</v>
       </c>
     </row>
     <row r="13">
@@ -881,11 +881,11 @@
         <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>38204.55</v>
+        <v>58602.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>38204.55</v>
+        <v>58602.55</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>190639.29</v>
+        <v>191435.29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>190639.29</v>
+        <v>191435.29</v>
       </c>
     </row>
     <row r="16">
@@ -1119,11 +1119,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>105286</v>
+        <v>115286</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>105286</v>
+        <v>115286</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>87308</v>
+        <v>125986</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>87308</v>
+        <v>125986</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>11074.36</v>
+        <v>42764.36</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>178.8%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>-8721.639999999999</v>
+        <v>22968.36</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>30493.04</v>
+        <v>88179.03999999999</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>29697.04</v>
+        <v>87383.03999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>4388</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>373.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>-16400</v>
+        <v>-12012</v>
       </c>
     </row>
     <row r="26">
@@ -1289,11 +1289,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>22190</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>-10000</v>
+        <v>12190</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>70000</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>22592</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>22592</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>5548</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>5548</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>200000</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>171510</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>-3960</v>
+        <v>167550</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>200000</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>398820</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>199.4%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>398820</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>200000</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>5390</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>129.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>-6960</v>
+        <v>-1570</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>200000</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>277500</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>138.8%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>-112250</v>
+        <v>165250</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>250000</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>66320</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>-1980</v>
+        <v>64340</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>250000</v>
       </c>
       <c r="D34" t="n">
-        <v>49800</v>
+        <v>105540</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1573,11 +1573,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>200.8%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>-50200</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>250000</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>99600</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1607,11 +1607,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>-180</v>
+        <v>99420</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>250000</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>57900</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>57900</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>250000</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>14140</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>14140</v>
       </c>
     </row>
     <row r="38">
@@ -1697,11 +1697,11 @@
         <v>250000</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>53760</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1709,11 +1709,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>-27920</v>
+        <v>25840</v>
       </c>
     </row>
     <row r="39">
@@ -1731,11 +1731,11 @@
         <v>250000</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>19980</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1743,11 +1743,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>-3510</v>
+        <v>16470</v>
       </c>
     </row>
     <row r="40">
@@ -1765,11 +1765,11 @@
         <v>250000</v>
       </c>
       <c r="D40" t="n">
-        <v>7673.02</v>
+        <v>187459.02</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>7673.02</v>
+        <v>187459.02</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>130000</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>60300</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1811,11 +1811,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>-14500</v>
+        <v>45800</v>
       </c>
     </row>
     <row r="42">
@@ -1833,11 +1833,11 @@
         <v>115000</v>
       </c>
       <c r="D42" t="n">
-        <v>1000.3</v>
+        <v>71596.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>949.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>-8499.700000000001</v>
+        <v>62096.3</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>115000</v>
       </c>
       <c r="D43" t="n">
-        <v>2209.68</v>
+        <v>51295.68</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2209.68</v>
+        <v>51295.68</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>125000</v>
       </c>
       <c r="D44" t="n">
-        <v>3422.2</v>
+        <v>52808.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1913,11 +1913,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>248.4%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>-5077.799999999999</v>
+        <v>44308.2</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>65000</v>
       </c>
       <c r="D45" t="n">
-        <v>400</v>
+        <v>33794</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>400</v>
+        <v>33794</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>150000</v>
       </c>
       <c r="D46" t="n">
-        <v>9843.300000000001</v>
+        <v>71221.3</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1981,11 +1981,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>349.0%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>-24511.7</v>
+        <v>36866.3</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>150000</v>
       </c>
       <c r="D47" t="n">
-        <v>2477.8</v>
+        <v>3273.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>403.6%</t>
+          <t>305.5%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>-7522.2</v>
+        <v>-6726.2</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>100000</v>
       </c>
       <c r="D48" t="n">
-        <v>2199.76</v>
+        <v>36385.77</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2049,11 +2049,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>180.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>-1760.24</v>
+        <v>32425.77</v>
       </c>
     </row>
     <row r="49">
@@ -2105,11 +2105,11 @@
         <v>200000</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>89114</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2117,11 +2117,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>-20000</v>
+        <v>69114</v>
       </c>
     </row>
     <row r="51">
@@ -2139,11 +2139,11 @@
         <v>200000</v>
       </c>
       <c r="D51" t="n">
-        <v>1980</v>
+        <v>60750</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2151,11 +2151,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>-3960</v>
+        <v>54810</v>
       </c>
     </row>
     <row r="52">
@@ -2173,11 +2173,11 @@
         <v>150000</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>2378</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2185,11 +2185,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>-1980</v>
+        <v>398</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>70000</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>30074</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2219,11 +2219,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>-19083.33</v>
+        <v>10990.67</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>37996.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2253,11 +2253,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>-22800</v>
+        <v>15196.8</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>50000</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>9792</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>9792</v>
       </c>
     </row>
     <row r="56">
@@ -2309,11 +2309,11 @@
         <v>30000</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>2476</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="57">
@@ -2343,11 +2343,11 @@
         <v>110000</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>72986</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>72986</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>110000</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>128988</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>117.3%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>-14600</v>
+        <v>114388</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>110000</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>53194</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>53194</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>70000</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>7694</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2457,11 +2457,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>-1200</v>
+        <v>6494</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>160000</v>
       </c>
       <c r="D61" t="n">
-        <v>13885.04</v>
+        <v>75069.04000000001</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>13885.04</v>
+        <v>75069.04000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>160000</v>
       </c>
       <c r="D62" t="n">
-        <v>13125.89</v>
+        <v>60513.89</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1525.889999999999</v>
+        <v>48913.89</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>160000</v>
       </c>
       <c r="D63" t="n">
-        <v>21181.05</v>
+        <v>74593.05</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>21181.05</v>
+        <v>74593.05</v>
       </c>
     </row>
     <row r="64">
@@ -2581,11 +2581,11 @@
         <v>110000</v>
       </c>
       <c r="D64" t="n">
-        <v>500</v>
+        <v>47796</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>500</v>
+        <v>47796</v>
       </c>
     </row>
     <row r="65">
@@ -2615,11 +2615,11 @@
         <v>110000</v>
       </c>
       <c r="D65" t="n">
-        <v>272.7</v>
+        <v>85970.7</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2627,11 +2627,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>9094.2%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>-24527.3</v>
+        <v>61170.7</v>
       </c>
     </row>
     <row r="66">
@@ -2649,11 +2649,11 @@
         <v>150000</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>42398</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>42398</v>
       </c>
     </row>
     <row r="67">
@@ -2683,11 +2683,11 @@
         <v>90000</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>104594</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2695,11 +2695,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>-2000</v>
+        <v>102594</v>
       </c>
     </row>
     <row r="68">
@@ -2717,11 +2717,11 @@
         <v>80000</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>66590</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>83.2%</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2729,11 +2729,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>-1680</v>
+        <v>64910</v>
       </c>
     </row>
     <row r="69">
@@ -2751,11 +2751,11 @@
         <v>80000</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>43588</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>43588</v>
       </c>
     </row>
     <row r="70">
@@ -2785,11 +2785,11 @@
         <v>70000</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>87192</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2797,11 +2797,11 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>-1000</v>
+        <v>86192</v>
       </c>
     </row>
     <row r="71">
@@ -2819,11 +2819,11 @@
         <v>50000</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>89986</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>180.0%</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2831,11 +2831,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>-6600</v>
+        <v>83386</v>
       </c>
     </row>
     <row r="72">
@@ -2853,11 +2853,11 @@
         <v>30000</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>20796</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>20796</v>
       </c>
     </row>
     <row r="73">
@@ -2921,11 +2921,11 @@
         <v>170000</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>98782</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2933,11 +2933,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>-5400</v>
+        <v>93382</v>
       </c>
     </row>
     <row r="75">
@@ -2955,11 +2955,11 @@
         <v>50000</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1194</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="76">
@@ -2989,11 +2989,11 @@
         <v>50000</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>23792</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>23792</v>
       </c>
     </row>
     <row r="77">
@@ -3023,11 +3023,11 @@
         <v>40000</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>25192</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>25192</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>芊雅</t>
+          <t>王芊雅</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2064,30 +2064,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>黄惠作</t>
+          <t>黄慧作</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>200000</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>197010</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>98.5%</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>54910</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>142100</v>
       </c>
     </row>
     <row r="50">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -429,12 +429,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>目标</t>
+          <t>目标(元)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>完成(元)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -444,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>本月退费</t>
+          <t>本月退费(元)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>本月净流水</t>
+          <t>本月净流水(元)</t>
         </is>
       </c>
     </row>
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>140562</v>
+        <v>160562</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>100.4%</t>
+          <t>114.7%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>140562</v>
+        <v>160562</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>508504</v>
+        <v>594420</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>145.3%</t>
+          <t>169.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>436224</v>
+        <v>522140</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>124064</v>
+        <v>158464</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>113.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -553,11 +553,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>109664</v>
+        <v>144064</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>140000</v>
       </c>
       <c r="D5" t="n">
-        <v>90998</v>
+        <v>92297.89999999999</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1680</v>
+        <v>3180</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>89318</v>
+        <v>89117.89999999999</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>66584</v>
+        <v>123582</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>88.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -621,11 +621,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>44184</v>
+        <v>101182</v>
       </c>
     </row>
     <row r="7">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>102278</v>
+        <v>122278</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>100598</v>
+        <v>120598</v>
       </c>
     </row>
     <row r="9">
@@ -745,11 +745,11 @@
         <v>140000</v>
       </c>
       <c r="D10" t="n">
-        <v>24068</v>
+        <v>45068</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>21068</v>
+        <v>42068</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>30366</v>
+        <v>50366</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>100.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>24368</v>
+        <v>44368</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>74998.47000000009</v>
+        <v>104277.4700000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>74998.47000000009</v>
+        <v>104277.4700000001</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>58602.55</v>
+        <v>125912.05</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>58602.55</v>
+        <v>125912.05</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>191435.29</v>
+        <v>244343.29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>191435.29</v>
+        <v>244343.29</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>158036.3</v>
+        <v>153595.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>158036.3</v>
+        <v>153595.3</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>196025.61</v>
+        <v>210771.11</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>196025.61</v>
+        <v>210771.11</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>90000</v>
       </c>
       <c r="D18" t="n">
-        <v>5090</v>
+        <v>7694</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5090</v>
+        <v>7694</v>
       </c>
     </row>
     <row r="19">
@@ -1085,11 +1085,11 @@
         <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>245315.8800000001</v>
+        <v>280724.8800000001</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>245315.8800000001</v>
+        <v>280724.8800000001</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>115286</v>
+        <v>119016.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>115286</v>
+        <v>119016.8</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>125986</v>
+        <v>159380</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>125986</v>
+        <v>159380</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>42764.36</v>
+        <v>77164.36</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>22968.36</v>
+        <v>57368.36</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>88179.03999999999</v>
+        <v>125075.68</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>87383.03999999999</v>
+        <v>124279.68</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>4388</v>
+        <v>54986</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>373.7%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>-12012</v>
+        <v>38586</v>
       </c>
     </row>
     <row r="26">
@@ -1289,23 +1289,23 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>22190</v>
+        <v>24568</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10000</v>
+        <v>19000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>12190</v>
+        <v>5568</v>
       </c>
     </row>
     <row r="27">
@@ -1357,11 +1357,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>5548</v>
+        <v>6146</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5548</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>200000</v>
       </c>
       <c r="D29" t="n">
-        <v>171510</v>
+        <v>183450</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>167550</v>
+        <v>179490</v>
       </c>
     </row>
     <row r="30">
@@ -1459,11 +1459,11 @@
         <v>200000</v>
       </c>
       <c r="D31" t="n">
-        <v>5390</v>
+        <v>177350</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>129.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>-1570</v>
+        <v>170390</v>
       </c>
     </row>
     <row r="32">
@@ -1527,11 +1527,11 @@
         <v>250000</v>
       </c>
       <c r="D33" t="n">
-        <v>66320</v>
+        <v>167420</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>64340</v>
+        <v>165440</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>250000</v>
       </c>
       <c r="D34" t="n">
-        <v>105540</v>
+        <v>109500</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1573,11 +1573,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>5540</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="35">
@@ -1663,7 +1663,7 @@
         <v>250000</v>
       </c>
       <c r="D37" t="n">
-        <v>14140</v>
+        <v>14320</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>14140</v>
+        <v>14320</v>
       </c>
     </row>
     <row r="38">
@@ -1765,11 +1765,11 @@
         <v>250000</v>
       </c>
       <c r="D40" t="n">
-        <v>187459.02</v>
+        <v>199405.02</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>187459.02</v>
+        <v>199405.02</v>
       </c>
     </row>
     <row r="41">
@@ -1807,15 +1807,15 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>14500</v>
+        <v>31300</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>45800</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="42">
@@ -1833,11 +1833,11 @@
         <v>115000</v>
       </c>
       <c r="D42" t="n">
-        <v>71596.3</v>
+        <v>79096.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>62096.3</v>
+        <v>69596.3</v>
       </c>
     </row>
     <row r="43">
@@ -1901,11 +1901,11 @@
         <v>125000</v>
       </c>
       <c r="D44" t="n">
-        <v>52808.2</v>
+        <v>62825.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1913,11 +1913,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>44308.2</v>
+        <v>54325.2</v>
       </c>
     </row>
     <row r="45">
@@ -1969,11 +1969,11 @@
         <v>150000</v>
       </c>
       <c r="D46" t="n">
-        <v>71221.3</v>
+        <v>86209.3</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1981,11 +1981,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>36866.3</v>
+        <v>51854.3</v>
       </c>
     </row>
     <row r="47">
@@ -2003,23 +2003,23 @@
         <v>150000</v>
       </c>
       <c r="D47" t="n">
-        <v>3273.8</v>
+        <v>4807.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>10000</v>
+        <v>10079.6</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>305.5%</t>
+          <t>209.7%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>-6726.2</v>
+        <v>-5271.8</v>
       </c>
     </row>
     <row r="48">
@@ -2071,11 +2071,11 @@
         <v>200000</v>
       </c>
       <c r="D49" t="n">
-        <v>197010</v>
+        <v>199388</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>98.5%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2083,11 +2083,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>142100</v>
+        <v>144478</v>
       </c>
     </row>
     <row r="50">
@@ -2105,11 +2105,11 @@
         <v>200000</v>
       </c>
       <c r="D50" t="n">
-        <v>89114</v>
+        <v>91094</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2117,11 +2117,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>69114</v>
+        <v>71094</v>
       </c>
     </row>
     <row r="51">
@@ -2173,19 +2173,19 @@
         <v>150000</v>
       </c>
       <c r="D52" t="n">
+        <v>2776</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
         <v>2378</v>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>1980</v>
-      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -2241,11 +2241,11 @@
         <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>37996.8</v>
+        <v>65796.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2253,11 +2253,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>15196.8</v>
+        <v>42996.8</v>
       </c>
     </row>
     <row r="55">
@@ -2351,15 +2351,15 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>29800</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>72986</v>
+        <v>43186</v>
       </c>
     </row>
     <row r="58">
@@ -2411,11 +2411,11 @@
         <v>110000</v>
       </c>
       <c r="D59" t="n">
-        <v>53194</v>
+        <v>53592</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>53194</v>
+        <v>53592</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>70000</v>
       </c>
       <c r="D60" t="n">
-        <v>7694</v>
+        <v>8092</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2457,11 +2457,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>6494</v>
+        <v>6892</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>160000</v>
       </c>
       <c r="D61" t="n">
-        <v>75069.04000000001</v>
+        <v>117267.04</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>75069.04000000001</v>
+        <v>117267.04</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>160000</v>
       </c>
       <c r="D62" t="n">
-        <v>60513.89</v>
+        <v>117691.02</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>48913.89</v>
+        <v>106091.02</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>160000</v>
       </c>
       <c r="D63" t="n">
-        <v>74593.05</v>
+        <v>107125.6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>74593.05</v>
+        <v>107125.6</v>
       </c>
     </row>
     <row r="64">
@@ -2615,11 +2615,11 @@
         <v>110000</v>
       </c>
       <c r="D65" t="n">
-        <v>85970.7</v>
+        <v>100970.7</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2627,11 +2627,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>61170.7</v>
+        <v>76170.7</v>
       </c>
     </row>
     <row r="66">
@@ -2649,11 +2649,11 @@
         <v>150000</v>
       </c>
       <c r="D66" t="n">
-        <v>42398</v>
+        <v>42796</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>42398</v>
+        <v>42796</v>
       </c>
     </row>
     <row r="67">
@@ -2683,11 +2683,11 @@
         <v>90000</v>
       </c>
       <c r="D67" t="n">
-        <v>104594</v>
+        <v>118590</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>131.8%</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2695,11 +2695,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>102594</v>
+        <v>116590</v>
       </c>
     </row>
     <row r="68">
@@ -2717,11 +2717,11 @@
         <v>80000</v>
       </c>
       <c r="D68" t="n">
-        <v>66590</v>
+        <v>66988</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>83.2%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>64910</v>
+        <v>65308</v>
       </c>
     </row>
     <row r="69">
@@ -2785,11 +2785,11 @@
         <v>70000</v>
       </c>
       <c r="D70" t="n">
-        <v>87192</v>
+        <v>87590</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>124.6%</t>
+          <t>125.1%</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>86192</v>
+        <v>86590</v>
       </c>
     </row>
     <row r="71">
@@ -2819,11 +2819,11 @@
         <v>50000</v>
       </c>
       <c r="D71" t="n">
-        <v>89986</v>
+        <v>100782</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>180.0%</t>
+          <t>201.6%</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2831,11 +2831,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>83386</v>
+        <v>94182</v>
       </c>
     </row>
     <row r="72">
@@ -2853,11 +2853,11 @@
         <v>30000</v>
       </c>
       <c r="D72" t="n">
-        <v>20796</v>
+        <v>21194</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>20796</v>
+        <v>21194</v>
       </c>
     </row>
     <row r="73">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
     </row>
     <row r="74">
@@ -2921,11 +2921,11 @@
         <v>170000</v>
       </c>
       <c r="D74" t="n">
-        <v>98782</v>
+        <v>109778</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2933,11 +2933,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>93382</v>
+        <v>104378</v>
       </c>
     </row>
     <row r="75">
@@ -2989,11 +2989,11 @@
         <v>50000</v>
       </c>
       <c r="D76" t="n">
-        <v>23792</v>
+        <v>24190</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>23792</v>
+        <v>24190</v>
       </c>
     </row>
     <row r="77">
@@ -3023,11 +3023,11 @@
         <v>40000</v>
       </c>
       <c r="D77" t="n">
-        <v>25192</v>
+        <v>38790</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>25192</v>
+        <v>38790</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>160562</v>
+        <v>176382</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>114.7%</t>
+          <t>126.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>160562</v>
+        <v>176382</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>594420</v>
+        <v>628880</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>169.8%</t>
+          <t>179.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>522140</v>
+        <v>556600</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>158464</v>
+        <v>166862</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>113.2%</t>
+          <t>119.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -553,11 +553,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>144064</v>
+        <v>152462</v>
       </c>
     </row>
     <row r="5">
@@ -609,11 +609,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>123582</v>
+        <v>138978</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>88.3%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -621,11 +621,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>101182</v>
+        <v>116578</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>140000</v>
       </c>
       <c r="D7" t="n">
-        <v>27396</v>
+        <v>37396</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>27396</v>
+        <v>37396</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>122278</v>
+        <v>143478</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>120598</v>
+        <v>141798</v>
       </c>
     </row>
     <row r="9">
@@ -813,11 +813,11 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>50366</v>
+        <v>91162</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>100.7%</t>
+          <t>182.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>44368</v>
+        <v>85164</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>104277.4700000001</v>
+        <v>108311.4700000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>104277.4700000001</v>
+        <v>108311.4700000001</v>
       </c>
     </row>
     <row r="14">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>244343.29</v>
+        <v>241280.29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>83.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>244343.29</v>
+        <v>241280.29</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>153595.3</v>
+        <v>155795.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>153595.3</v>
+        <v>155795.3</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>210771.11</v>
+        <v>226029.11</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>210771.11</v>
+        <v>226029.11</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>90000</v>
       </c>
       <c r="D18" t="n">
-        <v>7694</v>
+        <v>23092</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>7694</v>
+        <v>23092</v>
       </c>
     </row>
     <row r="19">
@@ -1085,11 +1085,11 @@
         <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>280724.8800000001</v>
+        <v>307005.8800000001</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>280724.8800000001</v>
+        <v>307005.8800000001</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>119016.8</v>
+        <v>119974.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>119016.8</v>
+        <v>119974.8</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>159380</v>
+        <v>177318</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>159380</v>
+        <v>177318</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>77164.36</v>
+        <v>129164.36</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>57368.36</v>
+        <v>109368.36</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>125075.68</v>
+        <v>185473.68</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>124279.68</v>
+        <v>184677.68</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>54986</v>
+        <v>114586</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>38586</v>
+        <v>98186</v>
       </c>
     </row>
     <row r="26">
@@ -1391,11 +1391,11 @@
         <v>200000</v>
       </c>
       <c r="D29" t="n">
-        <v>183450</v>
+        <v>185430</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1403,11 +1403,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>179490</v>
+        <v>181470</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>200000</v>
       </c>
       <c r="D30" t="n">
-        <v>398820</v>
+        <v>400800</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>199.4%</t>
+          <t>200.4%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>398820</v>
+        <v>400800</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>200000</v>
       </c>
       <c r="D31" t="n">
-        <v>177350</v>
+        <v>178250</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>170390</v>
+        <v>171290</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>200000</v>
       </c>
       <c r="D32" t="n">
-        <v>277500</v>
+        <v>297300</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>138.8%</t>
+          <t>148.7%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>165250</v>
+        <v>185050</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>250000</v>
       </c>
       <c r="D33" t="n">
-        <v>167420</v>
+        <v>169400</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>165440</v>
+        <v>167420</v>
       </c>
     </row>
     <row r="34">
@@ -1697,11 +1697,11 @@
         <v>250000</v>
       </c>
       <c r="D38" t="n">
-        <v>53760</v>
+        <v>54158</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1709,11 +1709,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>25840</v>
+        <v>26238</v>
       </c>
     </row>
     <row r="39">
@@ -1867,11 +1867,11 @@
         <v>115000</v>
       </c>
       <c r="D43" t="n">
-        <v>51295.68</v>
+        <v>57093.68</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>51295.68</v>
+        <v>57093.68</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>125000</v>
       </c>
       <c r="D44" t="n">
-        <v>62825.2</v>
+        <v>73223.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1913,11 +1913,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>54325.2</v>
+        <v>64723.2</v>
       </c>
     </row>
     <row r="45">
@@ -1969,11 +1969,11 @@
         <v>150000</v>
       </c>
       <c r="D46" t="n">
-        <v>86209.3</v>
+        <v>99262.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1981,11 +1981,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>51854.3</v>
+        <v>64907.5</v>
       </c>
     </row>
     <row r="47">
@@ -2037,11 +2037,11 @@
         <v>100000</v>
       </c>
       <c r="D48" t="n">
-        <v>36385.77</v>
+        <v>46385.77</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2049,11 +2049,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>32425.77</v>
+        <v>42425.77</v>
       </c>
     </row>
     <row r="49">
@@ -2071,11 +2071,11 @@
         <v>200000</v>
       </c>
       <c r="D49" t="n">
-        <v>199388</v>
+        <v>229388</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>114.7%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2083,11 +2083,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>144478</v>
+        <v>174478</v>
       </c>
     </row>
     <row r="50">
@@ -2241,11 +2241,11 @@
         <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>65796.8</v>
+        <v>71796.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2253,11 +2253,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>42996.8</v>
+        <v>48996.8</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>50000</v>
       </c>
       <c r="D55" t="n">
-        <v>9792</v>
+        <v>10190</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>9792</v>
+        <v>10190</v>
       </c>
     </row>
     <row r="56">
@@ -2309,11 +2309,11 @@
         <v>30000</v>
       </c>
       <c r="D56" t="n">
-        <v>2476</v>
+        <v>12874</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2476</v>
+        <v>12874</v>
       </c>
     </row>
     <row r="57">
@@ -2411,11 +2411,11 @@
         <v>110000</v>
       </c>
       <c r="D59" t="n">
-        <v>53592</v>
+        <v>53990</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>53592</v>
+        <v>53990</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>70000</v>
       </c>
       <c r="D60" t="n">
-        <v>8092</v>
+        <v>8690</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2457,11 +2457,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>6892</v>
+        <v>7490</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>160000</v>
       </c>
       <c r="D61" t="n">
-        <v>117267.04</v>
+        <v>133407.13</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>83.4%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>117267.04</v>
+        <v>133407.13</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>160000</v>
       </c>
       <c r="D62" t="n">
-        <v>117691.02</v>
+        <v>134391.27</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>106091.02</v>
+        <v>122791.27</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>160000</v>
       </c>
       <c r="D63" t="n">
-        <v>107125.6</v>
+        <v>123192.99</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>107125.6</v>
+        <v>123192.99</v>
       </c>
     </row>
     <row r="64">
@@ -2615,11 +2615,11 @@
         <v>110000</v>
       </c>
       <c r="D65" t="n">
-        <v>100970.7</v>
+        <v>109270.7</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2627,11 +2627,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>76170.7</v>
+        <v>84470.7</v>
       </c>
     </row>
     <row r="66">
@@ -2649,11 +2649,11 @@
         <v>150000</v>
       </c>
       <c r="D66" t="n">
-        <v>42796</v>
+        <v>43596</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>42796</v>
+        <v>43596</v>
       </c>
     </row>
     <row r="67">
@@ -2683,11 +2683,11 @@
         <v>90000</v>
       </c>
       <c r="D67" t="n">
-        <v>118590</v>
+        <v>118988</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>131.8%</t>
+          <t>132.2%</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>116590</v>
+        <v>116988</v>
       </c>
     </row>
     <row r="68">
@@ -2819,11 +2819,11 @@
         <v>50000</v>
       </c>
       <c r="D71" t="n">
-        <v>100782</v>
+        <v>101180</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>201.6%</t>
+          <t>202.4%</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>94182</v>
+        <v>94580</v>
       </c>
     </row>
     <row r="72">
@@ -3023,11 +3023,11 @@
         <v>40000</v>
       </c>
       <c r="D77" t="n">
-        <v>38790</v>
+        <v>46790</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>117.0%</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>38790</v>
+        <v>46790</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>176382</v>
+        <v>181362</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>126.0%</t>
+          <t>129.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>176382</v>
+        <v>181362</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>628880</v>
+        <v>653680</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>179.7%</t>
+          <t>186.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -519,11 +519,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>556600</v>
+        <v>581400</v>
       </c>
     </row>
     <row r="4">
@@ -549,15 +549,15 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>14400</v>
+        <v>15600</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>152462</v>
+        <v>151262</v>
       </c>
     </row>
     <row r="5">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>143478</v>
+        <v>163278</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>141798</v>
+        <v>161598</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>140000</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-598</v>
+        <v>9402</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>140000</v>
       </c>
       <c r="D10" t="n">
-        <v>45068</v>
+        <v>55466</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -757,11 +757,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>42068</v>
+        <v>52466</v>
       </c>
     </row>
     <row r="11">
@@ -847,11 +847,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>108311.4700000001</v>
+        <v>121587.4700000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>108311.4700000001</v>
+        <v>121587.4700000001</v>
       </c>
     </row>
     <row r="14">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>241280.29</v>
+        <v>256280.29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>83.2%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>241280.29</v>
+        <v>256280.29</v>
       </c>
     </row>
     <row r="16">
@@ -1051,11 +1051,11 @@
         <v>90000</v>
       </c>
       <c r="D19" t="n">
-        <v>10000</v>
+        <v>10398</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>10000</v>
+        <v>10398</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>307005.8800000001</v>
+        <v>355607.17</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>104.6%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>307005.8800000001</v>
+        <v>355607.17</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>119974.8</v>
+        <v>120974.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>119974.8</v>
+        <v>120974.8</v>
       </c>
     </row>
     <row r="22">
@@ -1187,11 +1187,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>129164.36</v>
+        <v>149164.36</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>109368.36</v>
+        <v>129368.36</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>185473.68</v>
+        <v>205473.68</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>184677.68</v>
+        <v>204677.68</v>
       </c>
     </row>
     <row r="25">
@@ -1263,15 +1263,15 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>16400</v>
+        <v>18400</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>98186</v>
+        <v>96186</v>
       </c>
     </row>
     <row r="26">
@@ -1391,11 +1391,11 @@
         <v>200000</v>
       </c>
       <c r="D29" t="n">
-        <v>185430</v>
+        <v>187410</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>181470</v>
+        <v>183450</v>
       </c>
     </row>
     <row r="30">
@@ -1535,15 +1535,15 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1980</v>
+        <v>23960</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>167420</v>
+        <v>145440</v>
       </c>
     </row>
     <row r="34">
@@ -1637,15 +1637,15 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>57900</v>
+        <v>55920</v>
       </c>
     </row>
     <row r="37">
@@ -1739,15 +1739,15 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3510</v>
+        <v>5490</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>16470</v>
+        <v>14490</v>
       </c>
     </row>
     <row r="40">
@@ -1765,11 +1765,11 @@
         <v>250000</v>
       </c>
       <c r="D40" t="n">
-        <v>199405.02</v>
+        <v>260205.02</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>104.1%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>199405.02</v>
+        <v>260205.02</v>
       </c>
     </row>
     <row r="41">
@@ -1867,11 +1867,11 @@
         <v>115000</v>
       </c>
       <c r="D43" t="n">
-        <v>57093.68</v>
+        <v>58593.68</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>57093.68</v>
+        <v>58593.68</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>125000</v>
       </c>
       <c r="D44" t="n">
-        <v>73223.2</v>
+        <v>73621.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1913,11 +1913,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>64723.2</v>
+        <v>65121.2</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>65000</v>
       </c>
       <c r="D45" t="n">
-        <v>33794</v>
+        <v>43794</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>33794</v>
+        <v>43794</v>
       </c>
     </row>
     <row r="46">
@@ -2105,11 +2105,11 @@
         <v>200000</v>
       </c>
       <c r="D50" t="n">
-        <v>91094</v>
+        <v>96444</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2117,11 +2117,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>71094</v>
+        <v>76444</v>
       </c>
     </row>
     <row r="51">
@@ -2139,11 +2139,11 @@
         <v>200000</v>
       </c>
       <c r="D51" t="n">
-        <v>60750</v>
+        <v>62730</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2151,11 +2151,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>54810</v>
+        <v>56790</v>
       </c>
     </row>
     <row r="52">
@@ -2207,11 +2207,11 @@
         <v>70000</v>
       </c>
       <c r="D53" t="n">
-        <v>30074</v>
+        <v>45074</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2219,11 +2219,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>10990.67</v>
+        <v>25990.67</v>
       </c>
     </row>
     <row r="54">
@@ -2275,11 +2275,11 @@
         <v>50000</v>
       </c>
       <c r="D55" t="n">
-        <v>10190</v>
+        <v>10588</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>10190</v>
+        <v>10588</v>
       </c>
     </row>
     <row r="56">
@@ -2309,11 +2309,11 @@
         <v>30000</v>
       </c>
       <c r="D56" t="n">
-        <v>12874</v>
+        <v>13272</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>12874</v>
+        <v>13272</v>
       </c>
     </row>
     <row r="57">
@@ -2445,11 +2445,11 @@
         <v>70000</v>
       </c>
       <c r="D60" t="n">
-        <v>8690</v>
+        <v>18690</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2457,11 +2457,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>7490</v>
+        <v>17490</v>
       </c>
     </row>
     <row r="61">
@@ -2513,11 +2513,11 @@
         <v>160000</v>
       </c>
       <c r="D62" t="n">
-        <v>134391.27</v>
+        <v>150598.95</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>122791.27</v>
+        <v>138998.95</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>160000</v>
       </c>
       <c r="D63" t="n">
-        <v>123192.99</v>
+        <v>143192.99</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>123192.99</v>
+        <v>143192.99</v>
       </c>
     </row>
     <row r="64">
@@ -2581,11 +2581,11 @@
         <v>110000</v>
       </c>
       <c r="D64" t="n">
-        <v>47796</v>
+        <v>56976</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>47796</v>
+        <v>56976</v>
       </c>
     </row>
     <row r="65">
@@ -2615,23 +2615,23 @@
         <v>110000</v>
       </c>
       <c r="D65" t="n">
-        <v>109270.7</v>
+        <v>117843.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>24800</v>
+        <v>46300</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>84470.7</v>
+        <v>71543.39999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2649,11 +2649,11 @@
         <v>150000</v>
       </c>
       <c r="D66" t="n">
-        <v>43596</v>
+        <v>68596</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>43596</v>
+        <v>68596</v>
       </c>
     </row>
     <row r="67">
@@ -2853,11 +2853,11 @@
         <v>30000</v>
       </c>
       <c r="D72" t="n">
-        <v>21194</v>
+        <v>31194</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>104.0%</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>21194</v>
+        <v>31194</v>
       </c>
     </row>
     <row r="73">
@@ -2921,11 +2921,11 @@
         <v>170000</v>
       </c>
       <c r="D74" t="n">
-        <v>109778</v>
+        <v>124376</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2933,11 +2933,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>104378</v>
+        <v>118976</v>
       </c>
     </row>
     <row r="75">
@@ -2997,15 +2997,15 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>24190</v>
+        <v>23690</v>
       </c>
     </row>
     <row r="77">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>181362</v>
+        <v>176682</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>129.5%</t>
+          <t>126.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>181362</v>
+        <v>176682</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>653680</v>
+        <v>689916</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>186.8%</t>
+          <t>197.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>72280</v>
+        <v>123380</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>581400</v>
+        <v>566536</v>
       </c>
     </row>
     <row r="4">
@@ -575,11 +575,11 @@
         <v>140000</v>
       </c>
       <c r="D5" t="n">
-        <v>92297.89999999999</v>
+        <v>92597.89999999999</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>89117.89999999999</v>
+        <v>89417.89999999999</v>
       </c>
     </row>
     <row r="6">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>163278</v>
+        <v>163676</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>161598</v>
+        <v>161996</v>
       </c>
     </row>
     <row r="9">
@@ -719,15 +719,15 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>598</v>
+        <v>14998</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>150.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>9402</v>
+        <v>-4998</v>
       </c>
     </row>
     <row r="10">
@@ -813,11 +813,11 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>91162</v>
+        <v>101958</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>182.3%</t>
+          <t>203.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>85164</v>
+        <v>95960</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>121587.4700000001</v>
+        <v>131587.4700000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>121587.4700000001</v>
+        <v>131587.4700000001</v>
       </c>
     </row>
     <row r="14">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>256280.29</v>
+        <v>256678.29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>256280.29</v>
+        <v>256678.29</v>
       </c>
     </row>
     <row r="16">
@@ -1017,11 +1017,11 @@
         <v>90000</v>
       </c>
       <c r="D18" t="n">
-        <v>23092</v>
+        <v>26092</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>23092</v>
+        <v>26092</v>
       </c>
     </row>
     <row r="19">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>177318</v>
+        <v>177716</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>177318</v>
+        <v>177716</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>149164.36</v>
+        <v>159164.36</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>83.8%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>129368.36</v>
+        <v>139368.36</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>205473.68</v>
+        <v>210473.68</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>204677.68</v>
+        <v>209677.68</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>114586</v>
+        <v>115184</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>96186</v>
+        <v>96784</v>
       </c>
     </row>
     <row r="26">
@@ -1535,15 +1535,15 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>23960</v>
+        <v>40760</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>145440</v>
+        <v>128640</v>
       </c>
     </row>
     <row r="34">
@@ -1595,11 +1595,11 @@
         <v>250000</v>
       </c>
       <c r="D35" t="n">
-        <v>99600</v>
+        <v>99998</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>99420</v>
+        <v>99818</v>
       </c>
     </row>
     <row r="36">
@@ -1697,11 +1697,11 @@
         <v>250000</v>
       </c>
       <c r="D38" t="n">
-        <v>54158</v>
+        <v>58118</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1709,11 +1709,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>26238</v>
+        <v>30198</v>
       </c>
     </row>
     <row r="39">
@@ -1765,23 +1765,23 @@
         <v>250000</v>
       </c>
       <c r="D40" t="n">
-        <v>260205.02</v>
+        <v>285205.02</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>104.1%</t>
+          <t>114.1%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>260205.02</v>
+        <v>277205.02</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>130000</v>
       </c>
       <c r="D41" t="n">
-        <v>60300</v>
+        <v>103100</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1811,11 +1811,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>29000</v>
+        <v>71800</v>
       </c>
     </row>
     <row r="42">
@@ -1901,11 +1901,11 @@
         <v>125000</v>
       </c>
       <c r="D44" t="n">
-        <v>73621.2</v>
+        <v>83621.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1913,11 +1913,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>65121.2</v>
+        <v>75121.2</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>65000</v>
       </c>
       <c r="D45" t="n">
-        <v>43794</v>
+        <v>44192</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>43794</v>
+        <v>44192</v>
       </c>
     </row>
     <row r="46">
@@ -2079,15 +2079,15 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>54910</v>
+        <v>56890</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>174478</v>
+        <v>172498</v>
       </c>
     </row>
     <row r="50">
@@ -2105,11 +2105,11 @@
         <v>200000</v>
       </c>
       <c r="D50" t="n">
-        <v>96444</v>
+        <v>97121.60000000001</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2117,11 +2117,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>76444</v>
+        <v>77121.60000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2207,11 +2207,11 @@
         <v>70000</v>
       </c>
       <c r="D53" t="n">
-        <v>45074</v>
+        <v>51870</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2219,11 +2219,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>25990.67</v>
+        <v>32786.67</v>
       </c>
     </row>
     <row r="54">
@@ -2275,11 +2275,11 @@
         <v>50000</v>
       </c>
       <c r="D55" t="n">
-        <v>10588</v>
+        <v>10986</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>10588</v>
+        <v>10986</v>
       </c>
     </row>
     <row r="56">
@@ -2343,11 +2343,11 @@
         <v>110000</v>
       </c>
       <c r="D57" t="n">
-        <v>72986</v>
+        <v>92786</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>84.4%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2355,11 +2355,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>43186</v>
+        <v>62986</v>
       </c>
     </row>
     <row r="58">
@@ -2385,15 +2385,15 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>14600</v>
+        <v>18200</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>114388</v>
+        <v>110788</v>
       </c>
     </row>
     <row r="59">
@@ -2479,11 +2479,11 @@
         <v>160000</v>
       </c>
       <c r="D61" t="n">
-        <v>133407.13</v>
+        <v>133805.13</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>83.6%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>133407.13</v>
+        <v>133805.13</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>160000</v>
       </c>
       <c r="D62" t="n">
-        <v>150598.95</v>
+        <v>166598.95</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>104.1%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>138998.95</v>
+        <v>154998.95</v>
       </c>
     </row>
     <row r="63">
@@ -2581,11 +2581,11 @@
         <v>110000</v>
       </c>
       <c r="D64" t="n">
-        <v>56976</v>
+        <v>80874</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>56976</v>
+        <v>80874</v>
       </c>
     </row>
     <row r="65">
@@ -2683,23 +2683,23 @@
         <v>90000</v>
       </c>
       <c r="D67" t="n">
-        <v>118988</v>
+        <v>132188</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>132.2%</t>
+          <t>146.9%</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>116988</v>
+        <v>121188</v>
       </c>
     </row>
     <row r="68">
@@ -2751,11 +2751,11 @@
         <v>80000</v>
       </c>
       <c r="D69" t="n">
-        <v>43588</v>
+        <v>53588</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>43588</v>
+        <v>53588</v>
       </c>
     </row>
     <row r="70">
@@ -2785,11 +2785,11 @@
         <v>70000</v>
       </c>
       <c r="D70" t="n">
-        <v>87590</v>
+        <v>107390</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>125.1%</t>
+          <t>153.4%</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2797,11 +2797,11 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>86590</v>
+        <v>106390</v>
       </c>
     </row>
     <row r="71">
@@ -2819,11 +2819,11 @@
         <v>50000</v>
       </c>
       <c r="D71" t="n">
-        <v>101180</v>
+        <v>124780</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>202.4%</t>
+          <t>249.6%</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2831,11 +2831,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>94580</v>
+        <v>118180</v>
       </c>
     </row>
     <row r="72">
@@ -2921,11 +2921,11 @@
         <v>170000</v>
       </c>
       <c r="D74" t="n">
-        <v>124376</v>
+        <v>134376</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2933,11 +2933,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>118976</v>
+        <v>128976</v>
       </c>
     </row>
     <row r="75">
@@ -3023,11 +3023,11 @@
         <v>40000</v>
       </c>
       <c r="D77" t="n">
-        <v>46790</v>
+        <v>47388</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>117.0%</t>
+          <t>118.5%</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>46790</v>
+        <v>47388</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>176682</v>
+        <v>177080</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>126.2%</t>
+          <t>126.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>176682</v>
+        <v>177080</v>
       </c>
     </row>
     <row r="3">
@@ -507,23 +507,23 @@
         <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>689916</v>
+        <v>717554</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>197.1%</t>
+          <t>205.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>123380</v>
+        <v>132380</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>566536</v>
+        <v>585174</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>166862</v>
+        <v>186238</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>119.2%</t>
+          <t>133.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -553,11 +553,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>151262</v>
+        <v>170638</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>140000</v>
       </c>
       <c r="D5" t="n">
-        <v>92597.89999999999</v>
+        <v>138993.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>89417.89999999999</v>
+        <v>135813.9</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>138978</v>
+        <v>166174</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>118.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -621,11 +621,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>116578</v>
+        <v>143774</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>140000</v>
       </c>
       <c r="D7" t="n">
-        <v>37396</v>
+        <v>37794</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>37396</v>
+        <v>37794</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>163676</v>
+        <v>224472</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>106.9%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>161996</v>
+        <v>222792</v>
       </c>
     </row>
     <row r="9">
@@ -719,15 +719,15 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>14998</v>
+        <v>19998</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>150.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-4998</v>
+        <v>-9998</v>
       </c>
     </row>
     <row r="10">
@@ -745,19 +745,19 @@
         <v>140000</v>
       </c>
       <c r="D10" t="n">
-        <v>55466</v>
+        <v>55864</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3000</v>
+        <v>3398</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -813,11 +813,11 @@
         <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>101958</v>
+        <v>123152</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>203.9%</t>
+          <t>246.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -825,11 +825,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>95960</v>
+        <v>117154</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>131587.4700000001</v>
+        <v>134456.4700000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>131587.4700000001</v>
+        <v>134456.4700000001</v>
       </c>
     </row>
     <row r="14">
@@ -915,11 +915,11 @@
         <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>256678.29</v>
+        <v>280708.09</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>256678.29</v>
+        <v>280708.09</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>155795.3</v>
+        <v>194629.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>155795.3</v>
+        <v>194629.3</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>226029.11</v>
+        <v>243552.11</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>105.9%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>226029.11</v>
+        <v>243552.11</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>90000</v>
       </c>
       <c r="D18" t="n">
-        <v>26092</v>
+        <v>26658</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>26092</v>
+        <v>26658</v>
       </c>
     </row>
     <row r="19">
@@ -1085,11 +1085,11 @@
         <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>355607.17</v>
+        <v>397183.17</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>104.6%</t>
+          <t>116.8%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>355607.17</v>
+        <v>397183.17</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>120974.8</v>
+        <v>124110.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>120974.8</v>
+        <v>124110.8</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>177716</v>
+        <v>211877.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>177716</v>
+        <v>211877.5</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>159164.36</v>
+        <v>169562.36</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>139368.36</v>
+        <v>149766.36</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>210473.68</v>
+        <v>262537.04</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>138.2%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>209677.68</v>
+        <v>261741.04</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>115184</v>
+        <v>115782</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>96784</v>
+        <v>97382</v>
       </c>
     </row>
     <row r="26">
@@ -1289,23 +1289,23 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>24568</v>
+        <v>46828</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>19000</v>
+        <v>19598</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5568</v>
+        <v>27230</v>
       </c>
     </row>
     <row r="27">
@@ -1357,11 +1357,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>6146</v>
+        <v>8126</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>6146</v>
+        <v>8126</v>
       </c>
     </row>
     <row r="29">
@@ -1391,23 +1391,23 @@
         <v>200000</v>
       </c>
       <c r="D29" t="n">
-        <v>187410</v>
+        <v>207210</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>103.6%</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3960</v>
+        <v>55740</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>183450</v>
+        <v>151470</v>
       </c>
     </row>
     <row r="30">
@@ -1433,15 +1433,15 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>7920</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>400800</v>
+        <v>392880</v>
       </c>
     </row>
     <row r="31">
@@ -1459,23 +1459,23 @@
         <v>200000</v>
       </c>
       <c r="D31" t="n">
-        <v>178250</v>
+        <v>180230</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6960</v>
+        <v>10920</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>171290</v>
+        <v>169310</v>
       </c>
     </row>
     <row r="32">
@@ -1501,15 +1501,15 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>112250</v>
+        <v>120170</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>185050</v>
+        <v>177130</v>
       </c>
     </row>
     <row r="33">
@@ -1535,15 +1535,15 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>40760</v>
+        <v>46700</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>128640</v>
+        <v>122700</v>
       </c>
     </row>
     <row r="34">
@@ -1561,23 +1561,23 @@
         <v>250000</v>
       </c>
       <c r="D34" t="n">
-        <v>109500</v>
+        <v>160370</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>100000</v>
+        <v>101980</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>9500</v>
+        <v>58390</v>
       </c>
     </row>
     <row r="35">
@@ -1595,23 +1595,23 @@
         <v>250000</v>
       </c>
       <c r="D35" t="n">
-        <v>99998</v>
+        <v>101978</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>180</v>
+        <v>13380</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>99818</v>
+        <v>88598</v>
       </c>
     </row>
     <row r="36">
@@ -1671,15 +1671,15 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>3960</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>14320</v>
+        <v>10360</v>
       </c>
     </row>
     <row r="38">
@@ -1697,11 +1697,11 @@
         <v>250000</v>
       </c>
       <c r="D38" t="n">
-        <v>58118</v>
+        <v>109898</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1709,11 +1709,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>30198</v>
+        <v>81978</v>
       </c>
     </row>
     <row r="39">
@@ -1765,11 +1765,11 @@
         <v>250000</v>
       </c>
       <c r="D40" t="n">
-        <v>285205.02</v>
+        <v>302293.52</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>114.1%</t>
+          <t>120.9%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>277205.02</v>
+        <v>294293.52</v>
       </c>
     </row>
     <row r="41">
@@ -1799,23 +1799,23 @@
         <v>130000</v>
       </c>
       <c r="D41" t="n">
-        <v>103100</v>
+        <v>121096</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>93.2%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>31300</v>
+        <v>35300</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>71800</v>
+        <v>85796</v>
       </c>
     </row>
     <row r="42">
@@ -1833,11 +1833,11 @@
         <v>115000</v>
       </c>
       <c r="D42" t="n">
-        <v>79096.3</v>
+        <v>88876.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>69596.3</v>
+        <v>79376.3</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>115000</v>
       </c>
       <c r="D43" t="n">
-        <v>58593.68</v>
+        <v>96801.38</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>58593.68</v>
+        <v>96801.38</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>125000</v>
       </c>
       <c r="D44" t="n">
-        <v>83621.2</v>
+        <v>95018.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1913,11 +1913,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>75121.2</v>
+        <v>86518.2</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>65000</v>
       </c>
       <c r="D45" t="n">
-        <v>44192</v>
+        <v>59012</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>44192</v>
+        <v>59012</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>150000</v>
       </c>
       <c r="D46" t="n">
-        <v>99262.5</v>
+        <v>99012.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1981,11 +1981,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>64907.5</v>
+        <v>64657.2</v>
       </c>
     </row>
     <row r="47">
@@ -2071,11 +2071,11 @@
         <v>200000</v>
       </c>
       <c r="D49" t="n">
-        <v>229388</v>
+        <v>231368</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>114.7%</t>
+          <t>115.7%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2083,11 +2083,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>172498</v>
+        <v>174478</v>
       </c>
     </row>
     <row r="50">
@@ -2105,11 +2105,11 @@
         <v>200000</v>
       </c>
       <c r="D50" t="n">
-        <v>97121.60000000001</v>
+        <v>101559.3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2117,11 +2117,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>77121.60000000001</v>
+        <v>81559.3</v>
       </c>
     </row>
     <row r="51">
@@ -2139,11 +2139,11 @@
         <v>200000</v>
       </c>
       <c r="D51" t="n">
-        <v>62730</v>
+        <v>64710</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2151,11 +2151,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>56790</v>
+        <v>58770</v>
       </c>
     </row>
     <row r="52">
@@ -2173,11 +2173,11 @@
         <v>150000</v>
       </c>
       <c r="D52" t="n">
-        <v>2776</v>
+        <v>3514</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2185,11 +2185,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>398</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>70000</v>
       </c>
       <c r="D53" t="n">
-        <v>51870</v>
+        <v>52268</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2219,11 +2219,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>32786.67</v>
+        <v>33184.67</v>
       </c>
     </row>
     <row r="54">
@@ -2275,11 +2275,11 @@
         <v>50000</v>
       </c>
       <c r="D55" t="n">
-        <v>10986</v>
+        <v>18986</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>10986</v>
+        <v>18986</v>
       </c>
     </row>
     <row r="56">
@@ -2309,11 +2309,11 @@
         <v>30000</v>
       </c>
       <c r="D56" t="n">
-        <v>13272</v>
+        <v>14670</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>13272</v>
+        <v>14670</v>
       </c>
     </row>
     <row r="57">
@@ -2343,11 +2343,11 @@
         <v>110000</v>
       </c>
       <c r="D57" t="n">
-        <v>92786</v>
+        <v>99582</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2355,11 +2355,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>62986</v>
+        <v>69782</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>110000</v>
       </c>
       <c r="D58" t="n">
-        <v>128988</v>
+        <v>129386</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>117.3%</t>
+          <t>117.6%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>110788</v>
+        <v>111186</v>
       </c>
     </row>
     <row r="59">
@@ -2479,23 +2479,23 @@
         <v>160000</v>
       </c>
       <c r="D61" t="n">
-        <v>133805.13</v>
+        <v>155005.13</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>133805.13</v>
+        <v>151005.13</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>160000</v>
       </c>
       <c r="D62" t="n">
-        <v>166598.95</v>
+        <v>187038.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>104.1%</t>
+          <t>116.9%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>154998.95</v>
+        <v>175438.5</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>160000</v>
       </c>
       <c r="D63" t="n">
-        <v>143192.99</v>
+        <v>144390.99</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>143192.99</v>
+        <v>144390.99</v>
       </c>
     </row>
     <row r="64">
@@ -2615,11 +2615,11 @@
         <v>110000</v>
       </c>
       <c r="D65" t="n">
-        <v>117843.4</v>
+        <v>154443.41</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>140.4%</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2627,11 +2627,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>71543.39999999999</v>
+        <v>108143.41</v>
       </c>
     </row>
     <row r="66">
@@ -2649,11 +2649,11 @@
         <v>150000</v>
       </c>
       <c r="D66" t="n">
-        <v>68596</v>
+        <v>69396</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>68596</v>
+        <v>69396</v>
       </c>
     </row>
     <row r="67">
@@ -2683,11 +2683,11 @@
         <v>90000</v>
       </c>
       <c r="D67" t="n">
-        <v>132188</v>
+        <v>146184</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>146.9%</t>
+          <t>162.4%</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2695,11 +2695,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>121188</v>
+        <v>135184</v>
       </c>
     </row>
     <row r="68">
@@ -2751,11 +2751,11 @@
         <v>80000</v>
       </c>
       <c r="D69" t="n">
-        <v>53588</v>
+        <v>53986</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>53588</v>
+        <v>53986</v>
       </c>
     </row>
     <row r="70">
@@ -2785,11 +2785,11 @@
         <v>70000</v>
       </c>
       <c r="D70" t="n">
-        <v>107390</v>
+        <v>107788</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>153.4%</t>
+          <t>154.0%</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>106390</v>
+        <v>106788</v>
       </c>
     </row>
     <row r="71">
@@ -2819,11 +2819,11 @@
         <v>50000</v>
       </c>
       <c r="D71" t="n">
-        <v>124780</v>
+        <v>125974</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>249.6%</t>
+          <t>251.9%</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2831,11 +2831,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>118180</v>
+        <v>119374</v>
       </c>
     </row>
     <row r="72">
@@ -2921,23 +2921,23 @@
         <v>170000</v>
       </c>
       <c r="D74" t="n">
-        <v>134376</v>
+        <v>154774</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>5400</v>
+        <v>10400</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>128976</v>
+        <v>144374</v>
       </c>
     </row>
     <row r="75">
@@ -2989,23 +2989,23 @@
         <v>50000</v>
       </c>
       <c r="D76" t="n">
-        <v>24190</v>
+        <v>40588</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>500</v>
+        <v>898</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>23690</v>
+        <v>39690</v>
       </c>
     </row>
     <row r="77">
@@ -3023,11 +3023,11 @@
         <v>40000</v>
       </c>
       <c r="D77" t="n">
-        <v>47388</v>
+        <v>48184</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>118.5%</t>
+          <t>120.5%</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>47388</v>
+        <v>48184</v>
       </c>
     </row>
   </sheetData>
